--- a/data/Capus_LHommeBicycle_1893/Capus_LHommeBicycle_1893.xlsx
+++ b/data/Capus_LHommeBicycle_1893/Capus_LHommeBicycle_1893.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mathilde\Desktop\Doctorat - 2025-2028\Pipeline\FrenchSFcorpus\src\Ontology\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mathilde\Desktop\Doctorat - 2025-2028\Pipeline\SFonto\data\Capus_LHommeBicycle_1893\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{340AE477-BC5F-4CC6-8537-8C3D943D3829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4094CCE4-3340-4B3F-9D6C-01C86BE5529E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Work" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="955" uniqueCount="473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="425">
   <si>
     <t>Classe</t>
   </si>
@@ -205,12 +205,6 @@
     <t>G3_Psychological_State</t>
   </si>
   <si>
-    <t>G18_Textual_Feature</t>
-  </si>
-  <si>
-    <t>E55_Type</t>
-  </si>
-  <si>
     <t>G0_Character-Stoff</t>
   </si>
   <si>
@@ -244,9 +238,6 @@
     <t>French Expression</t>
   </si>
   <si>
-    <t>:type_comedy</t>
-  </si>
-  <si>
     <t>Characters</t>
   </si>
   <si>
@@ -437,9 +428,6 @@
   </si>
   <si>
     <t>G5 Narrative Event</t>
-  </si>
-  <si>
-    <t>:Feature_structure_4_chapters</t>
   </si>
   <si>
     <t>G9 Narrative Unit</t>
@@ -523,55 +511,16 @@
     <t>:type_celebrity_relation</t>
   </si>
   <si>
-    <t>:type_role_obstacle</t>
-  </si>
-  <si>
-    <t>:type_role_catalyst</t>
-  </si>
-  <si>
     <t>:Feature_heterodiegetic_narrator</t>
   </si>
   <si>
-    <t>:Feature_ironic_tone</t>
-  </si>
-  <si>
-    <t>:Feature_direct_speech</t>
-  </si>
-  <si>
     <t>:type_short_story</t>
   </si>
   <si>
-    <t>:type_science_fiction</t>
-  </si>
-  <si>
     <t>:type_written_text</t>
   </si>
   <si>
     <t>:type_society</t>
-  </si>
-  <si>
-    <t>Route</t>
-  </si>
-  <si>
-    <t>Obstacle</t>
-  </si>
-  <si>
-    <t>Fabula</t>
-  </si>
-  <si>
-    <t>Syuzhet</t>
-  </si>
-  <si>
-    <t>:type_heterodiegetic_narrator</t>
-  </si>
-  <si>
-    <t>:type_ironic_tone</t>
-  </si>
-  <si>
-    <t>:type_structure_4_chapters</t>
-  </si>
-  <si>
-    <t>:type_direct_speech</t>
   </si>
   <si>
     <t>:Midi</t>
@@ -645,79 +594,7 @@
     <t>:type_age</t>
   </si>
   <si>
-    <t>Heterodiegetic narrator</t>
-  </si>
-  <si>
-    <t>Ironic tone</t>
-  </si>
-  <si>
-    <t>Chapter structure</t>
-  </si>
-  <si>
-    <t>Direct speech</t>
-  </si>
-  <si>
-    <t>Short Story</t>
-  </si>
-  <si>
-    <t>Science fiction</t>
-  </si>
-  <si>
-    <t>Comedy</t>
-  </si>
-  <si>
-    <t>Written text</t>
-  </si>
-  <si>
-    <t>Biological novum</t>
-  </si>
-  <si>
-    <t>Religious object</t>
-  </si>
-  <si>
-    <t>Medical object</t>
-  </si>
-  <si>
-    <t>Society</t>
-  </si>
-  <si>
-    <t>Historical period</t>
-  </si>
-  <si>
-    <t>Region</t>
-  </si>
-  <si>
-    <t>Private location</t>
-  </si>
-  <si>
     <t>:type_institutional_location</t>
-  </si>
-  <si>
-    <t>Institutional location</t>
-  </si>
-  <si>
-    <t>Natural location</t>
-  </si>
-  <si>
-    <t>City</t>
-  </si>
-  <si>
-    <t>Familial relation</t>
-  </si>
-  <si>
-    <t>Romantic relation</t>
-  </si>
-  <si>
-    <t>Medical relation</t>
-  </si>
-  <si>
-    <t>Celebrity relation</t>
-  </si>
-  <si>
-    <t>Catalyst</t>
-  </si>
-  <si>
-    <t>Character age</t>
   </si>
   <si>
     <t>GP1 is character in</t>
@@ -736,12 +613,6 @@
     <t>:Feature_third_person_narrator</t>
   </si>
   <si>
-    <t>Third person narrator</t>
-  </si>
-  <si>
-    <t>:type_third_person_narrator</t>
-  </si>
-  <si>
     <t>L'Homme-Bicycle (work)</t>
   </si>
   <si>
@@ -776,9 +647,6 @@
   </si>
   <si>
     <t>:type_institutional_object</t>
-  </si>
-  <si>
-    <t>Institutional object</t>
   </si>
   <si>
     <t>Common means of transportation</t>
@@ -1249,27 +1117,6 @@
     <t>:Skepticism</t>
   </si>
   <si>
-    <t>:Biographical_feature</t>
-  </si>
-  <si>
-    <t>Biographical feature</t>
-  </si>
-  <si>
-    <t>:Physical_feature</t>
-  </si>
-  <si>
-    <t>Physical feature</t>
-  </si>
-  <si>
-    <t>:Psychological_feature</t>
-  </si>
-  <si>
-    <t>Psychological feature</t>
-  </si>
-  <si>
-    <t>Technological object</t>
-  </si>
-  <si>
     <t>Melancholy</t>
   </si>
   <si>
@@ -1482,6 +1329,15 @@
   </si>
   <si>
     <t>:Female_character</t>
+  </si>
+  <si>
+    <t>GP0_has_feature</t>
+  </si>
+  <si>
+    <t>:Feature_science_fiction</t>
+  </si>
+  <si>
+    <t>:Feature_humorous_register</t>
   </si>
 </sst>
 </file>
@@ -1632,7 +1488,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1668,17 +1524,6 @@
       <bottom style="thin">
         <color rgb="FFCCCCCC"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -1762,9 +1607,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1802,6 +1644,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1832,13 +1675,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>129540</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2164,7 +2007,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -2173,18 +2016,18 @@
     <col min="5" max="5" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="46" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B1" s="47"/>
       <c r="C1" s="47"/>
       <c r="D1" s="47"/>
       <c r="E1" s="47"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -2193,21 +2036,21 @@
         <v>2</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="35" t="s">
-        <v>232</v>
+      <c r="C3" s="34" t="s">
+        <v>189</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>6</v>
@@ -2216,7 +2059,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>3</v>
       </c>
@@ -2225,13 +2068,13 @@
       </c>
       <c r="C4" s="13"/>
       <c r="D4" s="13" t="s">
-        <v>307</v>
+        <v>263</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -2243,10 +2086,10 @@
         <v>7</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
         <v>3</v>
       </c>
@@ -2257,11 +2100,11 @@
       <c r="D6" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="38">
+      <c r="E6" s="37">
         <v>1893</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>3</v>
       </c>
@@ -2273,10 +2116,10 @@
         <v>9</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" s="45" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
         <v>3</v>
       </c>
@@ -2284,14 +2127,14 @@
         <v>4</v>
       </c>
       <c r="C8" s="13"/>
-      <c r="D8" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="13" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D8" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" s="45" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>3</v>
       </c>
@@ -2300,13 +2143,13 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2" t="s">
-        <v>9</v>
+        <v>422</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.3">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
         <v>3</v>
       </c>
@@ -2314,29 +2157,29 @@
         <v>4</v>
       </c>
       <c r="C10" s="13"/>
-      <c r="D10" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="35" t="s">
+      <c r="D10" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B11" s="35" t="s">
-        <v>4</v>
-      </c>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35" t="s">
-        <v>309</v>
-      </c>
-      <c r="E11" s="35" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
         <v>3</v>
       </c>
@@ -2345,92 +2188,122 @@
       </c>
       <c r="C12" s="13"/>
       <c r="D12" s="13" t="s">
-        <v>385</v>
+        <v>265</v>
       </c>
       <c r="E12" s="13" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="34" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34" t="s">
+        <v>265</v>
+      </c>
+      <c r="E13" s="34" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="34"/>
+      <c r="D15" s="20" t="s">
+        <v>341</v>
+      </c>
+      <c r="E15" s="20" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="C13" s="35"/>
-      <c r="D13" s="20" t="s">
-        <v>385</v>
-      </c>
-      <c r="E13" s="20" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="G15" s="11"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="3"/>
+      <c r="C16" s="3" t="s">
+        <v>66</v>
+      </c>
       <c r="D16" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="G17" s="11"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E18" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B18" s="25"/>
-    </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B19" s="14"/>
-    </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B20" s="9"/>
-    </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B21" s="15"/>
-    </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B20" s="25"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B21" s="14"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B22" s="9"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B23" s="15"/>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B24" s="14"/>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B25" s="15"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B26" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2443,7 +2316,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -2454,7 +2327,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="46" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B1" s="47"/>
       <c r="C1" s="47"/>
@@ -2473,436 +2346,6 @@
       <c r="D2" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>200</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>163</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>202</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>164</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>203</v>
-      </c>
-      <c r="D6" s="17" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>204</v>
-      </c>
-      <c r="D7" s="12"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="30" t="s">
-        <v>57</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>166</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>205</v>
-      </c>
-      <c r="D8" s="17"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>206</v>
-      </c>
-      <c r="D9" s="23"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>399</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>400</v>
-      </c>
-      <c r="D10" s="17"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>401</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>402</v>
-      </c>
-      <c r="D11" s="12"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>403</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>404</v>
-      </c>
-      <c r="D12" s="17"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="D13" s="12"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="B14" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>405</v>
-      </c>
-      <c r="D14" s="17"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="D15" s="12"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="B16" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>209</v>
-      </c>
-      <c r="D16" s="17"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>210</v>
-      </c>
-      <c r="D17" s="12"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="B18" s="17" t="s">
-        <v>168</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>211</v>
-      </c>
-      <c r="D18" s="17"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>212</v>
-      </c>
-      <c r="D19" s="12"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="B20" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20" s="17" t="s">
-        <v>213</v>
-      </c>
-      <c r="D20" s="17"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="D21" s="12"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="B22" s="17" t="s">
-        <v>215</v>
-      </c>
-      <c r="C22" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="D22" s="17"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="D23" s="12"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="B24" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="C24" s="17" t="s">
-        <v>217</v>
-      </c>
-      <c r="D24" s="17"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="D25" s="12"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="B26" s="17" t="s">
-        <v>156</v>
-      </c>
-      <c r="C26" s="17" t="s">
-        <v>219</v>
-      </c>
-      <c r="D26" s="17"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="B27" s="20" t="s">
-        <v>157</v>
-      </c>
-      <c r="C27" s="20" t="s">
-        <v>220</v>
-      </c>
-      <c r="D27" s="20"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="B28" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="C28" s="17" t="s">
-        <v>221</v>
-      </c>
-      <c r="D28" s="17"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="B29" s="20" t="s">
-        <v>159</v>
-      </c>
-      <c r="C29" s="20" t="s">
-        <v>222</v>
-      </c>
-      <c r="D29" s="20"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="B30" s="17" t="s">
-        <v>160</v>
-      </c>
-      <c r="C30" s="17" t="s">
-        <v>170</v>
-      </c>
-      <c r="D30" s="17"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="B31" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="C31" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="D31" s="12"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="30" t="s">
-        <v>57</v>
-      </c>
-      <c r="B32" s="30" t="s">
-        <v>231</v>
-      </c>
-      <c r="C32" s="30" t="s">
-        <v>230</v>
-      </c>
-      <c r="D32" s="17"/>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="B33" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="C33" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="D33" s="12"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="B34" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="C34" s="17" t="s">
-        <v>172</v>
-      </c>
-      <c r="D34" s="17"/>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="B35" s="12" t="s">
-        <v>199</v>
-      </c>
-      <c r="C35" s="12" t="s">
-        <v>224</v>
-      </c>
-      <c r="D35" s="12"/>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="B36" s="17" t="s">
-        <v>229</v>
-      </c>
-      <c r="C36" s="17" t="s">
-        <v>230</v>
-      </c>
-      <c r="D36" s="17" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="B37" s="12" t="s">
-        <v>243</v>
-      </c>
-      <c r="C37" s="12" t="s">
-        <v>244</v>
-      </c>
-      <c r="D37" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2926,7 +2369,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="46" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B1" s="47"/>
       <c r="C1" s="47"/>
@@ -2941,30 +2384,30 @@
         <v>1</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>381</v>
+        <v>337</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>382</v>
+        <v>338</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="C3" s="22" t="s">
-        <v>62</v>
-      </c>
       <c r="D3" s="22" t="s">
-        <v>335</v>
+        <v>291</v>
       </c>
       <c r="E3" s="22" t="s">
-        <v>358</v>
+        <v>314</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2972,10 +2415,10 @@
       <c r="B4" s="20"/>
       <c r="C4" s="20"/>
       <c r="D4" s="20" t="s">
-        <v>336</v>
+        <v>292</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>359</v>
+        <v>315</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2983,10 +2426,10 @@
       <c r="B5" s="22"/>
       <c r="C5" s="22"/>
       <c r="D5" s="22" t="s">
-        <v>337</v>
+        <v>293</v>
       </c>
       <c r="E5" s="22" t="s">
-        <v>360</v>
+        <v>316</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2994,10 +2437,10 @@
       <c r="B6" s="20"/>
       <c r="C6" s="20"/>
       <c r="D6" s="20" t="s">
-        <v>338</v>
+        <v>294</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>361</v>
+        <v>317</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3005,10 +2448,10 @@
       <c r="B7" s="22"/>
       <c r="C7" s="22"/>
       <c r="D7" s="22" t="s">
-        <v>339</v>
+        <v>295</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>362</v>
+        <v>318</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3016,10 +2459,10 @@
       <c r="B8" s="20"/>
       <c r="C8" s="20"/>
       <c r="D8" s="20" t="s">
-        <v>340</v>
+        <v>296</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3027,10 +2470,10 @@
       <c r="B9" s="22"/>
       <c r="C9" s="22"/>
       <c r="D9" s="22" t="s">
-        <v>341</v>
+        <v>297</v>
       </c>
       <c r="E9" s="22" t="s">
-        <v>364</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3038,10 +2481,10 @@
       <c r="B10" s="20"/>
       <c r="C10" s="20"/>
       <c r="D10" s="20" t="s">
-        <v>342</v>
+        <v>298</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>365</v>
+        <v>321</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3049,10 +2492,10 @@
       <c r="B11" s="22"/>
       <c r="C11" s="22"/>
       <c r="D11" s="22" t="s">
-        <v>343</v>
+        <v>299</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>366</v>
+        <v>322</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3060,10 +2503,10 @@
       <c r="B12" s="20"/>
       <c r="C12" s="20"/>
       <c r="D12" s="20" t="s">
-        <v>344</v>
+        <v>300</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>367</v>
+        <v>323</v>
       </c>
     </row>
     <row r="13" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3071,10 +2514,10 @@
       <c r="B13" s="22"/>
       <c r="C13" s="22"/>
       <c r="D13" s="22" t="s">
-        <v>345</v>
+        <v>301</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>368</v>
+        <v>324</v>
       </c>
     </row>
     <row r="14" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3082,10 +2525,10 @@
       <c r="B14" s="20"/>
       <c r="C14" s="20"/>
       <c r="D14" s="20" t="s">
-        <v>346</v>
+        <v>302</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>369</v>
+        <v>325</v>
       </c>
     </row>
     <row r="15" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3093,10 +2536,10 @@
       <c r="B15" s="22"/>
       <c r="C15" s="22"/>
       <c r="D15" s="22" t="s">
-        <v>347</v>
+        <v>303</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>370</v>
+        <v>326</v>
       </c>
     </row>
     <row r="16" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3104,10 +2547,10 @@
       <c r="B16" s="20"/>
       <c r="C16" s="20"/>
       <c r="D16" s="20" t="s">
-        <v>348</v>
+        <v>304</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>371</v>
+        <v>327</v>
       </c>
     </row>
     <row r="17" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3115,10 +2558,10 @@
       <c r="B17" s="22"/>
       <c r="C17" s="22"/>
       <c r="D17" s="22" t="s">
-        <v>349</v>
+        <v>305</v>
       </c>
       <c r="E17" s="22" t="s">
-        <v>372</v>
+        <v>328</v>
       </c>
     </row>
     <row r="18" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3126,10 +2569,10 @@
       <c r="B18" s="20"/>
       <c r="C18" s="20"/>
       <c r="D18" s="20" t="s">
-        <v>350</v>
+        <v>306</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>373</v>
+        <v>329</v>
       </c>
     </row>
     <row r="19" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3137,10 +2580,10 @@
       <c r="B19" s="22"/>
       <c r="C19" s="22"/>
       <c r="D19" s="22" t="s">
-        <v>351</v>
+        <v>307</v>
       </c>
       <c r="E19" s="22" t="s">
-        <v>374</v>
+        <v>330</v>
       </c>
     </row>
     <row r="20" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3148,10 +2591,10 @@
       <c r="B20" s="20"/>
       <c r="C20" s="20"/>
       <c r="D20" s="20" t="s">
-        <v>352</v>
+        <v>308</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>375</v>
+        <v>331</v>
       </c>
     </row>
     <row r="21" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3159,10 +2602,10 @@
       <c r="B21" s="22"/>
       <c r="C21" s="22"/>
       <c r="D21" s="22" t="s">
-        <v>353</v>
+        <v>309</v>
       </c>
       <c r="E21" s="22" t="s">
-        <v>376</v>
+        <v>332</v>
       </c>
     </row>
     <row r="22" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3170,10 +2613,10 @@
       <c r="B22" s="20"/>
       <c r="C22" s="20"/>
       <c r="D22" s="20" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>377</v>
+        <v>333</v>
       </c>
     </row>
     <row r="23" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3181,10 +2624,10 @@
       <c r="B23" s="22"/>
       <c r="C23" s="22"/>
       <c r="D23" s="22" t="s">
-        <v>355</v>
+        <v>311</v>
       </c>
       <c r="E23" s="22" t="s">
-        <v>378</v>
+        <v>334</v>
       </c>
     </row>
     <row r="24" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3192,10 +2635,10 @@
       <c r="B24" s="20"/>
       <c r="C24" s="20"/>
       <c r="D24" s="20" t="s">
-        <v>356</v>
+        <v>312</v>
       </c>
       <c r="E24" s="20" t="s">
-        <v>379</v>
+        <v>335</v>
       </c>
     </row>
     <row r="25" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3203,27 +2646,27 @@
       <c r="B25" s="22"/>
       <c r="C25" s="22"/>
       <c r="D25" s="22" t="s">
-        <v>357</v>
+        <v>313</v>
       </c>
       <c r="E25" s="22" t="s">
-        <v>380</v>
+        <v>336</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="20" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B26" s="20" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D26" s="20" t="s">
-        <v>335</v>
+        <v>291</v>
       </c>
       <c r="E26" s="20" t="s">
-        <v>358</v>
+        <v>314</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
@@ -3231,10 +2674,10 @@
       <c r="B27" s="22"/>
       <c r="C27" s="22"/>
       <c r="D27" s="22" t="s">
-        <v>336</v>
+        <v>292</v>
       </c>
       <c r="E27" s="22" t="s">
-        <v>359</v>
+        <v>315</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
@@ -3242,10 +2685,10 @@
       <c r="B28" s="20"/>
       <c r="C28" s="20"/>
       <c r="D28" s="20" t="s">
-        <v>337</v>
+        <v>293</v>
       </c>
       <c r="E28" s="20" t="s">
-        <v>360</v>
+        <v>316</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
@@ -3253,10 +2696,10 @@
       <c r="B29" s="22"/>
       <c r="C29" s="22"/>
       <c r="D29" s="22" t="s">
-        <v>338</v>
+        <v>294</v>
       </c>
       <c r="E29" s="22" t="s">
-        <v>361</v>
+        <v>317</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
@@ -3264,10 +2707,10 @@
       <c r="B30" s="20"/>
       <c r="C30" s="20"/>
       <c r="D30" s="20" t="s">
-        <v>339</v>
+        <v>295</v>
       </c>
       <c r="E30" s="20" t="s">
-        <v>362</v>
+        <v>318</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
@@ -3275,10 +2718,10 @@
       <c r="B31" s="22"/>
       <c r="C31" s="22"/>
       <c r="D31" s="22" t="s">
-        <v>340</v>
+        <v>296</v>
       </c>
       <c r="E31" s="22" t="s">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
@@ -3286,10 +2729,10 @@
       <c r="B32" s="20"/>
       <c r="C32" s="20"/>
       <c r="D32" s="20" t="s">
-        <v>341</v>
+        <v>297</v>
       </c>
       <c r="E32" s="20" t="s">
-        <v>364</v>
+        <v>320</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
@@ -3297,10 +2740,10 @@
       <c r="B33" s="22"/>
       <c r="C33" s="22"/>
       <c r="D33" s="22" t="s">
-        <v>342</v>
+        <v>298</v>
       </c>
       <c r="E33" s="22" t="s">
-        <v>365</v>
+        <v>321</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
@@ -3308,10 +2751,10 @@
       <c r="B34" s="20"/>
       <c r="C34" s="20"/>
       <c r="D34" s="20" t="s">
-        <v>343</v>
+        <v>299</v>
       </c>
       <c r="E34" s="20" t="s">
-        <v>366</v>
+        <v>322</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
@@ -3319,10 +2762,10 @@
       <c r="B35" s="22"/>
       <c r="C35" s="22"/>
       <c r="D35" s="22" t="s">
-        <v>344</v>
+        <v>300</v>
       </c>
       <c r="E35" s="22" t="s">
-        <v>367</v>
+        <v>323</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
@@ -3330,10 +2773,10 @@
       <c r="B36" s="20"/>
       <c r="C36" s="20"/>
       <c r="D36" s="20" t="s">
-        <v>345</v>
+        <v>301</v>
       </c>
       <c r="E36" s="20" t="s">
-        <v>368</v>
+        <v>324</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
@@ -3341,10 +2784,10 @@
       <c r="B37" s="22"/>
       <c r="C37" s="22"/>
       <c r="D37" s="22" t="s">
-        <v>346</v>
+        <v>302</v>
       </c>
       <c r="E37" s="22" t="s">
-        <v>369</v>
+        <v>325</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
@@ -3352,10 +2795,10 @@
       <c r="B38" s="20"/>
       <c r="C38" s="20"/>
       <c r="D38" s="20" t="s">
-        <v>347</v>
+        <v>303</v>
       </c>
       <c r="E38" s="20" t="s">
-        <v>370</v>
+        <v>326</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
@@ -3363,10 +2806,10 @@
       <c r="B39" s="22"/>
       <c r="C39" s="22"/>
       <c r="D39" s="22" t="s">
-        <v>348</v>
+        <v>304</v>
       </c>
       <c r="E39" s="22" t="s">
-        <v>371</v>
+        <v>327</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
@@ -3374,10 +2817,10 @@
       <c r="B40" s="20"/>
       <c r="C40" s="20"/>
       <c r="D40" s="20" t="s">
-        <v>349</v>
+        <v>305</v>
       </c>
       <c r="E40" s="20" t="s">
-        <v>372</v>
+        <v>328</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
@@ -3385,10 +2828,10 @@
       <c r="B41" s="22"/>
       <c r="C41" s="22"/>
       <c r="D41" s="22" t="s">
-        <v>350</v>
+        <v>306</v>
       </c>
       <c r="E41" s="22" t="s">
-        <v>373</v>
+        <v>329</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
@@ -3396,10 +2839,10 @@
       <c r="B42" s="20"/>
       <c r="C42" s="20"/>
       <c r="D42" s="20" t="s">
-        <v>351</v>
+        <v>307</v>
       </c>
       <c r="E42" s="20" t="s">
-        <v>374</v>
+        <v>330</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
@@ -3407,10 +2850,10 @@
       <c r="B43" s="22"/>
       <c r="C43" s="22"/>
       <c r="D43" s="22" t="s">
-        <v>352</v>
+        <v>308</v>
       </c>
       <c r="E43" s="22" t="s">
-        <v>375</v>
+        <v>331</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
@@ -3418,10 +2861,10 @@
       <c r="B44" s="20"/>
       <c r="C44" s="20"/>
       <c r="D44" s="20" t="s">
-        <v>353</v>
+        <v>309</v>
       </c>
       <c r="E44" s="20" t="s">
-        <v>376</v>
+        <v>332</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
@@ -3429,10 +2872,10 @@
       <c r="B45" s="22"/>
       <c r="C45" s="22"/>
       <c r="D45" s="22" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="E45" s="22" t="s">
-        <v>377</v>
+        <v>333</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
@@ -3440,10 +2883,10 @@
       <c r="B46" s="20"/>
       <c r="C46" s="20"/>
       <c r="D46" s="20" t="s">
-        <v>355</v>
+        <v>311</v>
       </c>
       <c r="E46" s="20" t="s">
-        <v>378</v>
+        <v>334</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
@@ -3451,10 +2894,10 @@
       <c r="B47" s="22"/>
       <c r="C47" s="22"/>
       <c r="D47" s="22" t="s">
-        <v>356</v>
+        <v>312</v>
       </c>
       <c r="E47" s="22" t="s">
-        <v>379</v>
+        <v>335</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
@@ -3462,10 +2905,10 @@
       <c r="B48" s="20"/>
       <c r="C48" s="20"/>
       <c r="D48" s="20" t="s">
-        <v>357</v>
+        <v>313</v>
       </c>
       <c r="E48" s="20" t="s">
-        <v>380</v>
+        <v>336</v>
       </c>
     </row>
   </sheetData>
@@ -3496,7 +2939,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="46" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B1" s="47"/>
       <c r="C1" s="47"/>
@@ -3509,7 +2952,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -3518,48 +2961,48 @@
         <v>2</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>225</v>
+        <v>184</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>310</v>
+        <v>266</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>386</v>
+        <v>342</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>387</v>
+        <v>343</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>326</v>
+        <v>282</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>311</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="35" t="s">
+      <c r="B3" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="35" t="s">
+      <c r="C3" s="34" t="s">
         <v>17</v>
       </c>
       <c r="D3" s="20" t="s">
         <v>4</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>391</v>
+        <v>347</v>
       </c>
       <c r="G3" s="20" t="s">
-        <v>389</v>
+        <v>345</v>
       </c>
       <c r="H3" s="20" t="s">
-        <v>327</v>
+        <v>283</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>33</v>
@@ -3576,10 +3019,10 @@
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="17" t="s">
-        <v>394</v>
+        <v>350</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>390</v>
+        <v>346</v>
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
@@ -3595,10 +3038,10 @@
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="12" t="s">
-        <v>392</v>
+        <v>348</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>388</v>
+        <v>344</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
@@ -3614,34 +3057,34 @@
       <c r="D6" s="17"/>
       <c r="E6" s="17"/>
       <c r="F6" s="17" t="s">
-        <v>393</v>
+        <v>349</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>389</v>
+        <v>345</v>
       </c>
       <c r="H6" s="17"/>
       <c r="I6" s="17"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="35" t="s">
+      <c r="A7" s="34" t="s">
         <v>15</v>
       </c>
       <c r="B7" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34"/>
       <c r="F7" s="20" t="s">
-        <v>395</v>
+        <v>351</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>388</v>
-      </c>
-      <c r="H7" s="35"/>
-      <c r="I7" s="35"/>
-    </row>
-    <row r="8" spans="1:10" s="43" customFormat="1" x14ac:dyDescent="0.3">
+        <v>344</v>
+      </c>
+      <c r="H7" s="34"/>
+      <c r="I7" s="34"/>
+    </row>
+    <row r="8" spans="1:10" s="42" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>15</v>
       </c>
@@ -3652,10 +3095,10 @@
       <c r="D8" s="17"/>
       <c r="E8" s="17"/>
       <c r="F8" s="17" t="s">
-        <v>471</v>
+        <v>420</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>389</v>
+        <v>345</v>
       </c>
       <c r="H8" s="17"/>
       <c r="I8" s="17"/>
@@ -3665,23 +3108,23 @@
         <v>15</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>233</v>
+        <v>190</v>
       </c>
       <c r="D9" s="20" t="s">
         <v>4</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>471</v>
+        <v>420</v>
       </c>
       <c r="G9" s="20"/>
       <c r="H9" s="20" t="s">
-        <v>328</v>
+        <v>284</v>
       </c>
       <c r="I9" s="20"/>
     </row>
@@ -3690,25 +3133,25 @@
         <v>15</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>234</v>
+        <v>191</v>
       </c>
       <c r="D10" s="17" t="s">
         <v>4</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>396</v>
+        <v>352</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>390</v>
+        <v>346</v>
       </c>
       <c r="H10" s="17" t="s">
-        <v>329</v>
+        <v>285</v>
       </c>
       <c r="I10" s="17"/>
     </row>
@@ -3717,33 +3160,33 @@
         <v>15</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C11" s="20"/>
       <c r="D11" s="20"/>
       <c r="E11" s="20"/>
       <c r="F11" s="20" t="s">
-        <v>397</v>
+        <v>353</v>
       </c>
       <c r="G11" s="20" t="s">
-        <v>388</v>
+        <v>344</v>
       </c>
       <c r="H11" s="20"/>
       <c r="I11" s="20"/>
       <c r="J11" s="21"/>
     </row>
-    <row r="12" spans="1:10" s="43" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" s="42" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C12" s="17"/>
       <c r="D12" s="17"/>
       <c r="E12" s="17"/>
       <c r="F12" s="17" t="s">
-        <v>472</v>
+        <v>421</v>
       </c>
       <c r="G12" s="17"/>
       <c r="H12" s="17"/>
@@ -3754,19 +3197,19 @@
         <v>15</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>235</v>
+        <v>192</v>
       </c>
       <c r="D13" s="20" t="s">
         <v>4</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>471</v>
+        <v>420</v>
       </c>
       <c r="G13" s="20"/>
       <c r="H13" s="20"/>
@@ -3777,40 +3220,40 @@
         <v>15</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>236</v>
+        <v>193</v>
       </c>
       <c r="D14" s="17" t="s">
         <v>4</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>398</v>
+        <v>354</v>
       </c>
       <c r="G14" s="17" t="s">
-        <v>388</v>
+        <v>344</v>
       </c>
       <c r="H14" s="17"/>
       <c r="I14" s="17" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="21" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="35" t="s">
+      <c r="A15" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="35" t="s">
-        <v>77</v>
+      <c r="B15" s="34" t="s">
+        <v>74</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="20"/>
       <c r="E15" s="20"/>
       <c r="F15" s="20" t="s">
-        <v>471</v>
+        <v>420</v>
       </c>
       <c r="G15" s="20"/>
       <c r="H15" s="20"/>
@@ -3821,24 +3264,24 @@
         <v>15</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>237</v>
+        <v>194</v>
       </c>
       <c r="D16" s="17" t="s">
         <v>4</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>471</v>
+        <v>420</v>
       </c>
       <c r="G16" s="17"/>
       <c r="H16" s="17"/>
       <c r="I16" s="17" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3846,45 +3289,45 @@
         <v>18</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>238</v>
+        <v>195</v>
       </c>
       <c r="D17" s="20" t="s">
         <v>4</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>246</v>
+        <v>202</v>
       </c>
       <c r="G17" s="20" t="s">
-        <v>390</v>
+        <v>346</v>
       </c>
       <c r="H17" s="20"/>
       <c r="I17" s="20"/>
     </row>
-    <row r="18" spans="1:9" s="43" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" s="42" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>18</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C18" s="17"/>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
       <c r="F18" s="17" t="s">
-        <v>471</v>
+        <v>420</v>
       </c>
       <c r="G18" s="17"/>
       <c r="H18" s="17"/>
       <c r="I18" s="17"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="G26" s="42"/>
+      <c r="G26" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3909,7 +3352,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="46" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B1" s="47"/>
       <c r="C1" s="47"/>
@@ -3919,7 +3362,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -3928,13 +3371,13 @@
         <v>2</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>226</v>
+        <v>185</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>310</v>
+        <v>266</v>
       </c>
       <c r="G2" s="21"/>
     </row>
@@ -3946,31 +3389,31 @@
         <v>33</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>247</v>
+        <v>203</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E3" s="20" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>86</v>
-      </c>
-      <c r="G3" s="40"/>
+        <v>83</v>
+      </c>
+      <c r="G3" s="39"/>
     </row>
     <row r="4" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>249</v>
+        <v>205</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>250</v>
+        <v>206</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>4</v>
@@ -3979,16 +3422,16 @@
     </row>
     <row r="5" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="20" t="s">
-        <v>266</v>
+        <v>222</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>248</v>
-      </c>
-      <c r="C5" s="35" t="s">
-        <v>251</v>
+        <v>204</v>
+      </c>
+      <c r="C5" s="34" t="s">
+        <v>207</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E5" s="20" t="s">
         <v>4</v>
@@ -4000,13 +3443,13 @@
         <v>20</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>252</v>
+        <v>208</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>239</v>
+        <v>196</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E6" s="18" t="s">
         <v>4</v>
@@ -4018,13 +3461,13 @@
         <v>20</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>240</v>
+        <v>197</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E7" s="12" t="s">
         <v>4</v>
@@ -4036,13 +3479,13 @@
         <v>20</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>241</v>
+        <v>198</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E8" s="18" t="s">
         <v>4</v>
@@ -4051,16 +3494,16 @@
     </row>
     <row r="9" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="20" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>242</v>
+        <v>199</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>243</v>
+        <v>200</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>4</v>
@@ -4072,13 +3515,13 @@
         <v>20</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>245</v>
+        <v>201</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E10" s="18" t="s">
         <v>4</v>
@@ -4109,7 +3552,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="46" t="s">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="B1" s="47"/>
       <c r="C1" s="47"/>
@@ -4120,7 +3563,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -4129,33 +3572,33 @@
         <v>2</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>195</v>
-      </c>
-      <c r="G2" s="33" t="s">
-        <v>384</v>
+        <v>178</v>
+      </c>
+      <c r="G2" s="32" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>257</v>
+        <v>213</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>26</v>
@@ -4165,39 +3608,39 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="31" t="s">
-        <v>185</v>
-      </c>
-      <c r="B4" s="31" t="s">
-        <v>189</v>
-      </c>
-      <c r="C4" s="31" t="s">
-        <v>258</v>
-      </c>
-      <c r="D4" s="31" t="s">
-        <v>188</v>
-      </c>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="31" t="s">
+      <c r="A4" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="B4" s="30" t="s">
+        <v>172</v>
+      </c>
+      <c r="C4" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="D4" s="30" t="s">
+        <v>171</v>
+      </c>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="30" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>259</v>
+        <v>215</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="12" t="s">
@@ -4205,75 +3648,75 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="31" t="s">
-        <v>190</v>
-      </c>
-      <c r="B6" s="31" t="s">
-        <v>248</v>
-      </c>
-      <c r="C6" s="31" t="s">
-        <v>260</v>
-      </c>
-      <c r="D6" s="31" t="s">
-        <v>255</v>
-      </c>
-      <c r="E6" s="31" t="s">
-        <v>436</v>
-      </c>
-      <c r="F6" s="32"/>
-      <c r="G6" s="31" t="s">
+      <c r="A6" s="30" t="s">
+        <v>173</v>
+      </c>
+      <c r="B6" s="30" t="s">
+        <v>204</v>
+      </c>
+      <c r="C6" s="30" t="s">
+        <v>216</v>
+      </c>
+      <c r="D6" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="E6" s="30" t="s">
+        <v>385</v>
+      </c>
+      <c r="F6" s="31"/>
+      <c r="G6" s="30" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="35" t="s">
-        <v>253</v>
+      <c r="A7" s="34" t="s">
+        <v>209</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="C7" s="35" t="s">
-        <v>261</v>
+        <v>73</v>
+      </c>
+      <c r="C7" s="34" t="s">
+        <v>217</v>
       </c>
       <c r="D7" s="20"/>
       <c r="E7" s="20"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="35" t="s">
-        <v>4</v>
-      </c>
-      <c r="H7" s="35"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="H7" s="34"/>
     </row>
     <row r="8" spans="1:8" s="21" customFormat="1" ht="66" x14ac:dyDescent="0.3">
-      <c r="A8" s="31" t="s">
-        <v>190</v>
-      </c>
-      <c r="B8" s="31" t="s">
-        <v>263</v>
-      </c>
-      <c r="C8" s="31" t="s">
-        <v>262</v>
-      </c>
-      <c r="D8" s="31" t="s">
-        <v>256</v>
-      </c>
-      <c r="E8" s="31" t="s">
-        <v>254</v>
-      </c>
-      <c r="F8" s="31"/>
-      <c r="G8" s="31" t="s">
-        <v>4</v>
-      </c>
-      <c r="H8" s="35"/>
+      <c r="A8" s="30" t="s">
+        <v>173</v>
+      </c>
+      <c r="B8" s="30" t="s">
+        <v>219</v>
+      </c>
+      <c r="C8" s="30" t="s">
+        <v>218</v>
+      </c>
+      <c r="D8" s="30" t="s">
+        <v>212</v>
+      </c>
+      <c r="E8" s="30" t="s">
+        <v>210</v>
+      </c>
+      <c r="F8" s="30"/>
+      <c r="G8" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8" s="34"/>
     </row>
     <row r="9" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="20" t="s">
-        <v>253</v>
+        <v>209</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>264</v>
+        <v>220</v>
       </c>
       <c r="D9" s="20"/>
       <c r="E9" s="20"/>
@@ -4284,19 +3727,19 @@
       <c r="H9" s="20"/>
     </row>
     <row r="10" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="31" t="s">
-        <v>253</v>
-      </c>
-      <c r="B10" s="31" t="s">
-        <v>179</v>
-      </c>
-      <c r="C10" s="31" t="s">
-        <v>265</v>
-      </c>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31" t="s">
+      <c r="A10" s="30" t="s">
+        <v>209</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>162</v>
+      </c>
+      <c r="C10" s="30" t="s">
+        <v>221</v>
+      </c>
+      <c r="D10" s="30"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="30" t="s">
         <v>4</v>
       </c>
       <c r="H10" s="20"/>
@@ -4325,7 +3768,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="46" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B1" s="47"/>
       <c r="C1" s="47"/>
@@ -4336,7 +3779,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -4345,13 +3788,13 @@
         <v>2</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>316</v>
+        <v>272</v>
       </c>
       <c r="G2" s="16"/>
     </row>
@@ -4360,13 +3803,13 @@
         <v>21</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>267</v>
+        <v>223</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
@@ -4377,13 +3820,13 @@
         <v>21</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>268</v>
+        <v>224</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
@@ -4397,13 +3840,13 @@
         <v>23</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>269</v>
+        <v>225</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F5" s="12"/>
       <c r="G5" s="21"/>
@@ -4413,13 +3856,13 @@
         <v>22</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>270</v>
+        <v>226</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
@@ -4430,13 +3873,13 @@
         <v>22</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>271</v>
+        <v>227</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>215</v>
+        <v>183</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
@@ -4447,13 +3890,13 @@
         <v>22</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>272</v>
+        <v>228</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>215</v>
+        <v>183</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
@@ -4464,13 +3907,13 @@
         <v>22</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>273</v>
+        <v>229</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
@@ -4481,13 +3924,13 @@
         <v>22</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>274</v>
+        <v>230</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
@@ -4504,10 +3947,10 @@
         <v>27</v>
       </c>
       <c r="D11" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="E11" s="12" t="s">
         <v>96</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>99</v>
       </c>
       <c r="F11" s="12"/>
       <c r="G11" s="21"/>
@@ -4526,7 +3969,7 @@
         <v>24</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F12" s="19"/>
       <c r="G12" s="21"/>
@@ -4536,16 +3979,16 @@
         <v>22</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>318</v>
+        <v>274</v>
       </c>
       <c r="D13" s="20" t="s">
         <v>24</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>178</v>
+        <v>161</v>
       </c>
       <c r="F13" s="20" t="s">
         <v>23</v>
@@ -4556,10 +3999,10 @@
         <v>25</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>178</v>
+        <v>161</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>317</v>
+        <v>273</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>24</v>
@@ -4572,10 +4015,10 @@
         <v>25</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>275</v>
+        <v>231</v>
       </c>
       <c r="D15" s="20" t="s">
         <v>24</v>
@@ -4588,10 +4031,10 @@
         <v>25</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>276</v>
+        <v>232</v>
       </c>
       <c r="D16" s="19" t="s">
         <v>24</v>
@@ -4605,29 +4048,29 @@
         <v>25</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>277</v>
+        <v>233</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="19" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>278</v>
+        <v>234</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="E18" s="19" t="s">
         <v>16</v>
@@ -4636,16 +4079,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>279</v>
+        <v>235</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>16</v>
@@ -4680,7 +4123,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="46" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B1" s="48"/>
       <c r="C1" s="47"/>
@@ -4693,7 +4136,7 @@
     </row>
     <row r="2" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -4702,33 +4145,33 @@
         <v>2</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>330</v>
+        <v>286</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>313</v>
+        <v>269</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>315</v>
+        <v>271</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>312</v>
+        <v>268</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>314</v>
+        <v>270</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>333</v>
+        <v>289</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>280</v>
+        <v>236</v>
       </c>
       <c r="D3" s="12"/>
       <c r="E3" s="2" t="s">
@@ -4740,102 +4183,102 @@
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="12" t="s">
-        <v>334</v>
+        <v>290</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A4" s="22" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>281</v>
+        <v>237</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="F4" s="22" t="s">
-        <v>252</v>
+        <v>208</v>
       </c>
       <c r="G4" s="22" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H4" s="22" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="I4" s="22" t="s">
-        <v>334</v>
+        <v>290</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>282</v>
+        <v>238</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>252</v>
+        <v>208</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H5" s="12"/>
       <c r="I5" s="12" t="s">
-        <v>334</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A6" s="22" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>283</v>
+        <v>239</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="F6" s="7"/>
       <c r="G6" s="22" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="H6" s="22"/>
       <c r="I6" s="22" t="s">
-        <v>334</v>
+        <v>290</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>331</v>
+        <v>287</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>284</v>
+        <v>240</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>16</v>
@@ -4843,180 +4286,180 @@
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="12" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>334</v>
+        <v>290</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A8" s="22" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>285</v>
+        <v>241</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>331</v>
+        <v>287</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>252</v>
+        <v>208</v>
       </c>
       <c r="G8" s="22" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="H8" s="22"/>
       <c r="I8" s="22" t="s">
-        <v>334</v>
+        <v>290</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>286</v>
+        <v>242</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F9" s="12"/>
       <c r="G9" s="12" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H9" s="12"/>
       <c r="I9" s="12" t="s">
-        <v>334</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A10" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>243</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="E10" s="22" t="s">
         <v>133</v>
       </c>
-      <c r="B10" s="22" t="s">
-        <v>287</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>288</v>
-      </c>
-      <c r="D10" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="E10" s="22" t="s">
-        <v>137</v>
-      </c>
       <c r="F10" s="7" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="G10" s="22" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H10" s="22"/>
       <c r="I10" s="22" t="s">
-        <v>334</v>
+        <v>290</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A11" s="12" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>289</v>
+        <v>245</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>287</v>
+        <v>243</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H11" s="12"/>
       <c r="I11" s="12" t="s">
-        <v>334</v>
+        <v>290</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A12" s="22" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>290</v>
+        <v>246</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E12" s="22" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="F12" s="22"/>
       <c r="G12" s="22" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H12" s="22"/>
       <c r="I12" s="22" t="s">
-        <v>334</v>
+        <v>290</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A13" s="12" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>291</v>
+        <v>247</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="F13" s="12"/>
       <c r="G13" s="12" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H13" s="12"/>
       <c r="I13" s="12" t="s">
-        <v>334</v>
+        <v>290</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A14" s="22" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>292</v>
+        <v>248</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>16</v>
@@ -5025,44 +4468,44 @@
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
       <c r="I14" s="22" t="s">
-        <v>334</v>
+        <v>290</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="9" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>298</v>
+        <v>254</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="F15" s="12"/>
       <c r="G15" s="12"/>
       <c r="H15" s="12"/>
       <c r="I15" s="12" t="s">
-        <v>334</v>
+        <v>290</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>299</v>
+        <v>255</v>
       </c>
       <c r="D16" s="22" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>16</v>
@@ -5071,124 +4514,124 @@
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
       <c r="I16" s="22" t="s">
-        <v>334</v>
+        <v>290</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A17" s="12" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>293</v>
+        <v>249</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E17" s="12" t="s">
         <v>16</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="G17" s="12"/>
       <c r="H17" s="12"/>
       <c r="I17" s="12" t="s">
-        <v>334</v>
+        <v>290</v>
       </c>
     </row>
     <row r="18" spans="1:9" s="9" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>332</v>
+        <v>288</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>294</v>
+        <v>250</v>
       </c>
       <c r="D18" s="22" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
       <c r="H18" s="7"/>
       <c r="I18" s="22" t="s">
-        <v>334</v>
+        <v>290</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>295</v>
+        <v>251</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>332</v>
+        <v>288</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="12" t="s">
-        <v>334</v>
+        <v>290</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>296</v>
+        <v>252</v>
       </c>
       <c r="D20" s="22" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E20" s="22" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F20" s="22"/>
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
       <c r="I20" s="22" t="s">
-        <v>334</v>
+        <v>290</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>297</v>
+        <v>253</v>
       </c>
       <c r="D21" s="20" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>248</v>
+        <v>204</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="12" t="s">
-        <v>334</v>
+        <v>290</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
@@ -5219,7 +4662,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="46" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
@@ -5229,7 +4672,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -5238,28 +4681,28 @@
         <v>2</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>322</v>
+        <v>278</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>383</v>
+        <v>339</v>
       </c>
       <c r="H2" s="9"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>30</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>414</v>
+        <v>363</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E3" s="23"/>
       <c r="F3" s="12" t="s">
@@ -5270,18 +4713,18 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="24" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B4" s="24" t="s">
         <v>31</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>415</v>
+        <v>364</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="E4" s="36"/>
+        <v>100</v>
+      </c>
+      <c r="E4" s="35"/>
       <c r="F4" s="24" t="s">
         <v>4</v>
       </c>
@@ -5290,13 +4733,13 @@
     </row>
     <row r="5" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>32</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>416</v>
+        <v>365</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="23"/>
@@ -5308,16 +4751,16 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="24" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B6" s="24" t="s">
         <v>34</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>417</v>
+        <v>366</v>
       </c>
       <c r="D6" s="8"/>
-      <c r="E6" s="36"/>
+      <c r="E6" s="35"/>
       <c r="F6" s="24" t="s">
         <v>4</v>
       </c>
@@ -5325,19 +4768,19 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>35</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>418</v>
+        <v>367</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>324</v>
+        <v>280</v>
       </c>
       <c r="F7" s="12" t="s">
         <v>4</v>
@@ -5346,19 +4789,19 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="24" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B8" s="24" t="s">
         <v>36</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>419</v>
+        <v>368</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>324</v>
+        <v>280</v>
       </c>
       <c r="F8" s="24" t="s">
         <v>4</v>
@@ -5367,16 +4810,16 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>37</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>420</v>
+        <v>369</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E9" s="23"/>
       <c r="F9" s="12" t="s">
@@ -5386,19 +4829,19 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="24" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B10" s="24" t="s">
         <v>38</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>421</v>
+        <v>370</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>331</v>
+        <v>287</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>320</v>
+        <v>276</v>
       </c>
       <c r="F10" s="24" t="s">
         <v>4</v>
@@ -5407,19 +4850,19 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="12" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>39</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>422</v>
+        <v>371</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>321</v>
+        <v>277</v>
       </c>
       <c r="F11" s="12" t="s">
         <v>4</v>
@@ -5428,19 +4871,19 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="24" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B12" s="24" t="s">
         <v>40</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>423</v>
+        <v>372</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>321</v>
+        <v>277</v>
       </c>
       <c r="F12" s="24" t="s">
         <v>4</v>
@@ -5449,16 +4892,16 @@
     </row>
     <row r="13" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A13" s="12" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>41</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E13" s="23"/>
       <c r="F13" s="12" t="s">
@@ -5468,18 +4911,18 @@
     </row>
     <row r="14" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="24" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B14" s="24" t="s">
         <v>42</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>288</v>
+        <v>244</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>287</v>
-      </c>
-      <c r="E14" s="36"/>
+        <v>243</v>
+      </c>
+      <c r="E14" s="35"/>
       <c r="F14" s="24" t="s">
         <v>4</v>
       </c>
@@ -5487,16 +4930,16 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B15" s="12" t="s">
         <v>43</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>427</v>
+        <v>376</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E15" s="23"/>
       <c r="F15" s="12" t="s">
@@ -5506,18 +4949,18 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="24" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B16" s="24" t="s">
         <v>44</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>425</v>
+        <v>374</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="E16" s="36"/>
+        <v>107</v>
+      </c>
+      <c r="E16" s="35"/>
       <c r="F16" s="24" t="s">
         <v>4</v>
       </c>
@@ -5525,16 +4968,16 @@
     </row>
     <row r="17" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A17" s="12" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>45</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>426</v>
+        <v>375</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E17" s="23"/>
       <c r="F17" s="12" t="s">
@@ -5544,18 +4987,18 @@
     </row>
     <row r="18" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="24" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B18" s="24" t="s">
         <v>46</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>428</v>
+        <v>377</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="E18" s="36"/>
+        <v>109</v>
+      </c>
+      <c r="E18" s="35"/>
       <c r="F18" s="24" t="s">
         <v>4</v>
       </c>
@@ -5563,16 +5006,16 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="12" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B19" s="12" t="s">
         <v>47</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>429</v>
+        <v>378</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E19" s="23"/>
       <c r="F19" s="12" t="s">
@@ -5582,18 +5025,18 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="24" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B20" s="24" t="s">
         <v>48</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>430</v>
+        <v>379</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="E20" s="36"/>
+        <v>111</v>
+      </c>
+      <c r="E20" s="35"/>
       <c r="F20" s="24" t="s">
         <v>4</v>
       </c>
@@ -5601,36 +5044,36 @@
     </row>
     <row r="21" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="12" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B21" s="12" t="s">
         <v>49</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>431</v>
+        <v>380</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="E21" s="37"/>
-      <c r="F21" s="41" t="s">
+        <v>112</v>
+      </c>
+      <c r="E21" s="36"/>
+      <c r="F21" s="40" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="24" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B22" s="24" t="s">
         <v>50</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>432</v>
+        <v>381</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>332</v>
-      </c>
-      <c r="E22" s="36"/>
+        <v>288</v>
+      </c>
+      <c r="E22" s="35"/>
       <c r="F22" s="24" t="s">
         <v>4</v>
       </c>
@@ -5638,19 +5081,19 @@
     </row>
     <row r="23" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="12" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B23" s="12" t="s">
         <v>51</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>433</v>
+        <v>382</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>323</v>
+        <v>279</v>
       </c>
       <c r="F23" s="12" t="s">
         <v>4</v>
@@ -5659,18 +5102,18 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="24" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B24" s="24" t="s">
         <v>52</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>434</v>
+        <v>383</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>117</v>
-      </c>
-      <c r="E24" s="36"/>
+        <v>114</v>
+      </c>
+      <c r="E24" s="35"/>
       <c r="F24" s="24" t="s">
         <v>4</v>
       </c>
@@ -5678,16 +5121,16 @@
     </row>
     <row r="25" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A25" s="12" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>435</v>
+        <v>384</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E25" s="12"/>
       <c r="F25" s="12" t="s">
@@ -5764,7 +5207,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="46" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B1" s="47"/>
       <c r="C1" s="47"/>
@@ -5774,7 +5217,7 @@
     </row>
     <row r="2" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -5783,13 +5226,13 @@
         <v>2</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>410</v>
+        <v>359</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>411</v>
+        <v>360</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
@@ -5797,34 +5240,34 @@
         <v>53</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="C3" s="39" t="s">
+        <v>145</v>
+      </c>
+      <c r="C3" s="38" t="s">
+        <v>148</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="E3" s="38" t="s">
         <v>152</v>
       </c>
-      <c r="D3" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="E3" s="39" t="s">
-        <v>156</v>
-      </c>
-      <c r="F3" s="39"/>
+      <c r="F3" s="38"/>
     </row>
     <row r="4" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A4" s="12" t="s">
         <v>53</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C4" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="E4" s="23" t="s">
         <v>153</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="E4" s="23" t="s">
-        <v>157</v>
       </c>
       <c r="F4" s="23"/>
     </row>
@@ -5833,18 +5276,18 @@
         <v>53</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="C5" s="39" t="s">
+        <v>147</v>
+      </c>
+      <c r="C5" s="38" t="s">
+        <v>150</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="E5" s="38" t="s">
         <v>154</v>
       </c>
-      <c r="D5" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="E5" s="39" t="s">
-        <v>158</v>
-      </c>
-      <c r="F5" s="39"/>
+      <c r="F5" s="38"/>
     </row>
     <row r="6" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
@@ -5854,13 +5297,13 @@
         <v>54</v>
       </c>
       <c r="C6" s="23" t="s">
+        <v>151</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="E6" s="23" t="s">
         <v>155</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>319</v>
-      </c>
-      <c r="E6" s="23" t="s">
-        <v>159</v>
       </c>
       <c r="F6" s="23"/>
     </row>
@@ -5869,17 +5312,17 @@
         <v>55</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>408</v>
+        <v>357</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>406</v>
+        <v>355</v>
       </c>
       <c r="D7" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="39"/>
+      <c r="E7" s="38"/>
       <c r="F7" s="13" t="s">
-        <v>412</v>
+        <v>361</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
@@ -5887,236 +5330,236 @@
         <v>55</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>409</v>
+        <v>358</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>407</v>
+        <v>356</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E8" s="23"/>
       <c r="F8" s="12" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" s="34" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="E9" s="34" t="s">
-        <v>325</v>
+        <v>362</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="33" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="E9" s="33" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E10" s="16" t="s">
-        <v>451</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="42" t="s">
-        <v>437</v>
+      <c r="A11" s="41" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>438</v>
+        <v>387</v>
       </c>
       <c r="B14" t="s">
-        <v>443</v>
+        <v>392</v>
       </c>
       <c r="C14" t="s">
-        <v>444</v>
+        <v>393</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>439</v>
+        <v>388</v>
       </c>
       <c r="B15" t="s">
-        <v>440</v>
+        <v>389</v>
       </c>
       <c r="C15" t="s">
-        <v>444</v>
+        <v>393</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>438</v>
+        <v>387</v>
       </c>
       <c r="B16" t="s">
-        <v>441</v>
+        <v>390</v>
       </c>
       <c r="C16" t="s">
-        <v>439</v>
+        <v>388</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>442</v>
+        <v>391</v>
       </c>
       <c r="B17" t="s">
-        <v>443</v>
+        <v>392</v>
       </c>
       <c r="C17" t="s">
-        <v>445</v>
+        <v>394</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>442</v>
+        <v>391</v>
       </c>
       <c r="B18" t="s">
-        <v>443</v>
+        <v>392</v>
       </c>
       <c r="C18" t="s">
-        <v>446</v>
+        <v>395</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>439</v>
+        <v>388</v>
       </c>
       <c r="B19" t="s">
-        <v>440</v>
+        <v>389</v>
       </c>
       <c r="C19" t="s">
-        <v>446</v>
+        <v>395</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>439</v>
+        <v>388</v>
       </c>
       <c r="B20" t="s">
-        <v>440</v>
+        <v>389</v>
       </c>
       <c r="C20" t="s">
-        <v>445</v>
+        <v>394</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="29" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B23" s="29" t="s">
         <v>1</v>
       </c>
       <c r="C23" s="29" t="s">
-        <v>465</v>
+        <v>414</v>
       </c>
       <c r="D23" s="29" t="s">
-        <v>450</v>
-      </c>
-      <c r="E23" s="45" t="s">
-        <v>455</v>
+        <v>399</v>
+      </c>
+      <c r="E23" s="44" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>447</v>
+        <v>396</v>
       </c>
       <c r="B24" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C24" t="s">
-        <v>448</v>
-      </c>
-      <c r="D24" s="44" t="s">
-        <v>136</v>
-      </c>
-      <c r="E24" s="44" t="s">
-        <v>454</v>
+        <v>397</v>
+      </c>
+      <c r="D24" s="43" t="s">
+        <v>132</v>
+      </c>
+      <c r="E24" s="43" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>449</v>
+        <v>398</v>
       </c>
       <c r="B25" t="s">
-        <v>452</v>
+        <v>401</v>
       </c>
       <c r="C25" t="s">
-        <v>468</v>
-      </c>
-      <c r="E25" s="44" t="s">
-        <v>467</v>
+        <v>417</v>
+      </c>
+      <c r="E25" s="43" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>449</v>
+        <v>398</v>
       </c>
       <c r="B26" t="s">
-        <v>453</v>
+        <v>402</v>
       </c>
       <c r="C26" t="s">
-        <v>469</v>
-      </c>
-      <c r="E26" s="44" t="s">
-        <v>466</v>
+        <v>418</v>
+      </c>
+      <c r="E26" s="43" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>447</v>
+        <v>396</v>
       </c>
       <c r="B27" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C27" t="s">
-        <v>456</v>
-      </c>
-      <c r="D27" s="44" t="s">
-        <v>140</v>
+        <v>405</v>
+      </c>
+      <c r="D27" s="43" t="s">
+        <v>136</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>457</v>
+        <v>406</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>449</v>
+        <v>398</v>
       </c>
       <c r="B28" t="s">
-        <v>458</v>
+        <v>407</v>
       </c>
       <c r="C28" t="s">
-        <v>470</v>
-      </c>
-      <c r="E28" s="44" t="s">
-        <v>140</v>
+        <v>419</v>
+      </c>
+      <c r="E28" s="43" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>447</v>
+        <v>396</v>
       </c>
       <c r="B29" t="s">
-        <v>459</v>
+        <v>408</v>
       </c>
       <c r="C29" t="s">
-        <v>461</v>
-      </c>
-      <c r="D29" s="44" t="s">
-        <v>464</v>
-      </c>
-      <c r="E29" s="44" t="s">
-        <v>454</v>
+        <v>410</v>
+      </c>
+      <c r="D29" s="43" t="s">
+        <v>413</v>
+      </c>
+      <c r="E29" s="43" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>447</v>
+        <v>396</v>
       </c>
       <c r="B30" t="s">
-        <v>460</v>
+        <v>409</v>
       </c>
       <c r="C30" t="s">
-        <v>462</v>
-      </c>
-      <c r="D30" s="44" t="s">
-        <v>463</v>
-      </c>
-      <c r="E30" s="44" t="s">
-        <v>454</v>
+        <v>411</v>
+      </c>
+      <c r="D30" s="43" t="s">
+        <v>412</v>
+      </c>
+      <c r="E30" s="43" t="s">
+        <v>403</v>
       </c>
     </row>
   </sheetData>
@@ -6140,7 +5583,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="46" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B1" s="47"/>
       <c r="C1" s="47"/>
@@ -6148,7 +5591,7 @@
     </row>
     <row r="2" spans="1:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -6157,18 +5600,18 @@
         <v>2</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>227</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>300</v>
+        <v>256</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>16</v>
@@ -6176,13 +5619,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>301</v>
+        <v>257</v>
       </c>
       <c r="D4" s="19" t="s">
         <v>16</v>
@@ -6190,13 +5633,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>302</v>
+        <v>258</v>
       </c>
       <c r="D5" s="12" t="s">
         <v>16</v>
@@ -6204,13 +5647,13 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>303</v>
+        <v>259</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>4</v>
@@ -6218,13 +5661,13 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>304</v>
+        <v>260</v>
       </c>
       <c r="D7" s="12" t="s">
         <v>4</v>
@@ -6232,13 +5675,13 @@
     </row>
     <row r="8" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A8" s="19" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>305</v>
+        <v>261</v>
       </c>
       <c r="D8" s="19" t="s">
         <v>4</v>
@@ -6246,13 +5689,13 @@
     </row>
     <row r="9" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>306</v>
+        <v>262</v>
       </c>
       <c r="D9" s="12" t="s">
         <v>4</v>

--- a/data/Capus_LHommeBicycle_1893/Capus_LHommeBicycle_1893.xlsx
+++ b/data/Capus_LHommeBicycle_1893/Capus_LHommeBicycle_1893.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mathilde\Desktop\Doctorat - 2025-2028\Pipeline\SFonto\data\Capus_LHommeBicycle_1893\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4094CCE4-3340-4B3F-9D6C-01C86BE5529E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A9F08DD-6267-4FF4-9FCE-A7C770104465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Work" sheetId="1" r:id="rId1"/>

--- a/data/Capus_LHommeBicycle_1893/Capus_LHommeBicycle_1893.xlsx
+++ b/data/Capus_LHommeBicycle_1893/Capus_LHommeBicycle_1893.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mathilde\Desktop\Doctorat - 2025-2028\Pipeline\SFonto\data\Capus_LHommeBicycle_1893\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A9F08DD-6267-4FF4-9FCE-A7C770104465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66BFB3D0-F81C-4259-B724-3652B224675A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Work" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="425">
   <si>
     <t>Classe</t>
   </si>
@@ -49,9 +49,6 @@
     <t>F1_Work</t>
   </si>
   <si>
-    <t>:LHomme_Bicycle_Work</t>
-  </si>
-  <si>
     <t>L'Homme-Bicycle</t>
   </si>
   <si>
@@ -70,9 +67,6 @@
     <t>F2_Expression</t>
   </si>
   <si>
-    <t>:LHomme_Bicycle_Expr_FR</t>
-  </si>
-  <si>
     <t>R3i_realises</t>
   </si>
   <si>
@@ -407,18 +401,6 @@
   </si>
   <si>
     <t>:Archetype_Melancholic_Hero</t>
-  </si>
-  <si>
-    <t>:Motif_Man-Machine_Hybridization</t>
-  </si>
-  <si>
-    <t>:Motif_Birth_of_a_New_Race</t>
-  </si>
-  <si>
-    <t>:Motif_Hero_Surpassing_Humanity</t>
-  </si>
-  <si>
-    <t>:Motif_Science_Powerless_Against_the_Fantastic</t>
   </si>
   <si>
     <t>Narrative Sequence</t>
@@ -1338,6 +1320,24 @@
   </si>
   <si>
     <t>:Feature_humorous_register</t>
+  </si>
+  <si>
+    <t>:Pattern_Man-Machine_Hybridization</t>
+  </si>
+  <si>
+    <t>:Pattern_Birth_of_a_New_Race</t>
+  </si>
+  <si>
+    <t>:Pattern_Hero_Surpassing_Humanity</t>
+  </si>
+  <si>
+    <t>:Pattern_Science_Powerless_Against_the_Fantastic</t>
+  </si>
+  <si>
+    <t>:Work_LHomme_Bicycle</t>
+  </si>
+  <si>
+    <t>:Expr_FR_LHomme_Bicycle</t>
   </si>
 </sst>
 </file>
@@ -1530,7 +1530,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1633,9 +1633,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1645,12 +1642,16 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2018,7 +2019,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="46" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B1" s="47"/>
       <c r="C1" s="47"/>
@@ -2027,7 +2028,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -2036,10 +2037,10 @@
         <v>2</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -2047,244 +2048,188 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="C3" s="34" t="s">
+        <v>183</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="34" t="s">
-        <v>189</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>5</v>
-      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>4</v>
-      </c>
+      <c r="A4" s="13"/>
+      <c r="B4" s="3"/>
       <c r="C4" s="13"/>
       <c r="D4" s="13" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>4</v>
-      </c>
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>4</v>
-      </c>
+      <c r="A6" s="13"/>
+      <c r="B6" s="3"/>
       <c r="C6" s="13"/>
       <c r="D6" s="13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E6" s="37">
         <v>1893</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>4</v>
-      </c>
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" s="45" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>4</v>
-      </c>
+        <v>151</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" s="44" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="13"/>
+      <c r="B8" s="3"/>
       <c r="C8" s="13"/>
       <c r="D8" s="3" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" s="45" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>4</v>
-      </c>
+        <v>417</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" s="44" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>4</v>
-      </c>
+      <c r="A10" s="13"/>
+      <c r="B10" s="3"/>
       <c r="C10" s="13"/>
       <c r="D10" s="3" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>4</v>
-      </c>
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="21" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>4</v>
-      </c>
+      <c r="A12" s="13"/>
+      <c r="B12" s="3"/>
       <c r="C12" s="13"/>
       <c r="D12" s="13" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:5" s="21" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="34" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" s="34" t="s">
-        <v>4</v>
-      </c>
+      <c r="A13" s="34"/>
+      <c r="B13" s="34"/>
       <c r="C13" s="34"/>
       <c r="D13" s="34" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="E13" s="34" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:5" s="21" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>4</v>
-      </c>
+      <c r="A14" s="13"/>
+      <c r="B14" s="3"/>
       <c r="C14" s="13"/>
       <c r="D14" s="13" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15" spans="1:5" s="21" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="B15" s="20" t="s">
-        <v>4</v>
-      </c>
+      <c r="A15" s="20"/>
+      <c r="B15" s="34"/>
       <c r="C15" s="34"/>
       <c r="D15" s="20" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="E16" s="3" t="s">
-        <v>4</v>
+        <v>423</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G17" s="11"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>11</v>
-      </c>
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
       <c r="C18" s="3"/>
       <c r="D18" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
@@ -2294,7 +2239,7 @@
       <c r="B21" s="14"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B22" s="9"/>
+      <c r="B22" s="45"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B23" s="15"/>
@@ -2327,7 +2272,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="46" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B1" s="47"/>
       <c r="C1" s="47"/>
@@ -2344,7 +2289,7 @@
         <v>2</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -2369,7 +2314,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="46" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="B1" s="47"/>
       <c r="C1" s="47"/>
@@ -2384,30 +2329,30 @@
         <v>1</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="B3" s="22" t="s">
-        <v>59</v>
-      </c>
-      <c r="C3" s="22" t="s">
-        <v>60</v>
-      </c>
       <c r="D3" s="22" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="E3" s="22" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2415,10 +2360,10 @@
       <c r="B4" s="20"/>
       <c r="C4" s="20"/>
       <c r="D4" s="20" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2426,10 +2371,10 @@
       <c r="B5" s="22"/>
       <c r="C5" s="22"/>
       <c r="D5" s="22" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="E5" s="22" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2437,10 +2382,10 @@
       <c r="B6" s="20"/>
       <c r="C6" s="20"/>
       <c r="D6" s="20" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2448,10 +2393,10 @@
       <c r="B7" s="22"/>
       <c r="C7" s="22"/>
       <c r="D7" s="22" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2459,10 +2404,10 @@
       <c r="B8" s="20"/>
       <c r="C8" s="20"/>
       <c r="D8" s="20" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2470,10 +2415,10 @@
       <c r="B9" s="22"/>
       <c r="C9" s="22"/>
       <c r="D9" s="22" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="E9" s="22" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2481,10 +2426,10 @@
       <c r="B10" s="20"/>
       <c r="C10" s="20"/>
       <c r="D10" s="20" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2492,10 +2437,10 @@
       <c r="B11" s="22"/>
       <c r="C11" s="22"/>
       <c r="D11" s="22" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2503,10 +2448,10 @@
       <c r="B12" s="20"/>
       <c r="C12" s="20"/>
       <c r="D12" s="20" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
     </row>
     <row r="13" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2514,10 +2459,10 @@
       <c r="B13" s="22"/>
       <c r="C13" s="22"/>
       <c r="D13" s="22" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
     </row>
     <row r="14" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2525,10 +2470,10 @@
       <c r="B14" s="20"/>
       <c r="C14" s="20"/>
       <c r="D14" s="20" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="15" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2536,10 +2481,10 @@
       <c r="B15" s="22"/>
       <c r="C15" s="22"/>
       <c r="D15" s="22" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
     <row r="16" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2547,10 +2492,10 @@
       <c r="B16" s="20"/>
       <c r="C16" s="20"/>
       <c r="D16" s="20" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
     </row>
     <row r="17" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2558,10 +2503,10 @@
       <c r="B17" s="22"/>
       <c r="C17" s="22"/>
       <c r="D17" s="22" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="E17" s="22" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
     </row>
     <row r="18" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2569,10 +2514,10 @@
       <c r="B18" s="20"/>
       <c r="C18" s="20"/>
       <c r="D18" s="20" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
     </row>
     <row r="19" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2580,10 +2525,10 @@
       <c r="B19" s="22"/>
       <c r="C19" s="22"/>
       <c r="D19" s="22" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="E19" s="22" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
     </row>
     <row r="20" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2591,10 +2536,10 @@
       <c r="B20" s="20"/>
       <c r="C20" s="20"/>
       <c r="D20" s="20" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
     </row>
     <row r="21" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2602,10 +2547,10 @@
       <c r="B21" s="22"/>
       <c r="C21" s="22"/>
       <c r="D21" s="22" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="E21" s="22" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
     </row>
     <row r="22" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2613,10 +2558,10 @@
       <c r="B22" s="20"/>
       <c r="C22" s="20"/>
       <c r="D22" s="20" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
     </row>
     <row r="23" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2624,10 +2569,10 @@
       <c r="B23" s="22"/>
       <c r="C23" s="22"/>
       <c r="D23" s="22" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="E23" s="22" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="24" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2635,10 +2580,10 @@
       <c r="B24" s="20"/>
       <c r="C24" s="20"/>
       <c r="D24" s="20" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E24" s="20" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
     </row>
     <row r="25" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2646,27 +2591,27 @@
       <c r="B25" s="22"/>
       <c r="C25" s="22"/>
       <c r="D25" s="22" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="E25" s="22" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="20" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B26" s="20" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D26" s="20" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="E26" s="20" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
@@ -2674,10 +2619,10 @@
       <c r="B27" s="22"/>
       <c r="C27" s="22"/>
       <c r="D27" s="22" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="E27" s="22" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
@@ -2685,10 +2630,10 @@
       <c r="B28" s="20"/>
       <c r="C28" s="20"/>
       <c r="D28" s="20" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="E28" s="20" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
@@ -2696,10 +2641,10 @@
       <c r="B29" s="22"/>
       <c r="C29" s="22"/>
       <c r="D29" s="22" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="E29" s="22" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
@@ -2707,10 +2652,10 @@
       <c r="B30" s="20"/>
       <c r="C30" s="20"/>
       <c r="D30" s="20" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="E30" s="20" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
@@ -2718,10 +2663,10 @@
       <c r="B31" s="22"/>
       <c r="C31" s="22"/>
       <c r="D31" s="22" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="E31" s="22" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
@@ -2729,10 +2674,10 @@
       <c r="B32" s="20"/>
       <c r="C32" s="20"/>
       <c r="D32" s="20" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="E32" s="20" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
@@ -2740,10 +2685,10 @@
       <c r="B33" s="22"/>
       <c r="C33" s="22"/>
       <c r="D33" s="22" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="E33" s="22" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
@@ -2751,10 +2696,10 @@
       <c r="B34" s="20"/>
       <c r="C34" s="20"/>
       <c r="D34" s="20" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="E34" s="20" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
@@ -2762,10 +2707,10 @@
       <c r="B35" s="22"/>
       <c r="C35" s="22"/>
       <c r="D35" s="22" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E35" s="22" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
@@ -2773,10 +2718,10 @@
       <c r="B36" s="20"/>
       <c r="C36" s="20"/>
       <c r="D36" s="20" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="E36" s="20" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
@@ -2784,10 +2729,10 @@
       <c r="B37" s="22"/>
       <c r="C37" s="22"/>
       <c r="D37" s="22" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="E37" s="22" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
@@ -2795,10 +2740,10 @@
       <c r="B38" s="20"/>
       <c r="C38" s="20"/>
       <c r="D38" s="20" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="E38" s="20" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
@@ -2806,10 +2751,10 @@
       <c r="B39" s="22"/>
       <c r="C39" s="22"/>
       <c r="D39" s="22" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="E39" s="22" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
@@ -2817,10 +2762,10 @@
       <c r="B40" s="20"/>
       <c r="C40" s="20"/>
       <c r="D40" s="20" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="E40" s="20" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
@@ -2828,10 +2773,10 @@
       <c r="B41" s="22"/>
       <c r="C41" s="22"/>
       <c r="D41" s="22" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="E41" s="22" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
@@ -2839,10 +2784,10 @@
       <c r="B42" s="20"/>
       <c r="C42" s="20"/>
       <c r="D42" s="20" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="E42" s="20" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
@@ -2850,10 +2795,10 @@
       <c r="B43" s="22"/>
       <c r="C43" s="22"/>
       <c r="D43" s="22" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="E43" s="22" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
@@ -2861,10 +2806,10 @@
       <c r="B44" s="20"/>
       <c r="C44" s="20"/>
       <c r="D44" s="20" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="E44" s="20" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
@@ -2872,10 +2817,10 @@
       <c r="B45" s="22"/>
       <c r="C45" s="22"/>
       <c r="D45" s="22" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="E45" s="22" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
@@ -2883,10 +2828,10 @@
       <c r="B46" s="20"/>
       <c r="C46" s="20"/>
       <c r="D46" s="20" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="E46" s="20" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
@@ -2894,10 +2839,10 @@
       <c r="B47" s="22"/>
       <c r="C47" s="22"/>
       <c r="D47" s="22" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E47" s="22" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
@@ -2905,10 +2850,10 @@
       <c r="B48" s="20"/>
       <c r="C48" s="20"/>
       <c r="D48" s="20" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="E48" s="20" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
     </row>
   </sheetData>
@@ -2939,7 +2884,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="46" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B1" s="47"/>
       <c r="C1" s="47"/>
@@ -2952,7 +2897,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -2961,232 +2906,232 @@
         <v>2</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>4</v>
+      <c r="D3" s="34" t="s">
+        <v>423</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="G3" s="20" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="H3" s="20" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="17" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="12" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C6" s="17"/>
       <c r="D6" s="17"/>
       <c r="E6" s="17"/>
       <c r="F6" s="17" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="H6" s="17"/>
       <c r="I6" s="17"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="34" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C7" s="34"/>
       <c r="D7" s="34"/>
       <c r="E7" s="34"/>
       <c r="F7" s="20" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="H7" s="34"/>
       <c r="I7" s="34"/>
     </row>
-    <row r="8" spans="1:10" s="42" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C8" s="17"/>
       <c r="D8" s="17"/>
       <c r="E8" s="17"/>
       <c r="F8" s="17" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="H8" s="17"/>
       <c r="I8" s="17"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="20" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="D9" s="20" t="s">
-        <v>4</v>
+        <v>184</v>
+      </c>
+      <c r="D9" s="34" t="s">
+        <v>423</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="G9" s="20"/>
       <c r="H9" s="20" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="I9" s="20"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>191</v>
-      </c>
-      <c r="D10" s="17" t="s">
-        <v>4</v>
+        <v>185</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>423</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="H10" s="17" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="I10" s="17"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="20" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C11" s="20"/>
       <c r="D11" s="20"/>
       <c r="E11" s="20"/>
       <c r="F11" s="20" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="G11" s="20" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="H11" s="20"/>
       <c r="I11" s="20"/>
       <c r="J11" s="21"/>
     </row>
-    <row r="12" spans="1:10" s="42" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C12" s="17"/>
       <c r="D12" s="17"/>
       <c r="E12" s="17"/>
       <c r="F12" s="17" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="G12" s="17"/>
       <c r="H12" s="17"/>
@@ -3194,22 +3139,22 @@
     </row>
     <row r="13" spans="1:10" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="20" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>192</v>
-      </c>
-      <c r="D13" s="20" t="s">
-        <v>4</v>
+        <v>186</v>
+      </c>
+      <c r="D13" s="34" t="s">
+        <v>423</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="G13" s="20"/>
       <c r="H13" s="20"/>
@@ -3217,43 +3162,43 @@
     </row>
     <row r="14" spans="1:10" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>193</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>4</v>
+        <v>187</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>423</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="G14" s="17" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="H14" s="17"/>
       <c r="I14" s="17" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="34" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B15" s="34" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="20"/>
       <c r="E15" s="20"/>
       <c r="F15" s="20" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="G15" s="20"/>
       <c r="H15" s="20"/>
@@ -3261,73 +3206,73 @@
     </row>
     <row r="16" spans="1:10" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>194</v>
-      </c>
-      <c r="D16" s="17" t="s">
-        <v>4</v>
+        <v>188</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>423</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="G16" s="17"/>
       <c r="H16" s="17"/>
       <c r="I16" s="17" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="20" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>195</v>
-      </c>
-      <c r="D17" s="20" t="s">
-        <v>4</v>
+        <v>189</v>
+      </c>
+      <c r="D17" s="34" t="s">
+        <v>423</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G17" s="20" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="H17" s="20"/>
       <c r="I17" s="20"/>
     </row>
-    <row r="18" spans="1:9" s="42" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" s="41" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C18" s="17"/>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
       <c r="F18" s="17" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="G18" s="17"/>
       <c r="H18" s="17"/>
       <c r="I18" s="17"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="G26" s="41"/>
+      <c r="G26" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3352,7 +3297,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="46" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B1" s="47"/>
       <c r="C1" s="47"/>
@@ -3362,7 +3307,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -3371,160 +3316,160 @@
         <v>2</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="G2" s="21"/>
     </row>
     <row r="3" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="E3" s="20" t="s">
-        <v>4</v>
+        <v>76</v>
+      </c>
+      <c r="E3" s="34" t="s">
+        <v>423</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G3" s="39"/>
     </row>
     <row r="4" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>4</v>
+        <v>423</v>
       </c>
       <c r="F4" s="5"/>
     </row>
     <row r="5" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="20" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="C5" s="34" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>79</v>
-      </c>
-      <c r="E5" s="20" t="s">
-        <v>4</v>
+        <v>77</v>
+      </c>
+      <c r="E5" s="34" t="s">
+        <v>423</v>
       </c>
       <c r="F5" s="20"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="18" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>4</v>
+        <v>76</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>423</v>
       </c>
       <c r="F6" s="18"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>4</v>
+        <v>78</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>423</v>
       </c>
       <c r="F7" s="12"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="E8" s="18" t="s">
-        <v>4</v>
+        <v>79</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>423</v>
       </c>
       <c r="F8" s="18"/>
     </row>
     <row r="9" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="20" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>200</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>4</v>
+        <v>194</v>
+      </c>
+      <c r="E9" s="34" t="s">
+        <v>423</v>
       </c>
       <c r="F9" s="20"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="18" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="E10" s="18" t="s">
-        <v>4</v>
+        <v>76</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>423</v>
       </c>
       <c r="F10" s="18"/>
     </row>
@@ -3552,7 +3497,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="46" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="B1" s="47"/>
       <c r="C1" s="47"/>
@@ -3563,7 +3508,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -3571,176 +3516,176 @@
       <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="10" t="s">
-        <v>68</v>
+      <c r="D2" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="G2" s="32" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>213</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>169</v>
+        <v>207</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>163</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>4</v>
+        <v>24</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="30" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="B4" s="30" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C4" s="30" t="s">
-        <v>214</v>
-      </c>
-      <c r="D4" s="30" t="s">
-        <v>171</v>
+        <v>208</v>
+      </c>
+      <c r="D4" s="31" t="s">
+        <v>165</v>
       </c>
       <c r="E4" s="31"/>
       <c r="F4" s="31"/>
-      <c r="G4" s="30" t="s">
-        <v>4</v>
+      <c r="G4" s="31" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>175</v>
+        <v>209</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>169</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="F5" s="2"/>
-      <c r="G5" s="12" t="s">
-        <v>4</v>
+      <c r="G5" s="2" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A6" s="30" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="C6" s="30" t="s">
-        <v>216</v>
-      </c>
-      <c r="D6" s="30" t="s">
-        <v>211</v>
+        <v>210</v>
+      </c>
+      <c r="D6" s="31" t="s">
+        <v>205</v>
       </c>
       <c r="E6" s="30" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="F6" s="31"/>
-      <c r="G6" s="30" t="s">
-        <v>4</v>
+      <c r="G6" s="31" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="34" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C7" s="34" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="D7" s="20"/>
       <c r="E7" s="20"/>
       <c r="F7" s="34"/>
       <c r="G7" s="34" t="s">
-        <v>4</v>
+        <v>423</v>
       </c>
       <c r="H7" s="34"/>
     </row>
     <row r="8" spans="1:8" s="21" customFormat="1" ht="66" x14ac:dyDescent="0.3">
       <c r="A8" s="30" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="B8" s="30" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="C8" s="30" t="s">
-        <v>218</v>
-      </c>
-      <c r="D8" s="30" t="s">
         <v>212</v>
       </c>
+      <c r="D8" s="31" t="s">
+        <v>206</v>
+      </c>
       <c r="E8" s="30" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="F8" s="30"/>
-      <c r="G8" s="30" t="s">
-        <v>4</v>
+      <c r="G8" s="31" t="s">
+        <v>423</v>
       </c>
       <c r="H8" s="34"/>
     </row>
     <row r="9" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="20" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="D9" s="20"/>
       <c r="E9" s="20"/>
       <c r="F9" s="20"/>
-      <c r="G9" s="20" t="s">
-        <v>4</v>
+      <c r="G9" s="34" t="s">
+        <v>423</v>
       </c>
       <c r="H9" s="20"/>
     </row>
     <row r="10" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="30" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="B10" s="30" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="C10" s="30" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="D10" s="30"/>
       <c r="E10" s="30"/>
       <c r="F10" s="30"/>
-      <c r="G10" s="30" t="s">
-        <v>4</v>
+      <c r="G10" s="31" t="s">
+        <v>423</v>
       </c>
       <c r="H10" s="20"/>
     </row>
@@ -3768,7 +3713,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="46" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B1" s="47"/>
       <c r="C1" s="47"/>
@@ -3779,7 +3724,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -3788,28 +3733,28 @@
         <v>2</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="G2" s="16"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
@@ -3817,16 +3762,16 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
@@ -3834,35 +3779,35 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="E5" s="12" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F5" s="12"/>
       <c r="G5" s="21"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
@@ -3870,16 +3815,16 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
@@ -3887,16 +3832,16 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="19" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
@@ -3904,16 +3849,16 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
@@ -3921,16 +3866,16 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="19" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
@@ -3938,106 +3883,106 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F11" s="12"/>
       <c r="G11" s="21"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>24</v>
-      </c>
       <c r="E12" s="19" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F12" s="19"/>
       <c r="G12" s="21"/>
     </row>
     <row r="13" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>268</v>
+      </c>
+      <c r="D13" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="20" t="s">
-        <v>160</v>
-      </c>
-      <c r="C13" s="20" t="s">
-        <v>274</v>
-      </c>
-      <c r="D13" s="20" t="s">
-        <v>24</v>
-      </c>
       <c r="E13" s="20" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
     </row>
     <row r="15" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="20" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E15" s="20"/>
       <c r="F15" s="20"/>
     </row>
     <row r="16" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
@@ -4045,53 +3990,53 @@
     </row>
     <row r="17" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="19" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F18" s="19"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F19" s="2"/>
     </row>
@@ -4123,7 +4068,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="46" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B1" s="48"/>
       <c r="C1" s="47"/>
@@ -4136,7 +4081,7 @@
     </row>
     <row r="2" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -4145,493 +4090,493 @@
         <v>2</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="D3" s="12"/>
       <c r="E3" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="12" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A4" s="22" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="F4" s="22" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="G4" s="22" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H4" s="22" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="I4" s="22" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H5" s="12"/>
       <c r="I5" s="12" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A6" s="22" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="F6" s="7"/>
       <c r="G6" s="22" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H6" s="22"/>
       <c r="I6" s="22" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="12" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A8" s="22" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="G8" s="22" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H8" s="22"/>
       <c r="I8" s="22" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="D9" s="20" t="s">
-        <v>105</v>
+        <v>236</v>
+      </c>
+      <c r="D9" s="34" t="s">
+        <v>103</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="F9" s="12"/>
       <c r="G9" s="12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H9" s="12"/>
       <c r="I9" s="12" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A10" s="22" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="G10" s="22" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H10" s="22"/>
       <c r="I10" s="22" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A11" s="12" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H11" s="12"/>
       <c r="I11" s="12" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A12" s="22" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E12" s="22" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="F12" s="22"/>
       <c r="G12" s="22" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H12" s="22"/>
       <c r="I12" s="22" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A13" s="12" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="F13" s="12"/>
       <c r="G13" s="12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H13" s="12"/>
       <c r="I13" s="12" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A14" s="22" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
       <c r="I14" s="22" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="9" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F15" s="12"/>
       <c r="G15" s="12"/>
       <c r="H15" s="12"/>
       <c r="I15" s="12" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="D16" s="22" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
       <c r="I16" s="22" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A17" s="12" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="G17" s="12"/>
       <c r="H17" s="12"/>
       <c r="I17" s="12" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
     </row>
     <row r="18" spans="1:9" s="9" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="B18" s="22" t="s">
+        <v>282</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="D18" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="E18" s="7" t="s">
         <v>130</v>
-      </c>
-      <c r="B18" s="22" t="s">
-        <v>288</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="D18" s="22" t="s">
-        <v>112</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>136</v>
       </c>
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
       <c r="H18" s="7"/>
       <c r="I18" s="22" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>282</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="D19" s="20" t="s">
-        <v>288</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>136</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="12" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="D20" s="22" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E20" s="22" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F20" s="22"/>
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
       <c r="I20" s="22" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="D21" s="20" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="12" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
@@ -4662,7 +4607,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="46" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
@@ -4672,7 +4617,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -4681,460 +4626,460 @@
         <v>2</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="H2" s="9"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E3" s="23"/>
-      <c r="F3" s="12" t="s">
-        <v>4</v>
+      <c r="F3" s="2" t="s">
+        <v>423</v>
       </c>
       <c r="G3" s="9"/>
       <c r="H3" s="9"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="24" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E4" s="35"/>
-      <c r="F4" s="24" t="s">
-        <v>4</v>
+      <c r="F4" s="8" t="s">
+        <v>423</v>
       </c>
       <c r="G4" s="9"/>
       <c r="H4" s="9"/>
     </row>
     <row r="5" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="23"/>
-      <c r="F5" s="12" t="s">
-        <v>4</v>
+      <c r="F5" s="2" t="s">
+        <v>423</v>
       </c>
       <c r="G5" s="9"/>
       <c r="H5" s="9"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="24" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="35"/>
-      <c r="F6" s="24" t="s">
-        <v>4</v>
+      <c r="F6" s="8" t="s">
+        <v>423</v>
       </c>
       <c r="G6" s="9"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>367</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>101</v>
+        <v>361</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>99</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>280</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>4</v>
+        <v>274</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>423</v>
       </c>
       <c r="G7" s="9"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="24" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>280</v>
-      </c>
-      <c r="F8" s="24" t="s">
-        <v>4</v>
+        <v>274</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>423</v>
       </c>
       <c r="G8" s="9"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E9" s="23"/>
-      <c r="F9" s="12" t="s">
-        <v>4</v>
+      <c r="F9" s="2" t="s">
+        <v>423</v>
       </c>
       <c r="G9" s="9"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="24" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>276</v>
-      </c>
-      <c r="F10" s="24" t="s">
-        <v>4</v>
+        <v>270</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>423</v>
       </c>
       <c r="G10" s="9"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="12" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>277</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>4</v>
+        <v>271</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>423</v>
       </c>
       <c r="G11" s="9"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="24" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>277</v>
-      </c>
-      <c r="F12" s="24" t="s">
-        <v>4</v>
+        <v>271</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>423</v>
       </c>
       <c r="G12" s="9"/>
     </row>
     <row r="13" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A13" s="12" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E13" s="23"/>
-      <c r="F13" s="12" t="s">
-        <v>4</v>
+      <c r="F13" s="2" t="s">
+        <v>423</v>
       </c>
       <c r="G13" s="9"/>
     </row>
     <row r="14" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="24" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="E14" s="35"/>
-      <c r="F14" s="24" t="s">
-        <v>4</v>
+      <c r="F14" s="8" t="s">
+        <v>423</v>
       </c>
       <c r="G14" s="9"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E15" s="23"/>
-      <c r="F15" s="12" t="s">
-        <v>4</v>
+      <c r="F15" s="2" t="s">
+        <v>423</v>
       </c>
       <c r="G15" s="9"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="24" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E16" s="35"/>
-      <c r="F16" s="24" t="s">
-        <v>4</v>
+      <c r="F16" s="8" t="s">
+        <v>423</v>
       </c>
       <c r="G16" s="9"/>
     </row>
     <row r="17" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A17" s="12" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E17" s="23"/>
-      <c r="F17" s="12" t="s">
-        <v>4</v>
+      <c r="F17" s="2" t="s">
+        <v>423</v>
       </c>
       <c r="G17" s="9"/>
     </row>
     <row r="18" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="24" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E18" s="35"/>
-      <c r="F18" s="24" t="s">
-        <v>4</v>
+      <c r="F18" s="8" t="s">
+        <v>423</v>
       </c>
       <c r="G18" s="9"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="12" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E19" s="23"/>
-      <c r="F19" s="12" t="s">
-        <v>4</v>
+      <c r="F19" s="2" t="s">
+        <v>423</v>
       </c>
       <c r="G19" s="9"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="24" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E20" s="35"/>
-      <c r="F20" s="24" t="s">
-        <v>4</v>
+      <c r="F20" s="8" t="s">
+        <v>423</v>
       </c>
       <c r="G20" s="9"/>
     </row>
     <row r="21" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="12" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E21" s="36"/>
-      <c r="F21" s="40" t="s">
-        <v>4</v>
+      <c r="F21" s="49" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="24" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B22" s="24" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="E22" s="35"/>
-      <c r="F22" s="24" t="s">
-        <v>4</v>
+      <c r="F22" s="8" t="s">
+        <v>423</v>
       </c>
       <c r="G22" s="9"/>
     </row>
     <row r="23" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="12" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>279</v>
-      </c>
-      <c r="F23" s="12" t="s">
-        <v>4</v>
+        <v>273</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>423</v>
       </c>
       <c r="G23" s="9"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="24" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E24" s="35"/>
-      <c r="F24" s="24" t="s">
-        <v>4</v>
+      <c r="F24" s="8" t="s">
+        <v>423</v>
       </c>
       <c r="G24" s="9"/>
     </row>
     <row r="25" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A25" s="12" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E25" s="12"/>
-      <c r="F25" s="12" t="s">
-        <v>4</v>
+      <c r="F25" s="2" t="s">
+        <v>423</v>
       </c>
       <c r="G25" s="9"/>
     </row>
@@ -5207,7 +5152,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="46" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B1" s="47"/>
       <c r="C1" s="47"/>
@@ -5217,7 +5162,7 @@
     </row>
     <row r="2" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -5226,340 +5171,340 @@
         <v>2</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="C3" s="38" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="E3" s="38" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="F3" s="38"/>
     </row>
     <row r="4" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A4" s="12" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="E4" s="23" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="F4" s="23"/>
     </row>
     <row r="5" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="C5" s="38" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="E5" s="38" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="F5" s="38"/>
     </row>
     <row r="6" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="F6" s="23"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E7" s="38"/>
       <c r="F7" s="13" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E8" s="23"/>
       <c r="F8" s="12" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
     </row>
     <row r="9" spans="1:6" s="33" customFormat="1" x14ac:dyDescent="0.3">
       <c r="E9" s="33" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E10" s="16" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="41" t="s">
-        <v>386</v>
+      <c r="A11" s="40" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>381</v>
+      </c>
+      <c r="B14" t="s">
+        <v>386</v>
+      </c>
+      <c r="C14" t="s">
         <v>387</v>
-      </c>
-      <c r="B14" t="s">
-        <v>392</v>
-      </c>
-      <c r="C14" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="B15" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="C15" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="B16" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="C16" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="B17" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="C17" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="B18" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="C18" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="B19" t="s">
+        <v>383</v>
+      </c>
+      <c r="C19" t="s">
         <v>389</v>
-      </c>
-      <c r="C19" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>382</v>
+      </c>
+      <c r="B20" t="s">
+        <v>383</v>
+      </c>
+      <c r="C20" t="s">
         <v>388</v>
-      </c>
-      <c r="B20" t="s">
-        <v>389</v>
-      </c>
-      <c r="C20" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="29" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B23" s="29" t="s">
         <v>1</v>
       </c>
       <c r="C23" s="29" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="D23" s="29" t="s">
-        <v>399</v>
-      </c>
-      <c r="E23" s="44" t="s">
-        <v>404</v>
+        <v>393</v>
+      </c>
+      <c r="E23" s="43" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B24" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="C24" t="s">
+        <v>391</v>
+      </c>
+      <c r="D24" s="42" t="s">
+        <v>126</v>
+      </c>
+      <c r="E24" s="42" t="s">
         <v>397</v>
-      </c>
-      <c r="D24" s="43" t="s">
-        <v>132</v>
-      </c>
-      <c r="E24" s="43" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="B25" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="C25" t="s">
-        <v>417</v>
-      </c>
-      <c r="E25" s="43" t="s">
-        <v>416</v>
+        <v>411</v>
+      </c>
+      <c r="E25" s="42" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="B26" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="C26" t="s">
-        <v>418</v>
-      </c>
-      <c r="E26" s="43" t="s">
-        <v>415</v>
+        <v>412</v>
+      </c>
+      <c r="E26" s="42" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B27" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C27" t="s">
-        <v>405</v>
-      </c>
-      <c r="D27" s="43" t="s">
-        <v>136</v>
+        <v>399</v>
+      </c>
+      <c r="D27" s="42" t="s">
+        <v>130</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="B28" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="C28" t="s">
-        <v>419</v>
-      </c>
-      <c r="E28" s="43" t="s">
-        <v>136</v>
+        <v>413</v>
+      </c>
+      <c r="E28" s="42" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B29" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="C29" t="s">
-        <v>410</v>
-      </c>
-      <c r="D29" s="43" t="s">
-        <v>413</v>
-      </c>
-      <c r="E29" s="43" t="s">
-        <v>403</v>
+        <v>404</v>
+      </c>
+      <c r="D29" s="42" t="s">
+        <v>407</v>
+      </c>
+      <c r="E29" s="42" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B30" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="C30" t="s">
-        <v>411</v>
-      </c>
-      <c r="D30" s="43" t="s">
-        <v>412</v>
-      </c>
-      <c r="E30" s="43" t="s">
-        <v>403</v>
+        <v>405</v>
+      </c>
+      <c r="D30" s="42" t="s">
+        <v>406</v>
+      </c>
+      <c r="E30" s="42" t="s">
+        <v>397</v>
       </c>
     </row>
   </sheetData>
@@ -5583,7 +5528,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="46" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B1" s="47"/>
       <c r="C1" s="47"/>
@@ -5591,7 +5536,7 @@
     </row>
     <row r="2" spans="1:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -5600,105 +5545,105 @@
         <v>2</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>124</v>
+        <v>55</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>419</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>259</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>4</v>
+        <v>253</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>125</v>
+        <v>55</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>420</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>260</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>4</v>
+        <v>254</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A8" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>126</v>
+        <v>55</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>421</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>261</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>4</v>
+        <v>255</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>127</v>
+        <v>55</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>422</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>262</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>4</v>
+        <v>256</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">

--- a/data/Capus_LHommeBicycle_1893/Capus_LHommeBicycle_1893.xlsx
+++ b/data/Capus_LHommeBicycle_1893/Capus_LHommeBicycle_1893.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mathilde\Desktop\Doctorat - 2025-2028\Pipeline\SFonto\data\Capus_LHommeBicycle_1893\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66BFB3D0-F81C-4259-B724-3652B224675A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE28319B-8DA5-4AA5-922C-9EE234713C91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Work" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="856" uniqueCount="445">
   <si>
     <t>Classe</t>
   </si>
@@ -1078,25 +1078,13 @@
     <t>:Native_of_Provence</t>
   </si>
   <si>
-    <t>:Intelligence</t>
-  </si>
-  <si>
     <t>:Fame</t>
   </si>
   <si>
     <t>:Physical_ability</t>
   </si>
   <si>
-    <t>:Political_contempt</t>
-  </si>
-  <si>
     <t>:Beauty</t>
-  </si>
-  <si>
-    <t>:Love</t>
-  </si>
-  <si>
-    <t>:Skepticism</t>
   </si>
   <si>
     <t>Melancholy</t>
@@ -1338,6 +1326,78 @@
   </si>
   <si>
     <t>:Expr_FR_LHomme_Bicycle</t>
+  </si>
+  <si>
+    <t>H5_Personality_Assignment</t>
+  </si>
+  <si>
+    <t>:Marius_Intellect</t>
+  </si>
+  <si>
+    <t>Marius' intellect</t>
+  </si>
+  <si>
+    <t>:Marius_Cautiousness</t>
+  </si>
+  <si>
+    <t>:Marius_Cheerfulness</t>
+  </si>
+  <si>
+    <t>:Local_Doctor_Emotionality</t>
+  </si>
+  <si>
+    <t>:Local_Doctor_Trust</t>
+  </si>
+  <si>
+    <t>:Local_Doctor_Achievement_Striving</t>
+  </si>
+  <si>
+    <t>Marius' cautiousness</t>
+  </si>
+  <si>
+    <t>Marius' cheerfulness</t>
+  </si>
+  <si>
+    <t>Local doctor's achievement striving</t>
+  </si>
+  <si>
+    <t>Local doctor's trust</t>
+  </si>
+  <si>
+    <t>Local doctor's emotionality</t>
+  </si>
+  <si>
+    <t>:Intellect</t>
+  </si>
+  <si>
+    <t>:Cautiousness</t>
+  </si>
+  <si>
+    <t>:Cheerfulness</t>
+  </si>
+  <si>
+    <t>:Emotionality</t>
+  </si>
+  <si>
+    <t>:Trust</t>
+  </si>
+  <si>
+    <t>:Achievement_Striving</t>
+  </si>
+  <si>
+    <t>:Positive_Valence</t>
+  </si>
+  <si>
+    <t>:Negative_Valence</t>
+  </si>
+  <si>
+    <t>HP9 concerns character</t>
+  </si>
+  <si>
+    <t>HP7 has facet</t>
+  </si>
+  <si>
+    <t>HP8 has valence</t>
   </si>
 </sst>
 </file>
@@ -1530,7 +1590,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1643,15 +1703,16 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2018,13 +2079,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="48" t="s">
         <v>116</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
@@ -2048,7 +2109,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="C3" s="34" t="s">
         <v>183</v>
@@ -2109,10 +2170,10 @@
       <c r="B8" s="3"/>
       <c r="C8" s="13"/>
       <c r="D8" s="3" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="44" customFormat="1" x14ac:dyDescent="0.3">
@@ -2120,7 +2181,7 @@
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>182</v>
@@ -2131,7 +2192,7 @@
       <c r="B10" s="3"/>
       <c r="C10" s="13"/>
       <c r="D10" s="3" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>150</v>
@@ -2142,10 +2203,10 @@
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="21" customFormat="1" x14ac:dyDescent="0.3">
@@ -2197,7 +2258,7 @@
         <v>9</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>64</v>
@@ -2206,7 +2267,7 @@
         <v>10</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -2271,12 +2332,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="48" t="s">
         <v>117</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -2313,13 +2374,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="48" t="s">
         <v>122</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -2867,35 +2928,40 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:O23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="3" max="3" width="25.21875" customWidth="1"/>
     <col min="4" max="4" width="27.109375" style="9" customWidth="1"/>
     <col min="5" max="5" width="27.109375" style="16" customWidth="1"/>
     <col min="6" max="6" width="29.77734375" customWidth="1"/>
     <col min="7" max="7" width="28" customWidth="1"/>
     <col min="8" max="8" width="21" style="16" customWidth="1"/>
-    <col min="9" max="9" width="18.77734375" customWidth="1"/>
-    <col min="10" max="10" width="8.88671875" customWidth="1"/>
+    <col min="9" max="11" width="21" style="47" customWidth="1"/>
+    <col min="12" max="12" width="18.77734375" customWidth="1"/>
+    <col min="13" max="14" width="17.77734375" customWidth="1"/>
+    <col min="15" max="15" width="17.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="46" t="s">
+    <row r="1" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="48" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+    </row>
+    <row r="2" spans="1:15" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
         <v>75</v>
       </c>
@@ -2923,8 +2989,20 @@
       <c r="I2" s="10" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="J2" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="M2" s="47"/>
+      <c r="N2" s="47"/>
+      <c r="O2" s="47"/>
+    </row>
+    <row r="3" spans="1:15" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
         <v>13</v>
       </c>
@@ -2935,7 +3013,7 @@
         <v>15</v>
       </c>
       <c r="D3" s="34" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="E3" s="20" t="s">
         <v>81</v>
@@ -2952,8 +3030,11 @@
       <c r="I3" s="2" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J3" s="20"/>
+      <c r="K3" s="20"/>
+      <c r="L3" s="2"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
         <v>13</v>
       </c>
@@ -2964,319 +3045,464 @@
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="17" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G4" s="17" t="s">
         <v>340</v>
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+    </row>
+    <row r="5" spans="1:15" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="12" t="s">
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20" t="s">
         <v>342</v>
       </c>
-      <c r="G5" s="12" t="s">
-        <v>338</v>
-      </c>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="17" t="s">
+      <c r="G5" s="20" t="s">
+        <v>339</v>
+      </c>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="20"/>
+    </row>
+    <row r="6" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C6" s="17"/>
       <c r="D6" s="17"/>
       <c r="E6" s="17"/>
       <c r="F6" s="17" t="s">
-        <v>343</v>
+        <v>410</v>
       </c>
       <c r="G6" s="17" t="s">
         <v>339</v>
       </c>
       <c r="H6" s="17"/>
       <c r="I6" s="17"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="34" t="s">
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="17"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A7" s="20" t="s">
         <v>13</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
+        <v>67</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="D7" s="34" t="s">
+        <v>419</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>81</v>
+      </c>
       <c r="F7" s="20" t="s">
-        <v>345</v>
-      </c>
-      <c r="G7" s="20" t="s">
-        <v>338</v>
-      </c>
-      <c r="H7" s="34"/>
-      <c r="I7" s="34"/>
-    </row>
-    <row r="8" spans="1:10" s="41" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="G7" s="20"/>
+      <c r="H7" s="20" t="s">
+        <v>278</v>
+      </c>
+      <c r="I7" s="20"/>
+      <c r="J7" s="20"/>
+      <c r="K7" s="20"/>
+      <c r="L7" s="20"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A8" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
+      <c r="B8" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>185</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>81</v>
+      </c>
       <c r="F8" s="17" t="s">
-        <v>414</v>
+        <v>344</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>339</v>
-      </c>
-      <c r="H8" s="17"/>
+        <v>340</v>
+      </c>
+      <c r="H8" s="17" t="s">
+        <v>279</v>
+      </c>
       <c r="I8" s="17"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="20" t="s">
+      <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="17"/>
+    </row>
+    <row r="9" spans="1:15" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="C9" s="20" t="s">
-        <v>184</v>
-      </c>
-      <c r="D9" s="34" t="s">
-        <v>423</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>81</v>
-      </c>
+      <c r="B9" s="34" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
       <c r="F9" s="20" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="G9" s="20"/>
-      <c r="H9" s="20" t="s">
-        <v>278</v>
-      </c>
+      <c r="H9" s="20"/>
       <c r="I9" s="20"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J9" s="20"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
+    </row>
+    <row r="10" spans="1:15" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="s">
         <v>13</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>185</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>423</v>
+        <v>186</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>419</v>
       </c>
       <c r="E10" s="17" t="s">
         <v>81</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>346</v>
-      </c>
-      <c r="G10" s="17" t="s">
-        <v>340</v>
-      </c>
-      <c r="H10" s="17" t="s">
-        <v>279</v>
-      </c>
+        <v>410</v>
+      </c>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
       <c r="I10" s="17"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J10" s="17"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="17"/>
+    </row>
+    <row r="11" spans="1:15" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="20" t="s">
         <v>13</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="20" t="s">
-        <v>347</v>
-      </c>
-      <c r="G11" s="20" t="s">
-        <v>338</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>419</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="F11" s="20"/>
+      <c r="G11" s="34"/>
       <c r="H11" s="20"/>
-      <c r="I11" s="20"/>
-      <c r="J11" s="21"/>
-    </row>
-    <row r="12" spans="1:10" s="41" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
+      <c r="I11" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="J11" s="20"/>
+      <c r="K11" s="20"/>
+      <c r="L11" s="20"/>
+    </row>
+    <row r="12" spans="1:15" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>68</v>
+      <c r="B12" s="17" t="s">
+        <v>72</v>
       </c>
       <c r="C12" s="17"/>
       <c r="D12" s="17"/>
       <c r="E12" s="17"/>
       <c r="F12" s="17" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="G12" s="17"/>
       <c r="H12" s="17"/>
       <c r="I12" s="17"/>
-    </row>
-    <row r="13" spans="1:10" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="J12" s="17"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="17"/>
+    </row>
+    <row r="13" spans="1:15" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="20" t="s">
         <v>13</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>186</v>
-      </c>
-      <c r="D13" s="34" t="s">
-        <v>423</v>
+        <v>188</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>419</v>
       </c>
       <c r="E13" s="20" t="s">
         <v>81</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="G13" s="20"/>
       <c r="H13" s="20"/>
-      <c r="I13" s="20"/>
-    </row>
-    <row r="14" spans="1:10" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="I13" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="J13" s="20"/>
+      <c r="K13" s="20"/>
+      <c r="L13" s="20"/>
+    </row>
+    <row r="14" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="17" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>187</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>423</v>
+        <v>189</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>419</v>
       </c>
       <c r="E14" s="17" t="s">
         <v>81</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>348</v>
+        <v>196</v>
       </c>
       <c r="G14" s="17" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="H14" s="17"/>
-      <c r="I14" s="17" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" s="21" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="34" t="s">
-        <v>72</v>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="17"/>
+      <c r="L14" s="17"/>
+    </row>
+    <row r="15" spans="1:15" s="21" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>73</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="20"/>
       <c r="E15" s="20"/>
       <c r="F15" s="20" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="G15" s="20"/>
       <c r="H15" s="20"/>
       <c r="I15" s="20"/>
-    </row>
-    <row r="16" spans="1:10" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="17" t="s">
-        <v>13</v>
+        <v>421</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>70</v>
+        <v>422</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>188</v>
-      </c>
-      <c r="D16" s="4" t="s">
         <v>423</v>
       </c>
-      <c r="E16" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="F16" s="17" t="s">
-        <v>414</v>
-      </c>
-      <c r="G16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="17" t="s">
+        <v>338</v>
+      </c>
       <c r="H16" s="17"/>
-      <c r="I16" s="17" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I16" s="17"/>
+      <c r="J16" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="K16" s="17" t="s">
+        <v>434</v>
+      </c>
+      <c r="L16" s="17" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="20" t="s">
-        <v>16</v>
+        <v>421</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>73</v>
+        <v>424</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>189</v>
-      </c>
-      <c r="D17" s="34" t="s">
-        <v>423</v>
-      </c>
-      <c r="E17" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="F17" s="20" t="s">
-        <v>196</v>
-      </c>
+        <v>429</v>
+      </c>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
       <c r="G17" s="20" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="H17" s="20"/>
       <c r="I17" s="20"/>
-    </row>
-    <row r="18" spans="1:9" s="41" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C18" s="17"/>
+      <c r="J17" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K17" s="20" t="s">
+        <v>435</v>
+      </c>
+      <c r="L17" s="20" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" s="17" t="s">
+        <v>421</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>425</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>430</v>
+      </c>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
-      <c r="F18" s="17" t="s">
-        <v>414</v>
-      </c>
-      <c r="G18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="4" t="s">
+        <v>338</v>
+      </c>
       <c r="H18" s="17"/>
       <c r="I18" s="17"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="G26" s="40"/>
+      <c r="J18" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="K18" s="17" t="s">
+        <v>436</v>
+      </c>
+      <c r="L18" s="17" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="20" t="s">
+        <v>421</v>
+      </c>
+      <c r="B19" s="20" t="s">
+        <v>426</v>
+      </c>
+      <c r="C19" s="20" t="s">
+        <v>433</v>
+      </c>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20" t="s">
+        <v>338</v>
+      </c>
+      <c r="H19" s="20"/>
+      <c r="I19" s="20"/>
+      <c r="J19" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="K19" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="L19" s="20" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" s="17" t="s">
+        <v>421</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>427</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>432</v>
+      </c>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="17" t="s">
+        <v>338</v>
+      </c>
+      <c r="H20" s="17"/>
+      <c r="I20" s="17"/>
+      <c r="J20" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="K20" s="17" t="s">
+        <v>438</v>
+      </c>
+      <c r="L20" s="17" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" s="21" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="20" t="s">
+        <v>421</v>
+      </c>
+      <c r="B21" s="20" t="s">
+        <v>428</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>431</v>
+      </c>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20" t="s">
+        <v>338</v>
+      </c>
+      <c r="H21" s="20"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="K21" s="20" t="s">
+        <v>439</v>
+      </c>
+      <c r="L21" s="20" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="G22" s="20"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="G23" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3296,14 +3522,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
@@ -3340,7 +3566,7 @@
         <v>76</v>
       </c>
       <c r="E3" s="34" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="F3" s="20" t="s">
         <v>81</v>
@@ -3361,7 +3587,7 @@
         <v>77</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="F4" s="5"/>
     </row>
@@ -3379,7 +3605,7 @@
         <v>77</v>
       </c>
       <c r="E5" s="34" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="F5" s="20"/>
     </row>
@@ -3397,7 +3623,7 @@
         <v>76</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="F6" s="18"/>
     </row>
@@ -3415,7 +3641,7 @@
         <v>78</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="F7" s="12"/>
     </row>
@@ -3433,7 +3659,7 @@
         <v>79</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="F8" s="18"/>
     </row>
@@ -3451,7 +3677,7 @@
         <v>194</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="F9" s="20"/>
     </row>
@@ -3469,7 +3695,7 @@
         <v>76</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="F10" s="18"/>
     </row>
@@ -3496,15 +3722,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="48" t="s">
         <v>164</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
@@ -3549,7 +3775,7 @@
         <v>24</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -3568,7 +3794,7 @@
       <c r="E4" s="31"/>
       <c r="F4" s="31"/>
       <c r="G4" s="31" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
@@ -3589,7 +3815,7 @@
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
@@ -3606,11 +3832,11 @@
         <v>205</v>
       </c>
       <c r="E6" s="30" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="F6" s="31"/>
       <c r="G6" s="31" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.3">
@@ -3627,7 +3853,7 @@
       <c r="E7" s="20"/>
       <c r="F7" s="34"/>
       <c r="G7" s="34" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="H7" s="34"/>
     </row>
@@ -3649,7 +3875,7 @@
       </c>
       <c r="F8" s="30"/>
       <c r="G8" s="31" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="H8" s="34"/>
     </row>
@@ -3667,7 +3893,7 @@
       <c r="E9" s="20"/>
       <c r="F9" s="20"/>
       <c r="G9" s="34" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="H9" s="20"/>
     </row>
@@ -3685,7 +3911,7 @@
       <c r="E10" s="30"/>
       <c r="F10" s="30"/>
       <c r="G10" s="31" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="H10" s="20"/>
     </row>
@@ -3712,14 +3938,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="48" t="s">
         <v>80</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
       <c r="G1" s="21"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -4067,17 +4293,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="48" t="s">
         <v>97</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
     </row>
     <row r="2" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
@@ -4606,14 +4832,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="48" t="s">
         <v>114</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
@@ -4644,14 +4870,14 @@
         <v>28</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>98</v>
       </c>
       <c r="E3" s="23"/>
       <c r="F3" s="2" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="G3" s="9"/>
       <c r="H3" s="9"/>
@@ -4663,15 +4889,15 @@
       <c r="B4" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="24" t="s">
-        <v>358</v>
+      <c r="C4" s="8" t="s">
+        <v>354</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>98</v>
       </c>
       <c r="E4" s="35"/>
       <c r="F4" s="8" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="G4" s="9"/>
       <c r="H4" s="9"/>
@@ -4684,12 +4910,12 @@
         <v>30</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="23"/>
       <c r="F5" s="2" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="G5" s="9"/>
       <c r="H5" s="9"/>
@@ -4702,12 +4928,12 @@
         <v>32</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="35"/>
       <c r="F6" s="8" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="G6" s="9"/>
     </row>
@@ -4719,7 +4945,7 @@
         <v>33</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>99</v>
@@ -4728,7 +4954,7 @@
         <v>274</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="G7" s="9"/>
     </row>
@@ -4740,7 +4966,7 @@
         <v>34</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="D8" s="24" t="s">
         <v>100</v>
@@ -4749,7 +4975,7 @@
         <v>274</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="G8" s="9"/>
     </row>
@@ -4761,14 +4987,14 @@
         <v>35</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="D9" s="12" t="s">
         <v>101</v>
       </c>
       <c r="E9" s="23"/>
       <c r="F9" s="2" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="G9" s="9"/>
     </row>
@@ -4780,7 +5006,7 @@
         <v>36</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="D10" s="24" t="s">
         <v>281</v>
@@ -4789,7 +5015,7 @@
         <v>270</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="G10" s="9"/>
     </row>
@@ -4801,7 +5027,7 @@
         <v>37</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="D11" s="12" t="s">
         <v>103</v>
@@ -4810,7 +5036,7 @@
         <v>271</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="G11" s="9"/>
     </row>
@@ -4822,7 +5048,7 @@
         <v>38</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>103</v>
@@ -4831,7 +5057,7 @@
         <v>271</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="G12" s="9"/>
     </row>
@@ -4843,14 +5069,14 @@
         <v>39</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="D13" s="12" t="s">
         <v>104</v>
       </c>
       <c r="E13" s="23"/>
       <c r="F13" s="2" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="G13" s="9"/>
     </row>
@@ -4869,7 +5095,7 @@
       </c>
       <c r="E14" s="35"/>
       <c r="F14" s="8" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="G14" s="9"/>
     </row>
@@ -4881,14 +5107,14 @@
         <v>41</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="D15" s="12" t="s">
         <v>105</v>
       </c>
       <c r="E15" s="23"/>
       <c r="F15" s="2" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="G15" s="9"/>
     </row>
@@ -4900,14 +5126,14 @@
         <v>42</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>105</v>
       </c>
       <c r="E16" s="35"/>
       <c r="F16" s="8" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="G16" s="9"/>
     </row>
@@ -4919,14 +5145,14 @@
         <v>43</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="D17" s="12" t="s">
         <v>106</v>
       </c>
       <c r="E17" s="23"/>
       <c r="F17" s="2" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="G17" s="9"/>
     </row>
@@ -4938,14 +5164,14 @@
         <v>44</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="D18" s="8" t="s">
         <v>107</v>
       </c>
       <c r="E18" s="35"/>
       <c r="F18" s="8" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="G18" s="9"/>
     </row>
@@ -4957,14 +5183,14 @@
         <v>45</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>108</v>
       </c>
       <c r="E19" s="23"/>
       <c r="F19" s="2" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="G19" s="9"/>
     </row>
@@ -4976,14 +5202,14 @@
         <v>46</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>109</v>
       </c>
       <c r="E20" s="35"/>
       <c r="F20" s="8" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="G20" s="9"/>
     </row>
@@ -4995,14 +5221,14 @@
         <v>47</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="D21" s="12" t="s">
         <v>110</v>
       </c>
       <c r="E21" s="36"/>
-      <c r="F21" s="49" t="s">
-        <v>423</v>
+      <c r="F21" s="46" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -5013,14 +5239,14 @@
         <v>48</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="D22" s="24" t="s">
         <v>282</v>
       </c>
       <c r="E22" s="35"/>
       <c r="F22" s="8" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="G22" s="9"/>
     </row>
@@ -5032,7 +5258,7 @@
         <v>49</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="D23" s="12" t="s">
         <v>111</v>
@@ -5041,7 +5267,7 @@
         <v>273</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="G23" s="9"/>
     </row>
@@ -5053,14 +5279,14 @@
         <v>50</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="D24" s="24" t="s">
         <v>112</v>
       </c>
       <c r="E24" s="35"/>
       <c r="F24" s="8" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="G24" s="9"/>
     </row>
@@ -5072,14 +5298,14 @@
         <v>132</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="D25" s="12" t="s">
         <v>113</v>
       </c>
       <c r="E25" s="12"/>
       <c r="F25" s="2" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="G25" s="9"/>
     </row>
@@ -5151,14 +5377,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="48" t="s">
         <v>115</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
     </row>
     <row r="2" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
@@ -5171,13 +5397,13 @@
         <v>2</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>66</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
@@ -5257,17 +5483,17 @@
         <v>53</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="D7" s="13" t="s">
         <v>14</v>
       </c>
       <c r="E7" s="38"/>
       <c r="F7" s="13" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
@@ -5275,17 +5501,17 @@
         <v>53</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="D8" s="12" t="s">
         <v>68</v>
       </c>
       <c r="E8" s="23"/>
       <c r="F8" s="12" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9" spans="1:6" s="33" customFormat="1" x14ac:dyDescent="0.3">
@@ -5295,89 +5521,89 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E10" s="16" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="40" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="B14" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C14" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="B15" t="s">
+        <v>379</v>
+      </c>
+      <c r="C15" t="s">
         <v>383</v>
-      </c>
-      <c r="C15" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="B16" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="C16" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="B17" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C17" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>381</v>
+      </c>
+      <c r="B18" t="s">
+        <v>382</v>
+      </c>
+      <c r="C18" t="s">
         <v>385</v>
-      </c>
-      <c r="B18" t="s">
-        <v>386</v>
-      </c>
-      <c r="C18" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="B19" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="C19" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="B20" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="C20" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -5388,86 +5614,86 @@
         <v>1</v>
       </c>
       <c r="C23" s="29" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D23" s="29" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="E23" s="43" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="B24" t="s">
         <v>139</v>
       </c>
       <c r="C24" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="D24" s="42" t="s">
         <v>126</v>
       </c>
       <c r="E24" s="42" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="B25" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="C25" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="E25" s="42" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>388</v>
+      </c>
+      <c r="B26" t="s">
         <v>392</v>
       </c>
-      <c r="B26" t="s">
-        <v>396</v>
-      </c>
       <c r="C26" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="E26" s="42" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="B27" t="s">
         <v>140</v>
       </c>
       <c r="C27" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="D27" s="42" t="s">
         <v>130</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="B28" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C28" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="E28" s="42" t="s">
         <v>130</v>
@@ -5475,36 +5701,36 @@
     </row>
     <row r="29" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="B29" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="C29" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="D29" s="42" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="E29" s="42" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="B30" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="C30" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="D30" s="42" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="E30" s="42" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
     </row>
   </sheetData>
@@ -5527,12 +5753,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="48" t="s">
         <v>118</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
     </row>
     <row r="2" spans="1:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
@@ -5595,13 +5821,13 @@
         <v>55</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C6" s="19" t="s">
         <v>253</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -5609,13 +5835,13 @@
         <v>55</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>254</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
@@ -5623,13 +5849,13 @@
         <v>55</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C8" s="19" t="s">
         <v>255</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
@@ -5637,13 +5863,13 @@
         <v>55</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>256</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">

--- a/data/Capus_LHommeBicycle_1893/Capus_LHommeBicycle_1893.xlsx
+++ b/data/Capus_LHommeBicycle_1893/Capus_LHommeBicycle_1893.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mathilde\Desktop\Doctorat - 2025-2028\Pipeline\SFonto\data\Capus_LHommeBicycle_1893\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE28319B-8DA5-4AA5-922C-9EE234713C91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84BF3EA7-3754-4B19-9996-54F811C8604E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Work" sheetId="1" r:id="rId1"/>
@@ -22,8 +22,7 @@
     <sheet name="Narrative Units" sheetId="6" r:id="rId7"/>
     <sheet name="Relations" sheetId="7" r:id="rId8"/>
     <sheet name="Archetypes" sheetId="9" r:id="rId9"/>
-    <sheet name="Features" sheetId="8" r:id="rId10"/>
-    <sheet name="Narrative Sequence" sheetId="10" r:id="rId11"/>
+    <sheet name="Narrative Sequence" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -35,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="856" uniqueCount="445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="427">
   <si>
     <t>Classe</t>
   </si>
@@ -88,9 +87,6 @@
     <t>H4_Non_Human_Character</t>
   </si>
   <si>
-    <t>Type (E55)</t>
-  </si>
-  <si>
     <t>G16_Object</t>
   </si>
   <si>
@@ -190,12 +186,6 @@
     <t>:NU22</t>
   </si>
   <si>
-    <t>G4_Social_Relationship</t>
-  </si>
-  <si>
-    <t>:Rel_Marius_Public</t>
-  </si>
-  <si>
     <t>G3_Psychological_State</t>
   </si>
   <si>
@@ -386,9 +376,6 @@
   </si>
   <si>
     <t>Work</t>
-  </si>
-  <si>
-    <t>Features</t>
   </si>
   <si>
     <t>Archetypes</t>
@@ -460,37 +447,7 @@
     <t>:Impresario</t>
   </si>
   <si>
-    <t>:Rel_Marius_Father</t>
-  </si>
-  <si>
     <t>:Rel_Marius_Princess</t>
-  </si>
-  <si>
-    <t>:Rel_Marius_Doctor</t>
-  </si>
-  <si>
-    <t>A supportive father-son relationship</t>
-  </si>
-  <si>
-    <t>A romantic relationship</t>
-  </si>
-  <si>
-    <t>A doctor-patient relationship</t>
-  </si>
-  <si>
-    <t>A celebrity-public relationship</t>
-  </si>
-  <si>
-    <t>:type_familial_relation</t>
-  </si>
-  <si>
-    <t>:type_romantic_relation</t>
-  </si>
-  <si>
-    <t>:type_medical_relation</t>
-  </si>
-  <si>
-    <t>:type_celebrity_relation</t>
   </si>
   <si>
     <t>:Feature_heterodiegetic_narrator</t>
@@ -586,10 +543,6 @@
   </si>
   <si>
     <t>P130i features are also found on</t>
-  </si>
-  <si>
-    <t>:Marius,
-:Local_Doctor</t>
   </si>
   <si>
     <t>:Feature_third_person_narrator</t>
@@ -857,10 +810,6 @@
     <t>Midi</t>
   </si>
   <si>
-    <t>:Marius,
-:Humanity_20th</t>
-  </si>
-  <si>
     <t>:Function_lack</t>
   </si>
   <si>
@@ -874,9 +823,6 @@
   </si>
   <si>
     <t>:Function_magical_agent</t>
-  </si>
-  <si>
-    <t>pour G4, les types de relations peuvent être finis ? Il faut voir quand je devrais ajouter les RELATIONSHIP onto</t>
   </si>
   <si>
     <t>plays</t>
@@ -1099,10 +1045,6 @@
     <t>:State_love</t>
   </si>
   <si>
-    <t>G4 → involves
-G3 → state of</t>
-  </si>
-  <si>
     <t>Temporality</t>
   </si>
   <si>
@@ -1183,118 +1125,6 @@
 :Marius_Son</t>
   </si>
   <si>
-    <t>G6_Relationship_Role</t>
-  </si>
-  <si>
-    <t>G4 → HG &amp; HP &amp; RW</t>
-  </si>
-  <si>
-    <t>G1</t>
-  </si>
-  <si>
-    <t>dlp:plays</t>
-  </si>
-  <si>
-    <t>dlp:involves</t>
-  </si>
-  <si>
-    <t>G4 → HG &amp; RW</t>
-  </si>
-  <si>
-    <t>dlp:d-uses</t>
-  </si>
-  <si>
-    <t>G6 → friend</t>
-  </si>
-  <si>
-    <t>G6 → lover</t>
-  </si>
-  <si>
-    <t>G6 → beloved</t>
-  </si>
-  <si>
-    <t>G4</t>
-  </si>
-  <si>
-    <t>Relation between Marius and Marius' father</t>
-  </si>
-  <si>
-    <t>G6</t>
-  </si>
-  <si>
-    <t>involves</t>
-  </si>
-  <si>
-    <t>je peux instancier dans onto les relations pertinentes de RELATIONSHIP</t>
-  </si>
-  <si>
-    <t>:Child_Of</t>
-  </si>
-  <si>
-    <t>:Parent_Of</t>
-  </si>
-  <si>
-    <t>:Child_Of,
-:Parent_Of</t>
-  </si>
-  <si>
-    <t>G4 → d-uses
-G6 → played_by</t>
-  </si>
-  <si>
-    <t>Relation between Marius and the Princess</t>
-  </si>
-  <si>
-    <t>:Spouse_Of</t>
-  </si>
-  <si>
-    <t>:Spouse_of</t>
-  </si>
-  <si>
-    <t>:Rel_King_Princess</t>
-  </si>
-  <si>
-    <t>:Rel_Marius_Princess_Marius_son</t>
-  </si>
-  <si>
-    <t>Relation between the King and the Princess</t>
-  </si>
-  <si>
-    <t>Relation between Marius, the Princess, and the Marius' son</t>
-  </si>
-  <si>
-    <t>:Marius,
-:Princess,
-:Marius_son</t>
-  </si>
-  <si>
-    <t>:King,
-:Princess</t>
-  </si>
-  <si>
-    <t>label</t>
-  </si>
-  <si>
-    <t>:Marius_Father,
-:Marius,
-:Princess,
-:King</t>
-  </si>
-  <si>
-    <t>:Marius,
-:Princess,
-:Marius_Son</t>
-  </si>
-  <si>
-    <t>Child of</t>
-  </si>
-  <si>
-    <t>Parent of</t>
-  </si>
-  <si>
-    <t>Spouse of</t>
-  </si>
-  <si>
     <t>:Male_character</t>
   </si>
   <si>
@@ -1391,13 +1221,116 @@
     <t>:Negative_Valence</t>
   </si>
   <si>
-    <t>HP9 concerns character</t>
-  </si>
-  <si>
     <t>HP7 has facet</t>
   </si>
   <si>
     <t>HP8 has valence</t>
+  </si>
+  <si>
+    <t>schema:birthPlace</t>
+  </si>
+  <si>
+    <t>schema:gender</t>
+  </si>
+  <si>
+    <t>HP9i is personality of</t>
+  </si>
+  <si>
+    <t>:Event_doctor_consultation,
+:Event_surgeon_consultation</t>
+  </si>
+  <si>
+    <t>H7_Relationship_Assignment</t>
+  </si>
+  <si>
+    <t>:ChildOf_Role</t>
+  </si>
+  <si>
+    <t>:Marius_ChildOf</t>
+  </si>
+  <si>
+    <t>HP12i_is_relation_of G1_Character</t>
+  </si>
+  <si>
+    <t>d-uses G6_Relationship_Role</t>
+  </si>
+  <si>
+    <t>HP11_for_relationship G4_Social_Relationship</t>
+  </si>
+  <si>
+    <t>:ParentOf_Role</t>
+  </si>
+  <si>
+    <t>:MariusFather_ParentOf</t>
+  </si>
+  <si>
+    <t>:Rel_Marius_MariusFather</t>
+  </si>
+  <si>
+    <t>:Rel_Princess_King</t>
+  </si>
+  <si>
+    <t>:Princess_ChildOf</t>
+  </si>
+  <si>
+    <t>:King_ParentOf</t>
+  </si>
+  <si>
+    <t>:Princess_ParentOf</t>
+  </si>
+  <si>
+    <t>:MariusSon_ChildOf</t>
+  </si>
+  <si>
+    <t>:Rel_Princess_MariusSon</t>
+  </si>
+  <si>
+    <t>:Princess_SpouseOf</t>
+  </si>
+  <si>
+    <t>:Marius_SpouseOf</t>
+  </si>
+  <si>
+    <t>:SpouseOf_Role</t>
+  </si>
+  <si>
+    <t>generic dependant on</t>
+  </si>
+  <si>
+    <t>Marius is the child of</t>
+  </si>
+  <si>
+    <t>Marius' Father is the parent of</t>
+  </si>
+  <si>
+    <t>Marius is the spouse of</t>
+  </si>
+  <si>
+    <t>Princess is the spouse of</t>
+  </si>
+  <si>
+    <t>Princess is the child of</t>
+  </si>
+  <si>
+    <t>King is the parent of</t>
+  </si>
+  <si>
+    <t>Princess is the parent of</t>
+  </si>
+  <si>
+    <t>Marius' Son is the child of</t>
+  </si>
+  <si>
+    <t>:Humanity20th_KnowsByReputation</t>
+  </si>
+  <si>
+    <t>Humanity of the 20th century knows by reputation</t>
+  </si>
+  <si>
+    <t>:Rel_Humanity20th_Marius</t>
+  </si>
+  <si>
+    <t>:KnowsByReputation_Role</t>
   </si>
 </sst>
 </file>
@@ -1483,7 +1416,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1543,7 +1476,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1590,7 +1529,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1676,7 +1615,6 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1689,16 +1627,10 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1707,12 +1639,19 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2080,7 +2019,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="48" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B1" s="49"/>
       <c r="C1" s="49"/>
@@ -2089,7 +2028,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -2098,10 +2037,10 @@
         <v>2</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -2109,10 +2048,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="C3" s="34" t="s">
-        <v>183</v>
+        <v>367</v>
+      </c>
+      <c r="C3" s="33" t="s">
+        <v>168</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>5</v>
@@ -2126,10 +2065,10 @@
       <c r="B4" s="3"/>
       <c r="C4" s="13"/>
       <c r="D4" s="13" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -2140,7 +2079,7 @@
         <v>6</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -2150,7 +2089,7 @@
       <c r="D6" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="37">
+      <c r="E6" s="36">
         <v>1893</v>
       </c>
     </row>
@@ -2162,29 +2101,29 @@
         <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" s="44" customFormat="1" x14ac:dyDescent="0.3">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="13"/>
       <c r="B8" s="3"/>
       <c r="C8" s="13"/>
       <c r="D8" s="3" t="s">
-        <v>412</v>
+        <v>360</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" s="44" customFormat="1" x14ac:dyDescent="0.3">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2" t="s">
-        <v>412</v>
+        <v>360</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
@@ -2192,10 +2131,10 @@
       <c r="B10" s="3"/>
       <c r="C10" s="13"/>
       <c r="D10" s="3" t="s">
-        <v>412</v>
+        <v>360</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -2203,10 +2142,10 @@
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2" t="s">
-        <v>412</v>
+        <v>360</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>414</v>
+        <v>362</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="21" customFormat="1" x14ac:dyDescent="0.3">
@@ -2214,21 +2153,21 @@
       <c r="B12" s="3"/>
       <c r="C12" s="13"/>
       <c r="D12" s="13" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:5" s="21" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="34"/>
-      <c r="B13" s="34"/>
-      <c r="C13" s="34"/>
-      <c r="D13" s="34" t="s">
-        <v>259</v>
-      </c>
-      <c r="E13" s="34" t="s">
-        <v>81</v>
+      <c r="A13" s="33"/>
+      <c r="B13" s="33"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33" t="s">
+        <v>244</v>
+      </c>
+      <c r="E13" s="33" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:5" s="21" customFormat="1" x14ac:dyDescent="0.3">
@@ -2236,21 +2175,21 @@
       <c r="B14" s="3"/>
       <c r="C14" s="13"/>
       <c r="D14" s="13" t="s">
-        <v>335</v>
+        <v>318</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:5" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="20"/>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
+      <c r="B15" s="33"/>
+      <c r="C15" s="33"/>
       <c r="D15" s="20" t="s">
-        <v>335</v>
+        <v>318</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -2258,16 +2197,16 @@
         <v>9</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>420</v>
+        <v>368</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>419</v>
+        <v>367</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -2278,7 +2217,7 @@
         <v>8</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="G17" s="11"/>
     </row>
@@ -2300,7 +2239,7 @@
       <c r="B21" s="14"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B22" s="45"/>
+      <c r="B22" s="42"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B23" s="15"/>
@@ -2321,47 +2260,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="38" customWidth="1"/>
-    <col min="3" max="3" width="35" customWidth="1"/>
-    <col min="4" max="4" width="28" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="48" t="s">
-        <v>117</v>
-      </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2375,7 +2273,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="48" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B1" s="49"/>
       <c r="C1" s="49"/>
@@ -2390,30 +2288,30 @@
         <v>1</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>331</v>
+        <v>314</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>332</v>
+        <v>315</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D3" s="22" t="s">
-        <v>285</v>
+        <v>268</v>
       </c>
       <c r="E3" s="22" t="s">
-        <v>308</v>
+        <v>291</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2421,10 +2319,10 @@
       <c r="B4" s="20"/>
       <c r="C4" s="20"/>
       <c r="D4" s="20" t="s">
-        <v>286</v>
+        <v>269</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>309</v>
+        <v>292</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2432,10 +2330,10 @@
       <c r="B5" s="22"/>
       <c r="C5" s="22"/>
       <c r="D5" s="22" t="s">
-        <v>287</v>
+        <v>270</v>
       </c>
       <c r="E5" s="22" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2443,10 +2341,10 @@
       <c r="B6" s="20"/>
       <c r="C6" s="20"/>
       <c r="D6" s="20" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>311</v>
+        <v>294</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2454,10 +2352,10 @@
       <c r="B7" s="22"/>
       <c r="C7" s="22"/>
       <c r="D7" s="22" t="s">
-        <v>289</v>
+        <v>272</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>312</v>
+        <v>295</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2465,10 +2363,10 @@
       <c r="B8" s="20"/>
       <c r="C8" s="20"/>
       <c r="D8" s="20" t="s">
-        <v>290</v>
+        <v>273</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>313</v>
+        <v>296</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2476,10 +2374,10 @@
       <c r="B9" s="22"/>
       <c r="C9" s="22"/>
       <c r="D9" s="22" t="s">
-        <v>291</v>
+        <v>274</v>
       </c>
       <c r="E9" s="22" t="s">
-        <v>314</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2487,10 +2385,10 @@
       <c r="B10" s="20"/>
       <c r="C10" s="20"/>
       <c r="D10" s="20" t="s">
-        <v>292</v>
+        <v>275</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>315</v>
+        <v>298</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2498,10 +2396,10 @@
       <c r="B11" s="22"/>
       <c r="C11" s="22"/>
       <c r="D11" s="22" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>316</v>
+        <v>299</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2509,10 +2407,10 @@
       <c r="B12" s="20"/>
       <c r="C12" s="20"/>
       <c r="D12" s="20" t="s">
-        <v>294</v>
+        <v>277</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>317</v>
+        <v>300</v>
       </c>
     </row>
     <row r="13" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2520,10 +2418,10 @@
       <c r="B13" s="22"/>
       <c r="C13" s="22"/>
       <c r="D13" s="22" t="s">
-        <v>295</v>
+        <v>278</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>318</v>
+        <v>301</v>
       </c>
     </row>
     <row r="14" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2531,10 +2429,10 @@
       <c r="B14" s="20"/>
       <c r="C14" s="20"/>
       <c r="D14" s="20" t="s">
-        <v>296</v>
+        <v>279</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>319</v>
+        <v>302</v>
       </c>
     </row>
     <row r="15" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2542,10 +2440,10 @@
       <c r="B15" s="22"/>
       <c r="C15" s="22"/>
       <c r="D15" s="22" t="s">
-        <v>297</v>
+        <v>280</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>320</v>
+        <v>303</v>
       </c>
     </row>
     <row r="16" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2553,10 +2451,10 @@
       <c r="B16" s="20"/>
       <c r="C16" s="20"/>
       <c r="D16" s="20" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>321</v>
+        <v>304</v>
       </c>
     </row>
     <row r="17" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2564,10 +2462,10 @@
       <c r="B17" s="22"/>
       <c r="C17" s="22"/>
       <c r="D17" s="22" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="E17" s="22" t="s">
-        <v>322</v>
+        <v>305</v>
       </c>
     </row>
     <row r="18" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2575,10 +2473,10 @@
       <c r="B18" s="20"/>
       <c r="C18" s="20"/>
       <c r="D18" s="20" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>323</v>
+        <v>306</v>
       </c>
     </row>
     <row r="19" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2586,10 +2484,10 @@
       <c r="B19" s="22"/>
       <c r="C19" s="22"/>
       <c r="D19" s="22" t="s">
-        <v>301</v>
+        <v>284</v>
       </c>
       <c r="E19" s="22" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
     </row>
     <row r="20" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2597,10 +2495,10 @@
       <c r="B20" s="20"/>
       <c r="C20" s="20"/>
       <c r="D20" s="20" t="s">
-        <v>302</v>
+        <v>285</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>325</v>
+        <v>308</v>
       </c>
     </row>
     <row r="21" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2608,10 +2506,10 @@
       <c r="B21" s="22"/>
       <c r="C21" s="22"/>
       <c r="D21" s="22" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
       <c r="E21" s="22" t="s">
-        <v>326</v>
+        <v>309</v>
       </c>
     </row>
     <row r="22" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2619,10 +2517,10 @@
       <c r="B22" s="20"/>
       <c r="C22" s="20"/>
       <c r="D22" s="20" t="s">
-        <v>304</v>
+        <v>287</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>327</v>
+        <v>310</v>
       </c>
     </row>
     <row r="23" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2630,10 +2528,10 @@
       <c r="B23" s="22"/>
       <c r="C23" s="22"/>
       <c r="D23" s="22" t="s">
-        <v>305</v>
+        <v>288</v>
       </c>
       <c r="E23" s="22" t="s">
-        <v>328</v>
+        <v>311</v>
       </c>
     </row>
     <row r="24" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2641,10 +2539,10 @@
       <c r="B24" s="20"/>
       <c r="C24" s="20"/>
       <c r="D24" s="20" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="E24" s="20" t="s">
-        <v>329</v>
+        <v>312</v>
       </c>
     </row>
     <row r="25" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2652,27 +2550,27 @@
       <c r="B25" s="22"/>
       <c r="C25" s="22"/>
       <c r="D25" s="22" t="s">
-        <v>307</v>
+        <v>290</v>
       </c>
       <c r="E25" s="22" t="s">
-        <v>330</v>
+        <v>313</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="B26" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="B26" s="20" t="s">
-        <v>59</v>
-      </c>
       <c r="C26" s="20" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D26" s="20" t="s">
-        <v>285</v>
+        <v>268</v>
       </c>
       <c r="E26" s="20" t="s">
-        <v>308</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
@@ -2680,10 +2578,10 @@
       <c r="B27" s="22"/>
       <c r="C27" s="22"/>
       <c r="D27" s="22" t="s">
-        <v>286</v>
+        <v>269</v>
       </c>
       <c r="E27" s="22" t="s">
-        <v>309</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
@@ -2691,10 +2589,10 @@
       <c r="B28" s="20"/>
       <c r="C28" s="20"/>
       <c r="D28" s="20" t="s">
-        <v>287</v>
+        <v>270</v>
       </c>
       <c r="E28" s="20" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
@@ -2702,10 +2600,10 @@
       <c r="B29" s="22"/>
       <c r="C29" s="22"/>
       <c r="D29" s="22" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="E29" s="22" t="s">
-        <v>311</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
@@ -2713,10 +2611,10 @@
       <c r="B30" s="20"/>
       <c r="C30" s="20"/>
       <c r="D30" s="20" t="s">
-        <v>289</v>
+        <v>272</v>
       </c>
       <c r="E30" s="20" t="s">
-        <v>312</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
@@ -2724,10 +2622,10 @@
       <c r="B31" s="22"/>
       <c r="C31" s="22"/>
       <c r="D31" s="22" t="s">
-        <v>290</v>
+        <v>273</v>
       </c>
       <c r="E31" s="22" t="s">
-        <v>313</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
@@ -2735,10 +2633,10 @@
       <c r="B32" s="20"/>
       <c r="C32" s="20"/>
       <c r="D32" s="20" t="s">
-        <v>291</v>
+        <v>274</v>
       </c>
       <c r="E32" s="20" t="s">
-        <v>314</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
@@ -2746,10 +2644,10 @@
       <c r="B33" s="22"/>
       <c r="C33" s="22"/>
       <c r="D33" s="22" t="s">
-        <v>292</v>
+        <v>275</v>
       </c>
       <c r="E33" s="22" t="s">
-        <v>315</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
@@ -2757,10 +2655,10 @@
       <c r="B34" s="20"/>
       <c r="C34" s="20"/>
       <c r="D34" s="20" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="E34" s="20" t="s">
-        <v>316</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
@@ -2768,10 +2666,10 @@
       <c r="B35" s="22"/>
       <c r="C35" s="22"/>
       <c r="D35" s="22" t="s">
-        <v>294</v>
+        <v>277</v>
       </c>
       <c r="E35" s="22" t="s">
-        <v>317</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
@@ -2779,10 +2677,10 @@
       <c r="B36" s="20"/>
       <c r="C36" s="20"/>
       <c r="D36" s="20" t="s">
-        <v>295</v>
+        <v>278</v>
       </c>
       <c r="E36" s="20" t="s">
-        <v>318</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
@@ -2790,10 +2688,10 @@
       <c r="B37" s="22"/>
       <c r="C37" s="22"/>
       <c r="D37" s="22" t="s">
-        <v>296</v>
+        <v>279</v>
       </c>
       <c r="E37" s="22" t="s">
-        <v>319</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
@@ -2801,10 +2699,10 @@
       <c r="B38" s="20"/>
       <c r="C38" s="20"/>
       <c r="D38" s="20" t="s">
-        <v>297</v>
+        <v>280</v>
       </c>
       <c r="E38" s="20" t="s">
-        <v>320</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
@@ -2812,10 +2710,10 @@
       <c r="B39" s="22"/>
       <c r="C39" s="22"/>
       <c r="D39" s="22" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="E39" s="22" t="s">
-        <v>321</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
@@ -2823,10 +2721,10 @@
       <c r="B40" s="20"/>
       <c r="C40" s="20"/>
       <c r="D40" s="20" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="E40" s="20" t="s">
-        <v>322</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
@@ -2834,10 +2732,10 @@
       <c r="B41" s="22"/>
       <c r="C41" s="22"/>
       <c r="D41" s="22" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="E41" s="22" t="s">
-        <v>323</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
@@ -2845,10 +2743,10 @@
       <c r="B42" s="20"/>
       <c r="C42" s="20"/>
       <c r="D42" s="20" t="s">
-        <v>301</v>
+        <v>284</v>
       </c>
       <c r="E42" s="20" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
@@ -2856,10 +2754,10 @@
       <c r="B43" s="22"/>
       <c r="C43" s="22"/>
       <c r="D43" s="22" t="s">
-        <v>302</v>
+        <v>285</v>
       </c>
       <c r="E43" s="22" t="s">
-        <v>325</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
@@ -2867,10 +2765,10 @@
       <c r="B44" s="20"/>
       <c r="C44" s="20"/>
       <c r="D44" s="20" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
       <c r="E44" s="20" t="s">
-        <v>326</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
@@ -2878,10 +2776,10 @@
       <c r="B45" s="22"/>
       <c r="C45" s="22"/>
       <c r="D45" s="22" t="s">
-        <v>304</v>
+        <v>287</v>
       </c>
       <c r="E45" s="22" t="s">
-        <v>327</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
@@ -2889,10 +2787,10 @@
       <c r="B46" s="20"/>
       <c r="C46" s="20"/>
       <c r="D46" s="20" t="s">
-        <v>305</v>
+        <v>288</v>
       </c>
       <c r="E46" s="20" t="s">
-        <v>328</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
@@ -2900,10 +2798,10 @@
       <c r="B47" s="22"/>
       <c r="C47" s="22"/>
       <c r="D47" s="22" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="E47" s="22" t="s">
-        <v>329</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
@@ -2911,10 +2809,10 @@
       <c r="B48" s="20"/>
       <c r="C48" s="20"/>
       <c r="D48" s="20" t="s">
-        <v>307</v>
+        <v>290</v>
       </c>
       <c r="E48" s="20" t="s">
-        <v>330</v>
+        <v>313</v>
       </c>
     </row>
   </sheetData>
@@ -2928,7 +2826,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:O23"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -2939,7 +2837,7 @@
     <col min="6" max="6" width="29.77734375" customWidth="1"/>
     <col min="7" max="7" width="28" customWidth="1"/>
     <col min="8" max="8" width="21" style="16" customWidth="1"/>
-    <col min="9" max="11" width="21" style="47" customWidth="1"/>
+    <col min="9" max="11" width="21" style="44" customWidth="1"/>
     <col min="12" max="12" width="18.77734375" customWidth="1"/>
     <col min="13" max="14" width="17.77734375" customWidth="1"/>
     <col min="15" max="15" width="17.88671875" customWidth="1"/>
@@ -2947,7 +2845,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="48" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B1" s="49"/>
       <c r="C1" s="49"/>
@@ -2963,7 +2861,7 @@
     </row>
     <row r="2" spans="1:15" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -2972,63 +2870,63 @@
         <v>2</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>336</v>
+        <v>319</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>337</v>
+        <v>320</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>276</v>
+        <v>259</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>261</v>
+        <v>246</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>442</v>
+        <v>394</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>443</v>
+        <v>390</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="M2" s="47"/>
-      <c r="N2" s="47"/>
-      <c r="O2" s="47"/>
+        <v>391</v>
+      </c>
+      <c r="M2" s="44"/>
+      <c r="N2" s="44"/>
+      <c r="O2" s="44"/>
     </row>
     <row r="3" spans="1:15" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="34" t="s">
+      <c r="C3" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="34" t="s">
-        <v>419</v>
+      <c r="D3" s="33" t="s">
+        <v>367</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>341</v>
+        <v>324</v>
       </c>
       <c r="G3" s="20" t="s">
-        <v>339</v>
+        <v>322</v>
       </c>
       <c r="H3" s="20" t="s">
-        <v>277</v>
+        <v>260</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J3" s="20"/>
       <c r="K3" s="20"/>
@@ -3045,10 +2943,10 @@
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="17" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>340</v>
+        <v>323</v>
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
@@ -3067,10 +2965,10 @@
       <c r="D5" s="20"/>
       <c r="E5" s="20"/>
       <c r="F5" s="20" t="s">
-        <v>342</v>
+        <v>325</v>
       </c>
       <c r="G5" s="20" t="s">
-        <v>339</v>
+        <v>322</v>
       </c>
       <c r="H5" s="20"/>
       <c r="I5" s="20"/>
@@ -3078,7 +2976,7 @@
       <c r="K5" s="20"/>
       <c r="L5" s="20"/>
     </row>
-    <row r="6" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" s="39" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>13</v>
       </c>
@@ -3089,10 +2987,10 @@
       <c r="D6" s="17"/>
       <c r="E6" s="17"/>
       <c r="F6" s="17" t="s">
-        <v>410</v>
+        <v>358</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>339</v>
+        <v>322</v>
       </c>
       <c r="H6" s="17"/>
       <c r="I6" s="17"/>
@@ -3105,23 +3003,25 @@
         <v>13</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>184</v>
-      </c>
-      <c r="D7" s="34" t="s">
-        <v>419</v>
+        <v>169</v>
+      </c>
+      <c r="D7" s="33" t="s">
+        <v>367</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>410</v>
-      </c>
-      <c r="G7" s="20"/>
+        <v>358</v>
+      </c>
+      <c r="G7" s="33" t="s">
+        <v>322</v>
+      </c>
       <c r="H7" s="20" t="s">
-        <v>278</v>
+        <v>261</v>
       </c>
       <c r="I7" s="20"/>
       <c r="J7" s="20"/>
@@ -3133,25 +3033,25 @@
         <v>13</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>419</v>
+        <v>367</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>340</v>
+        <v>323</v>
       </c>
       <c r="H8" s="17" t="s">
-        <v>279</v>
+        <v>262</v>
       </c>
       <c r="I8" s="17"/>
       <c r="J8" s="17"/>
@@ -3159,19 +3059,21 @@
       <c r="L8" s="17"/>
     </row>
     <row r="9" spans="1:15" s="21" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="34" t="s">
+      <c r="A9" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="34" t="s">
-        <v>68</v>
+      <c r="B9" s="33" t="s">
+        <v>65</v>
       </c>
       <c r="C9" s="20"/>
       <c r="D9" s="20"/>
       <c r="E9" s="20"/>
       <c r="F9" s="20" t="s">
-        <v>411</v>
-      </c>
-      <c r="G9" s="20"/>
+        <v>359</v>
+      </c>
+      <c r="G9" s="33" t="s">
+        <v>322</v>
+      </c>
       <c r="H9" s="20"/>
       <c r="I9" s="20"/>
       <c r="J9" s="20"/>
@@ -3183,21 +3085,23 @@
         <v>13</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>419</v>
+        <v>367</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>410</v>
-      </c>
-      <c r="G10" s="17"/>
+        <v>358</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>322</v>
+      </c>
       <c r="H10" s="17"/>
       <c r="I10" s="17"/>
       <c r="J10" s="17"/>
@@ -3209,22 +3113,22 @@
         <v>13</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>419</v>
+        <v>367</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F11" s="20"/>
-      <c r="G11" s="34"/>
+      <c r="G11" s="33"/>
       <c r="H11" s="20"/>
       <c r="I11" s="20" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="J11" s="20"/>
       <c r="K11" s="20"/>
@@ -3235,15 +3139,17 @@
         <v>13</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C12" s="17"/>
       <c r="D12" s="17"/>
       <c r="E12" s="17"/>
       <c r="F12" s="17" t="s">
-        <v>410</v>
-      </c>
-      <c r="G12" s="17"/>
+        <v>358</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>322</v>
+      </c>
       <c r="H12" s="17"/>
       <c r="I12" s="17"/>
       <c r="J12" s="17"/>
@@ -3255,24 +3161,26 @@
         <v>13</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>419</v>
+        <v>367</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>410</v>
-      </c>
-      <c r="G13" s="20"/>
+        <v>358</v>
+      </c>
+      <c r="G13" s="33" t="s">
+        <v>322</v>
+      </c>
       <c r="H13" s="20"/>
       <c r="I13" s="20" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="J13" s="20"/>
       <c r="K13" s="20"/>
@@ -3283,22 +3191,22 @@
         <v>16</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>419</v>
+        <v>367</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="G14" s="17" t="s">
-        <v>340</v>
+        <v>323</v>
       </c>
       <c r="H14" s="17"/>
       <c r="I14" s="17"/>
@@ -3311,15 +3219,17 @@
         <v>16</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="20"/>
       <c r="E15" s="20"/>
       <c r="F15" s="20" t="s">
-        <v>410</v>
-      </c>
-      <c r="G15" s="20"/>
+        <v>358</v>
+      </c>
+      <c r="G15" s="33" t="s">
+        <v>322</v>
+      </c>
       <c r="H15" s="20"/>
       <c r="I15" s="20"/>
       <c r="J15" s="20"/>
@@ -3328,19 +3238,19 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="17" t="s">
-        <v>421</v>
+        <v>369</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>422</v>
+        <v>370</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>423</v>
+        <v>371</v>
       </c>
       <c r="D16" s="17"/>
       <c r="E16" s="17"/>
       <c r="F16" s="17"/>
       <c r="G16" s="17" t="s">
-        <v>338</v>
+        <v>321</v>
       </c>
       <c r="H16" s="17"/>
       <c r="I16" s="17"/>
@@ -3348,27 +3258,27 @@
         <v>14</v>
       </c>
       <c r="K16" s="17" t="s">
-        <v>434</v>
+        <v>382</v>
       </c>
       <c r="L16" s="17" t="s">
-        <v>440</v>
+        <v>388</v>
       </c>
     </row>
     <row r="17" spans="1:12" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="20" t="s">
-        <v>421</v>
+        <v>369</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>424</v>
+        <v>372</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>429</v>
+        <v>377</v>
       </c>
       <c r="D17" s="20"/>
       <c r="E17" s="20"/>
       <c r="F17" s="20"/>
       <c r="G17" s="20" t="s">
-        <v>338</v>
+        <v>321</v>
       </c>
       <c r="H17" s="20"/>
       <c r="I17" s="20"/>
@@ -3376,27 +3286,27 @@
         <v>14</v>
       </c>
       <c r="K17" s="20" t="s">
-        <v>435</v>
+        <v>383</v>
       </c>
       <c r="L17" s="20" t="s">
-        <v>441</v>
+        <v>389</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="17" t="s">
-        <v>421</v>
+        <v>369</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>425</v>
+        <v>373</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>430</v>
+        <v>378</v>
       </c>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
       <c r="F18" s="17"/>
       <c r="G18" s="4" t="s">
-        <v>338</v>
+        <v>321</v>
       </c>
       <c r="H18" s="17"/>
       <c r="I18" s="17"/>
@@ -3404,101 +3314,111 @@
         <v>14</v>
       </c>
       <c r="K18" s="17" t="s">
-        <v>436</v>
+        <v>384</v>
       </c>
       <c r="L18" s="17" t="s">
-        <v>440</v>
+        <v>388</v>
       </c>
     </row>
     <row r="19" spans="1:12" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="20" t="s">
-        <v>421</v>
+        <v>369</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>426</v>
+        <v>374</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>433</v>
+        <v>381</v>
       </c>
       <c r="D19" s="20"/>
       <c r="E19" s="20"/>
       <c r="F19" s="20"/>
       <c r="G19" s="20" t="s">
-        <v>338</v>
+        <v>321</v>
       </c>
       <c r="H19" s="20"/>
       <c r="I19" s="20"/>
       <c r="J19" s="20" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="K19" s="20" t="s">
-        <v>437</v>
+        <v>385</v>
       </c>
       <c r="L19" s="20" t="s">
-        <v>441</v>
+        <v>389</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
-        <v>421</v>
+        <v>369</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>427</v>
+        <v>375</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>432</v>
+        <v>380</v>
       </c>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
       <c r="F20" s="17"/>
       <c r="G20" s="17" t="s">
-        <v>338</v>
+        <v>321</v>
       </c>
       <c r="H20" s="17"/>
       <c r="I20" s="17"/>
       <c r="J20" s="17" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="K20" s="17" t="s">
-        <v>438</v>
+        <v>386</v>
       </c>
       <c r="L20" s="17" t="s">
-        <v>441</v>
+        <v>389</v>
       </c>
     </row>
     <row r="21" spans="1:12" s="21" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A21" s="20" t="s">
-        <v>421</v>
+        <v>369</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>428</v>
+        <v>376</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>431</v>
+        <v>379</v>
       </c>
       <c r="D21" s="20"/>
       <c r="E21" s="20"/>
       <c r="F21" s="20"/>
       <c r="G21" s="20" t="s">
-        <v>338</v>
+        <v>321</v>
       </c>
       <c r="H21" s="20"/>
       <c r="I21" s="20"/>
       <c r="J21" s="20" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="K21" s="20" t="s">
-        <v>439</v>
+        <v>387</v>
       </c>
       <c r="L21" s="20" t="s">
-        <v>441</v>
+        <v>389</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="G22" s="20"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="G23" s="40"/>
+      <c r="G23" s="38"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="F24" s="46" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="F25" s="46" t="s">
+        <v>393</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3523,7 +3443,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="48" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B1" s="49"/>
       <c r="C1" s="49"/>
@@ -3533,7 +3453,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -3542,160 +3462,160 @@
         <v>2</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
       <c r="G2" s="21"/>
     </row>
     <row r="3" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="E3" s="34" t="s">
-        <v>419</v>
+        <v>73</v>
+      </c>
+      <c r="E3" s="33" t="s">
+        <v>367</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="G3" s="39"/>
+        <v>78</v>
+      </c>
+      <c r="G3" s="37"/>
     </row>
     <row r="4" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>419</v>
+        <v>367</v>
       </c>
       <c r="F4" s="5"/>
     </row>
     <row r="5" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="20" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>198</v>
-      </c>
-      <c r="C5" s="34" t="s">
-        <v>201</v>
+        <v>183</v>
+      </c>
+      <c r="C5" s="33" t="s">
+        <v>186</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="E5" s="34" t="s">
-        <v>419</v>
+        <v>74</v>
+      </c>
+      <c r="E5" s="33" t="s">
+        <v>367</v>
       </c>
       <c r="F5" s="20"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>419</v>
+        <v>367</v>
       </c>
       <c r="F6" s="18"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>419</v>
+        <v>367</v>
       </c>
       <c r="F7" s="12"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>419</v>
+        <v>367</v>
       </c>
       <c r="F8" s="18"/>
     </row>
     <row r="9" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="20" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>194</v>
-      </c>
-      <c r="E9" s="34" t="s">
-        <v>419</v>
+        <v>179</v>
+      </c>
+      <c r="E9" s="33" t="s">
+        <v>367</v>
       </c>
       <c r="F9" s="20"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>419</v>
+        <v>367</v>
       </c>
       <c r="F10" s="18"/>
     </row>
@@ -3723,7 +3643,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="48" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="B1" s="49"/>
       <c r="C1" s="49"/>
@@ -3734,7 +3654,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -3743,175 +3663,175 @@
         <v>2</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="G2" s="32" t="s">
-        <v>334</v>
+        <v>317</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>419</v>
+        <v>367</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="30" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="B4" s="30" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C4" s="30" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="E4" s="31"/>
       <c r="F4" s="31"/>
       <c r="G4" s="31" t="s">
-        <v>419</v>
+        <v>367</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>419</v>
+        <v>367</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A6" s="30" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="C6" s="30" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="E6" s="30" t="s">
-        <v>375</v>
+        <v>357</v>
       </c>
       <c r="F6" s="31"/>
       <c r="G6" s="31" t="s">
-        <v>419</v>
+        <v>367</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="34" t="s">
-        <v>203</v>
+      <c r="A7" s="33" t="s">
+        <v>188</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" s="34" t="s">
-        <v>211</v>
+        <v>68</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>196</v>
       </c>
       <c r="D7" s="20"/>
       <c r="E7" s="20"/>
-      <c r="F7" s="34"/>
-      <c r="G7" s="34" t="s">
-        <v>419</v>
-      </c>
-      <c r="H7" s="34"/>
+      <c r="F7" s="33"/>
+      <c r="G7" s="33" t="s">
+        <v>367</v>
+      </c>
+      <c r="H7" s="33"/>
     </row>
     <row r="8" spans="1:8" s="21" customFormat="1" ht="66" x14ac:dyDescent="0.3">
       <c r="A8" s="30" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="B8" s="30" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="C8" s="30" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="E8" s="30" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F8" s="30"/>
       <c r="G8" s="31" t="s">
-        <v>419</v>
-      </c>
-      <c r="H8" s="34"/>
+        <v>367</v>
+      </c>
+      <c r="H8" s="33"/>
     </row>
     <row r="9" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="20" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="D9" s="20"/>
       <c r="E9" s="20"/>
       <c r="F9" s="20"/>
-      <c r="G9" s="34" t="s">
-        <v>419</v>
+      <c r="G9" s="33" t="s">
+        <v>367</v>
       </c>
       <c r="H9" s="20"/>
     </row>
     <row r="10" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="30" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="B10" s="30" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="C10" s="30" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="D10" s="30"/>
       <c r="E10" s="30"/>
       <c r="F10" s="30"/>
       <c r="G10" s="31" t="s">
-        <v>419</v>
+        <v>367</v>
       </c>
       <c r="H10" s="20"/>
     </row>
@@ -3939,7 +3859,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="48" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B1" s="49"/>
       <c r="C1" s="49"/>
@@ -3950,7 +3870,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -3959,28 +3879,28 @@
         <v>2</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="G2" s="16"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
@@ -3988,16 +3908,16 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
@@ -4005,35 +3925,35 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="E5" s="12" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F5" s="12"/>
       <c r="G5" s="21"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
@@ -4041,16 +3961,16 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
@@ -4058,16 +3978,16 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
@@ -4075,16 +3995,16 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
@@ -4092,16 +4012,16 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
@@ -4109,106 +4029,106 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="D11" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="E11" s="12" t="s">
         <v>91</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>94</v>
       </c>
       <c r="F11" s="12"/>
       <c r="G11" s="21"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>27</v>
-      </c>
       <c r="D12" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F12" s="19"/>
       <c r="G12" s="21"/>
     </row>
     <row r="13" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>253</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F13" s="20" t="s">
         <v>20</v>
-      </c>
-      <c r="B13" s="20" t="s">
-        <v>154</v>
-      </c>
-      <c r="C13" s="20" t="s">
-        <v>268</v>
-      </c>
-      <c r="D13" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="F13" s="20" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
     </row>
     <row r="15" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E15" s="20"/>
       <c r="F15" s="20"/>
     </row>
     <row r="16" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
@@ -4216,32 +4136,32 @@
     </row>
     <row r="17" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="19" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="E18" s="19" t="s">
         <v>14</v>
@@ -4250,16 +4170,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>14</v>
@@ -4294,7 +4214,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="48" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B1" s="50"/>
       <c r="C1" s="49"/>
@@ -4307,7 +4227,7 @@
     </row>
     <row r="2" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -4316,33 +4236,33 @@
         <v>2</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>280</v>
+        <v>263</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>263</v>
+        <v>248</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>264</v>
+        <v>249</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>283</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>98</v>
+        <v>120</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>95</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="D3" s="12"/>
       <c r="E3" s="2" t="s">
@@ -4350,106 +4270,106 @@
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="12" t="s">
-        <v>284</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A4" s="22" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="F4" s="22" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="G4" s="22" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="H4" s="22" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="I4" s="22" t="s">
-        <v>284</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>100</v>
+        <v>120</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="H5" s="12"/>
       <c r="I5" s="12" t="s">
-        <v>284</v>
+        <v>267</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A6" s="22" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="F6" s="7"/>
       <c r="G6" s="22" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H6" s="22"/>
       <c r="I6" s="22" t="s">
-        <v>284</v>
+        <v>267</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>281</v>
+        <v>264</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>14</v>
@@ -4457,180 +4377,180 @@
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="12" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>284</v>
+        <v>267</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A8" s="22" t="s">
-        <v>124</v>
-      </c>
-      <c r="B8" s="22" t="s">
-        <v>103</v>
+        <v>120</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>100</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>281</v>
+        <v>264</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>14</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="G8" s="22" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="H8" s="22"/>
       <c r="I8" s="22" t="s">
-        <v>284</v>
+        <v>267</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="D9" s="34" t="s">
-        <v>103</v>
+        <v>221</v>
+      </c>
+      <c r="D9" s="33" t="s">
+        <v>100</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F9" s="12"/>
       <c r="G9" s="12" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="H9" s="12"/>
       <c r="I9" s="12" t="s">
-        <v>284</v>
+        <v>267</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A10" s="22" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="G10" s="22" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="H10" s="22"/>
       <c r="I10" s="22" t="s">
-        <v>284</v>
+        <v>267</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A11" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>222</v>
+      </c>
+      <c r="E11" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="B11" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="D11" s="20" t="s">
-        <v>237</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>128</v>
-      </c>
       <c r="F11" s="20" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="H11" s="12"/>
       <c r="I11" s="12" t="s">
-        <v>284</v>
+        <v>267</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A12" s="22" t="s">
-        <v>124</v>
-      </c>
-      <c r="B12" s="22" t="s">
-        <v>106</v>
+        <v>120</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>103</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E12" s="22" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="F12" s="22"/>
       <c r="G12" s="22" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="H12" s="22"/>
       <c r="I12" s="22" t="s">
-        <v>284</v>
+        <v>267</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A13" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>107</v>
+        <v>120</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>104</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="F13" s="12"/>
       <c r="G13" s="12" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="H13" s="12"/>
       <c r="I13" s="12" t="s">
-        <v>284</v>
+        <v>267</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A14" s="22" t="s">
-        <v>124</v>
-      </c>
-      <c r="B14" s="22" t="s">
-        <v>108</v>
+        <v>120</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>105</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>14</v>
@@ -4639,44 +4559,44 @@
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
       <c r="I14" s="22" t="s">
-        <v>284</v>
+        <v>267</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="9" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F15" s="12"/>
       <c r="G15" s="12"/>
       <c r="H15" s="12"/>
       <c r="I15" s="12" t="s">
-        <v>284</v>
+        <v>267</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="D16" s="22" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>14</v>
@@ -4685,124 +4605,124 @@
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
       <c r="I16" s="22" t="s">
-        <v>284</v>
+        <v>267</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A17" s="12" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E17" s="12" t="s">
         <v>14</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="G17" s="12"/>
       <c r="H17" s="12"/>
       <c r="I17" s="12" t="s">
-        <v>284</v>
+        <v>267</v>
       </c>
     </row>
     <row r="18" spans="1:9" s="9" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="B18" s="22" t="s">
-        <v>282</v>
+        <v>120</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>265</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="D18" s="22" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
       <c r="H18" s="7"/>
       <c r="I18" s="22" t="s">
-        <v>284</v>
+        <v>267</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>245</v>
+        <v>230</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>282</v>
+        <v>265</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="12" t="s">
-        <v>284</v>
+        <v>267</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>246</v>
+        <v>231</v>
       </c>
       <c r="D20" s="22" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E20" s="22" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F20" s="22"/>
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
       <c r="I20" s="22" t="s">
-        <v>284</v>
+        <v>267</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>113</v>
+        <v>120</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>110</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="D21" s="20" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="12" t="s">
-        <v>284</v>
+        <v>267</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
@@ -4833,7 +4753,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="48" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B1" s="50"/>
       <c r="C1" s="50"/>
@@ -4843,7 +4763,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -4852,460 +4772,460 @@
         <v>2</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>272</v>
+        <v>256</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>333</v>
+        <v>316</v>
       </c>
       <c r="H2" s="9"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>353</v>
+        <v>335</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E3" s="23"/>
       <c r="F3" s="2" t="s">
-        <v>419</v>
+        <v>367</v>
       </c>
       <c r="G3" s="9"/>
       <c r="H3" s="9"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="24" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>354</v>
+        <v>336</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="E4" s="35"/>
+        <v>95</v>
+      </c>
+      <c r="E4" s="34"/>
       <c r="F4" s="8" t="s">
-        <v>419</v>
+        <v>367</v>
       </c>
       <c r="G4" s="9"/>
       <c r="H4" s="9"/>
     </row>
     <row r="5" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>355</v>
+        <v>337</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="23"/>
       <c r="F5" s="2" t="s">
-        <v>419</v>
+        <v>367</v>
       </c>
       <c r="G5" s="9"/>
       <c r="H5" s="9"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="24" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>356</v>
+        <v>338</v>
       </c>
       <c r="D6" s="8"/>
-      <c r="E6" s="35"/>
+      <c r="E6" s="34"/>
       <c r="F6" s="8" t="s">
-        <v>419</v>
+        <v>367</v>
       </c>
       <c r="G6" s="9"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>357</v>
+        <v>339</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>274</v>
+        <v>258</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>419</v>
+        <v>367</v>
       </c>
       <c r="G7" s="9"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="24" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>358</v>
+        <v>340</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>274</v>
+        <v>258</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>419</v>
+        <v>367</v>
       </c>
       <c r="G8" s="9"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>359</v>
+        <v>341</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E9" s="23"/>
       <c r="F9" s="2" t="s">
-        <v>419</v>
+        <v>367</v>
       </c>
       <c r="G9" s="9"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="24" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>360</v>
+        <v>342</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>281</v>
+        <v>264</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>270</v>
+        <v>254</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>419</v>
+        <v>367</v>
       </c>
       <c r="G10" s="9"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="12" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>361</v>
+        <v>343</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>271</v>
+        <v>255</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>419</v>
+        <v>367</v>
       </c>
       <c r="G11" s="9"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="24" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>271</v>
+        <v>255</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>419</v>
+        <v>367</v>
       </c>
       <c r="G12" s="9"/>
     </row>
     <row r="13" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A13" s="12" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>363</v>
+        <v>345</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E13" s="23"/>
       <c r="F13" s="2" t="s">
-        <v>419</v>
+        <v>367</v>
       </c>
       <c r="G13" s="9"/>
     </row>
     <row r="14" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="24" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>237</v>
-      </c>
-      <c r="E14" s="35"/>
+        <v>222</v>
+      </c>
+      <c r="E14" s="34"/>
       <c r="F14" s="8" t="s">
-        <v>419</v>
+        <v>367</v>
       </c>
       <c r="G14" s="9"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>366</v>
+        <v>348</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E15" s="23"/>
       <c r="F15" s="2" t="s">
-        <v>419</v>
+        <v>367</v>
       </c>
       <c r="G15" s="9"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="24" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>364</v>
+        <v>346</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="E16" s="35"/>
+        <v>102</v>
+      </c>
+      <c r="E16" s="34"/>
       <c r="F16" s="8" t="s">
-        <v>419</v>
+        <v>367</v>
       </c>
       <c r="G16" s="9"/>
     </row>
     <row r="17" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A17" s="12" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>365</v>
+        <v>347</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E17" s="23"/>
       <c r="F17" s="2" t="s">
-        <v>419</v>
+        <v>367</v>
       </c>
       <c r="G17" s="9"/>
     </row>
     <row r="18" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="24" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C18" s="24" t="s">
+        <v>349</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="E18" s="34"/>
+      <c r="F18" s="8" t="s">
         <v>367</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="E18" s="35"/>
-      <c r="F18" s="8" t="s">
-        <v>419</v>
       </c>
       <c r="G18" s="9"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="12" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>368</v>
+        <v>350</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E19" s="23"/>
       <c r="F19" s="2" t="s">
-        <v>419</v>
+        <v>367</v>
       </c>
       <c r="G19" s="9"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="24" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>369</v>
+        <v>351</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="E20" s="35"/>
+        <v>106</v>
+      </c>
+      <c r="E20" s="34"/>
       <c r="F20" s="8" t="s">
-        <v>419</v>
+        <v>367</v>
       </c>
       <c r="G20" s="9"/>
     </row>
     <row r="21" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="12" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>370</v>
+        <v>352</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="E21" s="36"/>
-      <c r="F21" s="46" t="s">
-        <v>419</v>
+        <v>107</v>
+      </c>
+      <c r="E21" s="35"/>
+      <c r="F21" s="43" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="24" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B22" s="24" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>371</v>
+        <v>353</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>282</v>
-      </c>
-      <c r="E22" s="35"/>
+        <v>265</v>
+      </c>
+      <c r="E22" s="34"/>
       <c r="F22" s="8" t="s">
-        <v>419</v>
+        <v>367</v>
       </c>
       <c r="G22" s="9"/>
     </row>
     <row r="23" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="12" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>372</v>
+        <v>354</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>273</v>
+        <v>257</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>419</v>
+        <v>367</v>
       </c>
       <c r="G23" s="9"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="24" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>112</v>
-      </c>
-      <c r="E24" s="35"/>
+        <v>109</v>
+      </c>
+      <c r="E24" s="34"/>
       <c r="F24" s="8" t="s">
-        <v>419</v>
+        <v>367</v>
       </c>
       <c r="G24" s="9"/>
     </row>
     <row r="25" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A25" s="12" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E25" s="12"/>
       <c r="F25" s="2" t="s">
-        <v>419</v>
+        <v>367</v>
       </c>
       <c r="G25" s="9"/>
     </row>
@@ -5365,30 +5285,32 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
     <col min="3" max="3" width="35" customWidth="1"/>
-    <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="29" style="16" customWidth="1"/>
-    <col min="6" max="6" width="39" customWidth="1"/>
+    <col min="4" max="4" width="26.109375" customWidth="1"/>
+    <col min="5" max="7" width="26.109375" style="47" customWidth="1"/>
+    <col min="8" max="8" width="39" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="48" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B1" s="49"/>
       <c r="C1" s="49"/>
       <c r="D1" s="49"/>
       <c r="E1" s="49"/>
       <c r="F1" s="49"/>
-    </row>
-    <row r="2" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+    </row>
+    <row r="2" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -5397,345 +5319,369 @@
         <v>2</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>349</v>
+        <v>401</v>
       </c>
       <c r="E2" s="10" t="s">
+        <v>400</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>399</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>398</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>415</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>404</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>397</v>
+      </c>
+      <c r="F3" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="H3" s="20"/>
+    </row>
+    <row r="4" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="52" t="s">
+        <v>396</v>
+      </c>
+      <c r="B4" s="52" t="s">
+        <v>403</v>
+      </c>
+      <c r="C4" s="52" t="s">
+        <v>416</v>
+      </c>
+      <c r="D4" s="52" t="s">
+        <v>404</v>
+      </c>
+      <c r="E4" s="52" t="s">
+        <v>402</v>
+      </c>
+      <c r="F4" s="52" t="s">
+        <v>64</v>
+      </c>
+      <c r="G4" s="52" t="s">
+        <v>95</v>
+      </c>
+      <c r="H4" s="52"/>
+    </row>
+    <row r="5" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>412</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>417</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>413</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="H5" s="20"/>
+    </row>
+    <row r="6" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="52" t="s">
+        <v>396</v>
+      </c>
+      <c r="B6" s="52" t="s">
+        <v>411</v>
+      </c>
+      <c r="C6" s="52" t="s">
+        <v>418</v>
+      </c>
+      <c r="D6" s="52" t="s">
+        <v>135</v>
+      </c>
+      <c r="E6" s="52" t="s">
+        <v>413</v>
+      </c>
+      <c r="F6" s="52" t="s">
+        <v>65</v>
+      </c>
+      <c r="G6" s="52" t="s">
+        <v>108</v>
+      </c>
+      <c r="H6" s="52"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>406</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>419</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>405</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>397</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>265</v>
+      </c>
+      <c r="H7" s="20"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="52" t="s">
+        <v>396</v>
+      </c>
+      <c r="B8" s="52" t="s">
+        <v>407</v>
+      </c>
+      <c r="C8" s="52" t="s">
+        <v>420</v>
+      </c>
+      <c r="D8" s="52" t="s">
+        <v>405</v>
+      </c>
+      <c r="E8" s="52" t="s">
+        <v>402</v>
+      </c>
+      <c r="F8" s="52" t="s">
         <v>66</v>
       </c>
-      <c r="F2" s="10" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="C3" s="38" t="s">
-        <v>142</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="E3" s="38" t="s">
-        <v>146</v>
-      </c>
-      <c r="F3" s="38"/>
-    </row>
-    <row r="4" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>143</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="E4" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="F4" s="23"/>
-    </row>
-    <row r="5" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="C5" s="38" t="s">
-        <v>144</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>181</v>
-      </c>
-      <c r="E5" s="38" t="s">
-        <v>148</v>
-      </c>
-      <c r="F5" s="38"/>
-    </row>
-    <row r="6" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="23" t="s">
-        <v>145</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>269</v>
-      </c>
-      <c r="E6" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="F6" s="23"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>347</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>345</v>
-      </c>
-      <c r="D7" s="13" t="s">
+      <c r="G8" s="52" t="s">
+        <v>265</v>
+      </c>
+      <c r="H8" s="52"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>421</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>410</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>402</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="H9" s="20"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="52" t="s">
+        <v>396</v>
+      </c>
+      <c r="B10" s="52" t="s">
+        <v>409</v>
+      </c>
+      <c r="C10" s="52" t="s">
+        <v>422</v>
+      </c>
+      <c r="D10" s="52" t="s">
+        <v>410</v>
+      </c>
+      <c r="E10" s="52" t="s">
+        <v>397</v>
+      </c>
+      <c r="F10" s="52" t="s">
+        <v>70</v>
+      </c>
+      <c r="G10" s="52" t="s">
+        <v>109</v>
+      </c>
+      <c r="H10" s="52"/>
+    </row>
+    <row r="11" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A11" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>423</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>424</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>425</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>426</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="G11" s="33" t="s">
+        <v>105</v>
+      </c>
+      <c r="H11" s="20"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="52" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" s="52" t="s">
+        <v>330</v>
+      </c>
+      <c r="C12" s="52" t="s">
+        <v>328</v>
+      </c>
+      <c r="D12" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="38"/>
-      <c r="F7" s="13" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>348</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>346</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="E8" s="23"/>
-      <c r="F8" s="12" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" s="33" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="E9" s="33" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="E10" s="16" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="40" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>377</v>
-      </c>
-      <c r="B14" t="s">
-        <v>382</v>
-      </c>
-      <c r="C14" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>378</v>
-      </c>
-      <c r="B15" t="s">
-        <v>379</v>
-      </c>
-      <c r="C15" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>377</v>
-      </c>
-      <c r="B16" t="s">
-        <v>380</v>
-      </c>
-      <c r="C16" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>381</v>
-      </c>
-      <c r="B17" t="s">
-        <v>382</v>
-      </c>
-      <c r="C17" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>381</v>
-      </c>
-      <c r="B18" t="s">
-        <v>382</v>
-      </c>
-      <c r="C18" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>378</v>
-      </c>
-      <c r="B19" t="s">
-        <v>379</v>
-      </c>
-      <c r="C19" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>378</v>
-      </c>
-      <c r="B20" t="s">
-        <v>379</v>
-      </c>
-      <c r="C20" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="29" t="s">
-        <v>75</v>
-      </c>
-      <c r="B23" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="C23" s="29" t="s">
-        <v>404</v>
-      </c>
-      <c r="D23" s="29" t="s">
-        <v>389</v>
-      </c>
-      <c r="E23" s="43" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>386</v>
-      </c>
-      <c r="B24" t="s">
-        <v>139</v>
-      </c>
-      <c r="C24" t="s">
-        <v>387</v>
-      </c>
-      <c r="D24" s="42" t="s">
-        <v>126</v>
-      </c>
-      <c r="E24" s="42" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>388</v>
-      </c>
-      <c r="B25" t="s">
-        <v>391</v>
-      </c>
-      <c r="C25" t="s">
-        <v>407</v>
-      </c>
-      <c r="E25" s="42" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>388</v>
-      </c>
-      <c r="B26" t="s">
-        <v>392</v>
-      </c>
-      <c r="C26" t="s">
-        <v>408</v>
-      </c>
-      <c r="E26" s="42" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>386</v>
-      </c>
-      <c r="B27" t="s">
-        <v>140</v>
-      </c>
-      <c r="C27" t="s">
-        <v>395</v>
-      </c>
-      <c r="D27" s="42" t="s">
-        <v>130</v>
-      </c>
-      <c r="E27" s="16" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>388</v>
-      </c>
-      <c r="B28" t="s">
-        <v>397</v>
-      </c>
-      <c r="C28" t="s">
-        <v>409</v>
-      </c>
-      <c r="E28" s="42" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>386</v>
-      </c>
-      <c r="B29" t="s">
-        <v>398</v>
-      </c>
-      <c r="C29" t="s">
-        <v>400</v>
-      </c>
-      <c r="D29" s="42" t="s">
-        <v>403</v>
-      </c>
-      <c r="E29" s="42" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>386</v>
-      </c>
-      <c r="B30" t="s">
-        <v>399</v>
-      </c>
-      <c r="C30" t="s">
-        <v>401</v>
-      </c>
-      <c r="D30" s="42" t="s">
-        <v>402</v>
-      </c>
-      <c r="E30" s="42" t="s">
-        <v>393</v>
-      </c>
+      <c r="E12" s="52"/>
+      <c r="F12" s="52"/>
+      <c r="G12" s="52"/>
+      <c r="H12" s="52" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>331</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>329</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="21"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E15"/>
+      <c r="F15"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="38"/>
+      <c r="E16"/>
+      <c r="F16"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="51"/>
+      <c r="E17"/>
+      <c r="F17"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="51"/>
+      <c r="E18"/>
+      <c r="F18"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="51"/>
+      <c r="C19" s="47"/>
+      <c r="E19"/>
+      <c r="F19"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C20" s="47"/>
+      <c r="E20"/>
+      <c r="F20"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C21" s="47"/>
+      <c r="E21"/>
+      <c r="F21"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C22" s="47"/>
+      <c r="D22" s="47"/>
+      <c r="E22"/>
+      <c r="F22"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C23" s="47"/>
+      <c r="D23" s="47"/>
+      <c r="E23"/>
+      <c r="F23"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="29"/>
+      <c r="B27" s="29"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="29"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D28" s="40"/>
+      <c r="E28" s="40"/>
+      <c r="F28" s="40"/>
+      <c r="G28" s="40"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D31" s="40"/>
+      <c r="E31" s="40"/>
+      <c r="F31" s="40"/>
+      <c r="G31" s="40"/>
+    </row>
+    <row r="33" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D33" s="40"/>
+      <c r="E33" s="40"/>
+      <c r="F33" s="40"/>
+      <c r="G33" s="40"/>
+    </row>
+    <row r="34" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D34" s="40"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="40"/>
+      <c r="G34" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5743,18 +5689,18 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
-    <col min="4" max="4" width="25" customWidth="1"/>
+    <col min="4" max="4" width="28.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="48" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B1" s="49"/>
       <c r="C1" s="49"/>
@@ -5762,7 +5708,7 @@
     </row>
     <row r="2" spans="1:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -5771,18 +5717,18 @@
         <v>2</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>14</v>
@@ -5790,13 +5736,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="D4" s="19" t="s">
         <v>14</v>
@@ -5804,13 +5750,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="D5" s="12" t="s">
         <v>14</v>
@@ -5818,62 +5764,65 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>415</v>
+        <v>363</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>253</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>419</v>
+        <v>238</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>416</v>
+        <v>364</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>254</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>419</v>
+        <v>239</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A8" s="19" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>417</v>
+        <v>365</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>255</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>419</v>
+        <v>240</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>418</v>
+        <v>366</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>256</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>419</v>
+        <v>241</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C10" s="16"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D11" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/Capus_LHommeBicycle_1893/Capus_LHommeBicycle_1893.xlsx
+++ b/data/Capus_LHommeBicycle_1893/Capus_LHommeBicycle_1893.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mathilde\Desktop\Doctorat - 2025-2028\Pipeline\SFonto\data\Capus_LHommeBicycle_1893\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84BF3EA7-3754-4B19-9996-54F811C8604E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61CC6BE3-FFAB-440E-89FE-E2BCA8D18353}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Work" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="427">
   <si>
     <t>Classe</t>
   </si>
@@ -521,16 +521,7 @@
     <t>has location</t>
   </si>
   <si>
-    <t>:Age_Marius_4yo</t>
-  </si>
-  <si>
-    <t>:Age_Marius_20yo</t>
-  </si>
-  <si>
     <t>Time_Interval</t>
-  </si>
-  <si>
-    <t>:type_age</t>
   </si>
   <si>
     <t>:type_institutional_location</t>
@@ -795,9 +786,6 @@
     <t>participant</t>
   </si>
   <si>
-    <t>temporal location</t>
-  </si>
-  <si>
     <t>P16 used specific object</t>
   </si>
   <si>
@@ -1051,10 +1039,6 @@
     <t>:temporally-overlaps :Event_melancholy</t>
   </si>
   <si>
-    <t>:temporally-overlaps :Event_meet_Marius_Princess,
-:temporally-overlaps :Event_wedding</t>
-  </si>
-  <si>
     <t>Marius is from Provence</t>
   </si>
   <si>
@@ -1331,6 +1315,21 @@
   </si>
   <si>
     <t>:KnowsByReputation_Role</t>
+  </si>
+  <si>
+    <t>state of</t>
+  </si>
+  <si>
+    <t>:follows :Event_meet_Marius_Princess</t>
+  </si>
+  <si>
+    <t>:Time_Marius_4yo</t>
+  </si>
+  <si>
+    <t>:Time_Marius_20yo</t>
+  </si>
+  <si>
+    <t>temporal location / duration</t>
   </si>
 </sst>
 </file>
@@ -1529,7 +1528,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1642,6 +1641,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1649,8 +1653,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2018,13 +2021,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="51" t="s">
         <v>113</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
@@ -2048,10 +2051,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>5</v>
@@ -2065,10 +2068,10 @@
       <c r="B4" s="3"/>
       <c r="C4" s="13"/>
       <c r="D4" s="13" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -2109,10 +2112,10 @@
       <c r="B8" s="3"/>
       <c r="C8" s="13"/>
       <c r="D8" s="3" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="41" customFormat="1" x14ac:dyDescent="0.3">
@@ -2120,10 +2123,10 @@
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
@@ -2131,7 +2134,7 @@
       <c r="B10" s="3"/>
       <c r="C10" s="13"/>
       <c r="D10" s="3" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>136</v>
@@ -2142,10 +2145,10 @@
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="21" customFormat="1" x14ac:dyDescent="0.3">
@@ -2153,7 +2156,7 @@
       <c r="B12" s="3"/>
       <c r="C12" s="13"/>
       <c r="D12" s="13" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E12" s="13" t="s">
         <v>79</v>
@@ -2164,7 +2167,7 @@
       <c r="B13" s="33"/>
       <c r="C13" s="33"/>
       <c r="D13" s="33" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E13" s="33" t="s">
         <v>78</v>
@@ -2175,7 +2178,7 @@
       <c r="B14" s="3"/>
       <c r="C14" s="13"/>
       <c r="D14" s="13" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="E14" s="13" t="s">
         <v>54</v>
@@ -2186,7 +2189,7 @@
       <c r="B15" s="33"/>
       <c r="C15" s="33"/>
       <c r="D15" s="20" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="E15" s="20" t="s">
         <v>56</v>
@@ -2197,7 +2200,7 @@
         <v>9</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>61</v>
@@ -2206,7 +2209,7 @@
         <v>10</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -2272,13 +2275,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="51" t="s">
         <v>118</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -2291,10 +2294,10 @@
         <v>119</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2308,10 +2311,10 @@
         <v>55</v>
       </c>
       <c r="D3" s="22" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="E3" s="22" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2319,10 +2322,10 @@
       <c r="B4" s="20"/>
       <c r="C4" s="20"/>
       <c r="D4" s="20" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2330,10 +2333,10 @@
       <c r="B5" s="22"/>
       <c r="C5" s="22"/>
       <c r="D5" s="22" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="E5" s="22" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2341,10 +2344,10 @@
       <c r="B6" s="20"/>
       <c r="C6" s="20"/>
       <c r="D6" s="20" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2352,10 +2355,10 @@
       <c r="B7" s="22"/>
       <c r="C7" s="22"/>
       <c r="D7" s="22" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2363,10 +2366,10 @@
       <c r="B8" s="20"/>
       <c r="C8" s="20"/>
       <c r="D8" s="20" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2374,10 +2377,10 @@
       <c r="B9" s="22"/>
       <c r="C9" s="22"/>
       <c r="D9" s="22" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="E9" s="22" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2385,10 +2388,10 @@
       <c r="B10" s="20"/>
       <c r="C10" s="20"/>
       <c r="D10" s="20" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2396,10 +2399,10 @@
       <c r="B11" s="22"/>
       <c r="C11" s="22"/>
       <c r="D11" s="22" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2407,10 +2410,10 @@
       <c r="B12" s="20"/>
       <c r="C12" s="20"/>
       <c r="D12" s="20" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="13" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2418,10 +2421,10 @@
       <c r="B13" s="22"/>
       <c r="C13" s="22"/>
       <c r="D13" s="22" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="14" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2429,10 +2432,10 @@
       <c r="B14" s="20"/>
       <c r="C14" s="20"/>
       <c r="D14" s="20" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="15" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2440,10 +2443,10 @@
       <c r="B15" s="22"/>
       <c r="C15" s="22"/>
       <c r="D15" s="22" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="16" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2451,10 +2454,10 @@
       <c r="B16" s="20"/>
       <c r="C16" s="20"/>
       <c r="D16" s="20" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="17" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2462,10 +2465,10 @@
       <c r="B17" s="22"/>
       <c r="C17" s="22"/>
       <c r="D17" s="22" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="E17" s="22" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="18" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2473,10 +2476,10 @@
       <c r="B18" s="20"/>
       <c r="C18" s="20"/>
       <c r="D18" s="20" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="19" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2484,10 +2487,10 @@
       <c r="B19" s="22"/>
       <c r="C19" s="22"/>
       <c r="D19" s="22" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="E19" s="22" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="20" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2495,10 +2498,10 @@
       <c r="B20" s="20"/>
       <c r="C20" s="20"/>
       <c r="D20" s="20" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="21" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2506,10 +2509,10 @@
       <c r="B21" s="22"/>
       <c r="C21" s="22"/>
       <c r="D21" s="22" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="E21" s="22" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="22" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2517,10 +2520,10 @@
       <c r="B22" s="20"/>
       <c r="C22" s="20"/>
       <c r="D22" s="20" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
     </row>
     <row r="23" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2528,10 +2531,10 @@
       <c r="B23" s="22"/>
       <c r="C23" s="22"/>
       <c r="D23" s="22" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="E23" s="22" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
     <row r="24" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2539,10 +2542,10 @@
       <c r="B24" s="20"/>
       <c r="C24" s="20"/>
       <c r="D24" s="20" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E24" s="20" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="25" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2550,10 +2553,10 @@
       <c r="B25" s="22"/>
       <c r="C25" s="22"/>
       <c r="D25" s="22" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E25" s="22" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2567,10 +2570,10 @@
         <v>57</v>
       </c>
       <c r="D26" s="20" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="E26" s="20" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
@@ -2578,10 +2581,10 @@
       <c r="B27" s="22"/>
       <c r="C27" s="22"/>
       <c r="D27" s="22" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="E27" s="22" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
@@ -2589,10 +2592,10 @@
       <c r="B28" s="20"/>
       <c r="C28" s="20"/>
       <c r="D28" s="20" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="E28" s="20" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
@@ -2600,10 +2603,10 @@
       <c r="B29" s="22"/>
       <c r="C29" s="22"/>
       <c r="D29" s="22" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="E29" s="22" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
@@ -2611,10 +2614,10 @@
       <c r="B30" s="20"/>
       <c r="C30" s="20"/>
       <c r="D30" s="20" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="E30" s="20" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
@@ -2622,10 +2625,10 @@
       <c r="B31" s="22"/>
       <c r="C31" s="22"/>
       <c r="D31" s="22" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="E31" s="22" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
@@ -2633,10 +2636,10 @@
       <c r="B32" s="20"/>
       <c r="C32" s="20"/>
       <c r="D32" s="20" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="E32" s="20" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
@@ -2644,10 +2647,10 @@
       <c r="B33" s="22"/>
       <c r="C33" s="22"/>
       <c r="D33" s="22" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="E33" s="22" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
@@ -2655,10 +2658,10 @@
       <c r="B34" s="20"/>
       <c r="C34" s="20"/>
       <c r="D34" s="20" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="E34" s="20" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
@@ -2666,10 +2669,10 @@
       <c r="B35" s="22"/>
       <c r="C35" s="22"/>
       <c r="D35" s="22" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="E35" s="22" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
@@ -2677,10 +2680,10 @@
       <c r="B36" s="20"/>
       <c r="C36" s="20"/>
       <c r="D36" s="20" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="E36" s="20" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
@@ -2688,10 +2691,10 @@
       <c r="B37" s="22"/>
       <c r="C37" s="22"/>
       <c r="D37" s="22" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="E37" s="22" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
@@ -2699,10 +2702,10 @@
       <c r="B38" s="20"/>
       <c r="C38" s="20"/>
       <c r="D38" s="20" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="E38" s="20" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
@@ -2710,10 +2713,10 @@
       <c r="B39" s="22"/>
       <c r="C39" s="22"/>
       <c r="D39" s="22" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="E39" s="22" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
@@ -2721,10 +2724,10 @@
       <c r="B40" s="20"/>
       <c r="C40" s="20"/>
       <c r="D40" s="20" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="E40" s="20" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
@@ -2732,10 +2735,10 @@
       <c r="B41" s="22"/>
       <c r="C41" s="22"/>
       <c r="D41" s="22" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="E41" s="22" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
@@ -2743,10 +2746,10 @@
       <c r="B42" s="20"/>
       <c r="C42" s="20"/>
       <c r="D42" s="20" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="E42" s="20" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
@@ -2754,10 +2757,10 @@
       <c r="B43" s="22"/>
       <c r="C43" s="22"/>
       <c r="D43" s="22" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="E43" s="22" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
@@ -2765,10 +2768,10 @@
       <c r="B44" s="20"/>
       <c r="C44" s="20"/>
       <c r="D44" s="20" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="E44" s="20" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
@@ -2776,10 +2779,10 @@
       <c r="B45" s="22"/>
       <c r="C45" s="22"/>
       <c r="D45" s="22" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="E45" s="22" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
@@ -2787,10 +2790,10 @@
       <c r="B46" s="20"/>
       <c r="C46" s="20"/>
       <c r="D46" s="20" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="E46" s="20" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
@@ -2798,10 +2801,10 @@
       <c r="B47" s="22"/>
       <c r="C47" s="22"/>
       <c r="D47" s="22" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E47" s="22" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
@@ -2809,10 +2812,10 @@
       <c r="B48" s="20"/>
       <c r="C48" s="20"/>
       <c r="D48" s="20" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E48" s="20" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>
@@ -2844,20 +2847,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
     </row>
     <row r="2" spans="1:15" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
@@ -2870,31 +2873,31 @@
         <v>2</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="M2" s="44"/>
       <c r="N2" s="44"/>
@@ -2911,19 +2914,19 @@
         <v>15</v>
       </c>
       <c r="D3" s="33" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="E3" s="20" t="s">
         <v>78</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="G3" s="20" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="H3" s="20" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>30</v>
@@ -2943,10 +2946,10 @@
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="17" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
@@ -2965,10 +2968,10 @@
       <c r="D5" s="20"/>
       <c r="E5" s="20"/>
       <c r="F5" s="20" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="G5" s="20" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="H5" s="20"/>
       <c r="I5" s="20"/>
@@ -2987,10 +2990,10 @@
       <c r="D6" s="17"/>
       <c r="E6" s="17"/>
       <c r="F6" s="17" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="H6" s="17"/>
       <c r="I6" s="17"/>
@@ -3006,22 +3009,22 @@
         <v>64</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>78</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="G7" s="33" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="I7" s="20"/>
       <c r="J7" s="20"/>
@@ -3036,22 +3039,22 @@
         <v>65</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="E8" s="17" t="s">
         <v>78</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="H8" s="17" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="I8" s="17"/>
       <c r="J8" s="17"/>
@@ -3069,10 +3072,10 @@
       <c r="D9" s="20"/>
       <c r="E9" s="20"/>
       <c r="F9" s="20" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="G9" s="33" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="H9" s="20"/>
       <c r="I9" s="20"/>
@@ -3088,19 +3091,19 @@
         <v>66</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="E10" s="17" t="s">
         <v>78</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="H10" s="17"/>
       <c r="I10" s="17"/>
@@ -3116,10 +3119,10 @@
         <v>69</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="E11" s="20" t="s">
         <v>78</v>
@@ -3145,10 +3148,10 @@
       <c r="D12" s="17"/>
       <c r="E12" s="17"/>
       <c r="F12" s="17" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="H12" s="17"/>
       <c r="I12" s="17"/>
@@ -3164,19 +3167,19 @@
         <v>67</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="E13" s="20" t="s">
         <v>78</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="G13" s="33" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="H13" s="20"/>
       <c r="I13" s="20" t="s">
@@ -3194,19 +3197,19 @@
         <v>70</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="E14" s="17" t="s">
         <v>78</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="G14" s="17" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="H14" s="17"/>
       <c r="I14" s="17"/>
@@ -3225,10 +3228,10 @@
       <c r="D15" s="20"/>
       <c r="E15" s="20"/>
       <c r="F15" s="20" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="G15" s="33" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="H15" s="20"/>
       <c r="I15" s="20"/>
@@ -3238,19 +3241,19 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="17" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="D16" s="17"/>
       <c r="E16" s="17"/>
       <c r="F16" s="17"/>
       <c r="G16" s="17" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="H16" s="17"/>
       <c r="I16" s="17"/>
@@ -3258,27 +3261,27 @@
         <v>14</v>
       </c>
       <c r="K16" s="17" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="L16" s="17" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
     </row>
     <row r="17" spans="1:12" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="20" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="B17" s="20" t="s">
+        <v>367</v>
+      </c>
+      <c r="C17" s="20" t="s">
         <v>372</v>
-      </c>
-      <c r="C17" s="20" t="s">
-        <v>377</v>
       </c>
       <c r="D17" s="20"/>
       <c r="E17" s="20"/>
       <c r="F17" s="20"/>
       <c r="G17" s="20" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="H17" s="20"/>
       <c r="I17" s="20"/>
@@ -3286,27 +3289,27 @@
         <v>14</v>
       </c>
       <c r="K17" s="20" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="L17" s="20" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="17" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="B18" s="17" t="s">
+        <v>368</v>
+      </c>
+      <c r="C18" s="17" t="s">
         <v>373</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>378</v>
       </c>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
       <c r="F18" s="17"/>
       <c r="G18" s="4" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="H18" s="17"/>
       <c r="I18" s="17"/>
@@ -3314,27 +3317,27 @@
         <v>14</v>
       </c>
       <c r="K18" s="17" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="L18" s="17" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
     </row>
     <row r="19" spans="1:12" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="20" t="s">
+        <v>364</v>
+      </c>
+      <c r="B19" s="20" t="s">
         <v>369</v>
       </c>
-      <c r="B19" s="20" t="s">
-        <v>374</v>
-      </c>
       <c r="C19" s="20" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="D19" s="20"/>
       <c r="E19" s="20"/>
       <c r="F19" s="20"/>
       <c r="G19" s="20" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="H19" s="20"/>
       <c r="I19" s="20"/>
@@ -3342,27 +3345,27 @@
         <v>69</v>
       </c>
       <c r="K19" s="20" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="L19" s="20" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="B20" s="17" t="s">
+        <v>370</v>
+      </c>
+      <c r="C20" s="17" t="s">
         <v>375</v>
-      </c>
-      <c r="C20" s="17" t="s">
-        <v>380</v>
       </c>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
       <c r="F20" s="17"/>
       <c r="G20" s="17" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="H20" s="17"/>
       <c r="I20" s="17"/>
@@ -3370,27 +3373,27 @@
         <v>69</v>
       </c>
       <c r="K20" s="17" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="L20" s="17" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
     </row>
     <row r="21" spans="1:12" s="21" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A21" s="20" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="D21" s="20"/>
       <c r="E21" s="20"/>
       <c r="F21" s="20"/>
       <c r="G21" s="20" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="H21" s="20"/>
       <c r="I21" s="20"/>
@@ -3398,10 +3401,10 @@
         <v>69</v>
       </c>
       <c r="K21" s="20" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="L21" s="20" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
@@ -3412,12 +3415,12 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F24" s="46" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F25" s="46" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
     </row>
   </sheetData>
@@ -3442,14 +3445,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="51" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
@@ -3465,10 +3468,10 @@
         <v>63</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="G2" s="21"/>
     </row>
@@ -3480,13 +3483,13 @@
         <v>30</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D3" s="20" t="s">
         <v>73</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F3" s="20" t="s">
         <v>78</v>
@@ -3498,34 +3501,34 @@
         <v>129</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>74</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F4" s="5"/>
     </row>
     <row r="5" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="20" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B5" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="C5" s="33" t="s">
         <v>183</v>
-      </c>
-      <c r="C5" s="33" t="s">
-        <v>186</v>
       </c>
       <c r="D5" s="20" t="s">
         <v>74</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F5" s="20"/>
     </row>
@@ -3534,16 +3537,16 @@
         <v>17</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D6" s="18" t="s">
         <v>73</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F6" s="18"/>
     </row>
@@ -3555,13 +3558,13 @@
         <v>145</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D7" s="12" t="s">
         <v>75</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F7" s="12"/>
     </row>
@@ -3573,13 +3576,13 @@
         <v>146</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D8" s="18" t="s">
         <v>76</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F8" s="18"/>
     </row>
@@ -3591,13 +3594,13 @@
         <v>147</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F9" s="20"/>
     </row>
@@ -3609,13 +3612,13 @@
         <v>131</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D10" s="18" t="s">
         <v>73</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F10" s="18"/>
     </row>
@@ -3642,15 +3645,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="51" t="s">
         <v>150</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
@@ -3672,7 +3675,7 @@
         <v>158</v>
       </c>
       <c r="G2" s="32" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -3683,7 +3686,7 @@
         <v>144</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>149</v>
@@ -3695,7 +3698,7 @@
         <v>23</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -3706,7 +3709,7 @@
         <v>152</v>
       </c>
       <c r="C4" s="30" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D4" s="31" t="s">
         <v>151</v>
@@ -3714,7 +3717,7 @@
       <c r="E4" s="31"/>
       <c r="F4" s="31"/>
       <c r="G4" s="31" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
@@ -3725,7 +3728,7 @@
         <v>154</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>155</v>
@@ -3735,7 +3738,7 @@
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
@@ -3743,37 +3746,37 @@
         <v>153</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C6" s="30" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E6" s="30" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="F6" s="31"/>
       <c r="G6" s="31" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="33" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B7" s="20" t="s">
         <v>68</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D7" s="20"/>
       <c r="E7" s="20"/>
       <c r="F7" s="33"/>
       <c r="G7" s="33" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="H7" s="33"/>
     </row>
@@ -3782,56 +3785,56 @@
         <v>153</v>
       </c>
       <c r="B8" s="30" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C8" s="30" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E8" s="30" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F8" s="30"/>
       <c r="G8" s="31" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="H8" s="33"/>
     </row>
     <row r="9" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="20" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B9" s="20" t="s">
         <v>134</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D9" s="20"/>
       <c r="E9" s="20"/>
       <c r="F9" s="20"/>
       <c r="G9" s="33" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="H9" s="20"/>
     </row>
     <row r="10" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="30" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B10" s="30" t="s">
         <v>142</v>
       </c>
       <c r="C10" s="30" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D10" s="30"/>
       <c r="E10" s="30"/>
       <c r="F10" s="30"/>
       <c r="G10" s="31" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="H10" s="20"/>
     </row>
@@ -3858,14 +3861,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="51" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
       <c r="G1" s="21"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -3885,7 +3888,7 @@
         <v>92</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="G2" s="16"/>
     </row>
@@ -3897,7 +3900,7 @@
         <v>78</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>139</v>
@@ -3914,7 +3917,7 @@
         <v>79</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D4" s="19" t="s">
         <v>84</v>
@@ -3931,7 +3934,7 @@
         <v>20</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>21</v>
@@ -3950,7 +3953,7 @@
         <v>80</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>85</v>
@@ -3967,10 +3970,10 @@
         <v>81</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
@@ -3984,10 +3987,10 @@
         <v>82</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
@@ -4001,7 +4004,7 @@
         <v>99</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D9" s="12" t="s">
         <v>86</v>
@@ -4018,7 +4021,7 @@
         <v>83</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D10" s="19" t="s">
         <v>87</v>
@@ -4073,7 +4076,7 @@
         <v>140</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="D13" s="20" t="s">
         <v>21</v>
@@ -4093,7 +4096,7 @@
         <v>141</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>21</v>
@@ -4109,7 +4112,7 @@
         <v>89</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D15" s="20" t="s">
         <v>21</v>
@@ -4125,7 +4128,7 @@
         <v>90</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D16" s="19" t="s">
         <v>21</v>
@@ -4142,7 +4145,7 @@
         <v>91</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D17" s="12" t="s">
         <v>88</v>
@@ -4152,38 +4155,30 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="B18" s="19" t="s">
         <v>159</v>
       </c>
+      <c r="B18" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="C18" s="19" t="s">
-        <v>213</v>
-      </c>
-      <c r="D18" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="E18" s="19" t="s">
-        <v>14</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
       <c r="F18" s="19"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>160</v>
+        <v>425</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>14</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
       <c r="F19" s="2"/>
     </row>
     <row r="21" spans="1:6" s="21" customFormat="1" x14ac:dyDescent="0.3"/>
@@ -4213,19 +4208,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-    </row>
-    <row r="2" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="53"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+    </row>
+    <row r="2" spans="1:9" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
         <v>72</v>
       </c>
@@ -4236,22 +4231,22 @@
         <v>2</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>249</v>
+        <v>426</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -4262,7 +4257,7 @@
         <v>95</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D3" s="12"/>
       <c r="E3" s="2" t="s">
@@ -4274,7 +4269,7 @@
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="12" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -4285,7 +4280,7 @@
         <v>96</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D4" s="22" t="s">
         <v>95</v>
@@ -4294,16 +4289,16 @@
         <v>156</v>
       </c>
       <c r="F4" s="22" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="G4" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="H4" s="22" t="s">
-        <v>159</v>
+      <c r="H4" s="7" t="s">
+        <v>424</v>
       </c>
       <c r="I4" s="22" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -4314,7 +4309,7 @@
         <v>97</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D5" s="20" t="s">
         <v>96</v>
@@ -4323,14 +4318,14 @@
         <v>14</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="G5" s="12" t="s">
         <v>80</v>
       </c>
       <c r="H5" s="12"/>
       <c r="I5" s="12" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -4341,7 +4336,7 @@
         <v>98</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D6" s="22" t="s">
         <v>97</v>
@@ -4355,7 +4350,7 @@
       </c>
       <c r="H6" s="22"/>
       <c r="I6" s="22" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -4363,10 +4358,10 @@
         <v>120</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D7" s="20" t="s">
         <v>98</v>
@@ -4376,11 +4371,11 @@
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
-      <c r="H7" s="12" t="s">
-        <v>160</v>
+      <c r="H7" s="2" t="s">
+        <v>425</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -4391,23 +4386,23 @@
         <v>100</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>14</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="G8" s="22" t="s">
         <v>83</v>
       </c>
       <c r="H8" s="22"/>
       <c r="I8" s="22" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -4418,7 +4413,7 @@
         <v>101</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D9" s="33" t="s">
         <v>100</v>
@@ -4432,7 +4427,7 @@
       </c>
       <c r="H9" s="12"/>
       <c r="I9" s="12" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -4440,10 +4435,10 @@
         <v>120</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D10" s="22" t="s">
         <v>101</v>
@@ -4459,7 +4454,7 @@
       </c>
       <c r="H10" s="22"/>
       <c r="I10" s="22" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -4470,10 +4465,10 @@
         <v>102</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E11" s="12" t="s">
         <v>124</v>
@@ -4486,7 +4481,7 @@
       </c>
       <c r="H11" s="12"/>
       <c r="I11" s="12" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -4497,7 +4492,7 @@
         <v>103</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D12" s="22" t="s">
         <v>102</v>
@@ -4511,7 +4506,7 @@
       </c>
       <c r="H12" s="22"/>
       <c r="I12" s="22" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -4522,7 +4517,7 @@
         <v>104</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D13" s="20" t="s">
         <v>103</v>
@@ -4536,7 +4531,7 @@
       </c>
       <c r="H13" s="12"/>
       <c r="I13" s="12" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -4547,7 +4542,7 @@
         <v>105</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D14" s="22" t="s">
         <v>104</v>
@@ -4559,7 +4554,7 @@
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
       <c r="I14" s="22" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="9" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
@@ -4570,7 +4565,7 @@
         <v>132</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D15" s="20" t="s">
         <v>105</v>
@@ -4582,7 +4577,7 @@
       <c r="G15" s="12"/>
       <c r="H15" s="12"/>
       <c r="I15" s="12" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -4593,7 +4588,7 @@
         <v>106</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="D16" s="22" t="s">
         <v>132</v>
@@ -4605,7 +4600,7 @@
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
       <c r="I16" s="22" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -4616,7 +4611,7 @@
         <v>107</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D17" s="20" t="s">
         <v>106</v>
@@ -4630,7 +4625,7 @@
       <c r="G17" s="12"/>
       <c r="H17" s="12"/>
       <c r="I17" s="12" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="18" spans="1:9" s="9" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
@@ -4638,10 +4633,10 @@
         <v>120</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D18" s="22" t="s">
         <v>107</v>
@@ -4653,7 +4648,7 @@
       <c r="G18" s="7"/>
       <c r="H18" s="7"/>
       <c r="I18" s="22" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -4664,10 +4659,10 @@
         <v>108</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>126</v>
@@ -4676,7 +4671,7 @@
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="12" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -4687,7 +4682,7 @@
         <v>109</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D20" s="22" t="s">
         <v>108</v>
@@ -4699,7 +4694,7 @@
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
       <c r="I20" s="22" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -4710,19 +4705,19 @@
         <v>110</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="D21" s="20" t="s">
         <v>109</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="12" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
@@ -4752,14 +4747,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="51" t="s">
         <v>111</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
@@ -4775,10 +4770,10 @@
         <v>127</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="H2" s="9"/>
     </row>
@@ -4790,14 +4785,14 @@
         <v>27</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>95</v>
       </c>
       <c r="E3" s="23"/>
       <c r="F3" s="2" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="G3" s="9"/>
       <c r="H3" s="9"/>
@@ -4810,14 +4805,14 @@
         <v>28</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>95</v>
       </c>
       <c r="E4" s="34"/>
       <c r="F4" s="8" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="G4" s="9"/>
       <c r="H4" s="9"/>
@@ -4830,12 +4825,12 @@
         <v>29</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="23"/>
       <c r="F5" s="2" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="G5" s="9"/>
       <c r="H5" s="9"/>
@@ -4848,12 +4843,12 @@
         <v>31</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="34"/>
       <c r="F6" s="8" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="G6" s="9"/>
     </row>
@@ -4865,16 +4860,16 @@
         <v>32</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>96</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="G7" s="9"/>
     </row>
@@ -4886,16 +4881,16 @@
         <v>33</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="D8" s="24" t="s">
         <v>97</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="G8" s="9"/>
     </row>
@@ -4907,14 +4902,14 @@
         <v>34</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="D9" s="12" t="s">
         <v>98</v>
       </c>
       <c r="E9" s="23"/>
       <c r="F9" s="2" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="G9" s="9"/>
     </row>
@@ -4926,16 +4921,16 @@
         <v>35</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="G10" s="9"/>
     </row>
@@ -4947,16 +4942,16 @@
         <v>36</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="D11" s="12" t="s">
         <v>100</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="G11" s="9"/>
     </row>
@@ -4968,16 +4963,16 @@
         <v>37</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>100</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="G12" s="9"/>
     </row>
@@ -4989,14 +4984,14 @@
         <v>38</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="D13" s="12" t="s">
         <v>101</v>
       </c>
       <c r="E13" s="23"/>
       <c r="F13" s="2" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="G13" s="9"/>
     </row>
@@ -5008,14 +5003,14 @@
         <v>39</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E14" s="34"/>
       <c r="F14" s="8" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="G14" s="9"/>
     </row>
@@ -5027,14 +5022,14 @@
         <v>40</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="D15" s="12" t="s">
         <v>102</v>
       </c>
       <c r="E15" s="23"/>
       <c r="F15" s="2" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="G15" s="9"/>
     </row>
@@ -5046,14 +5041,14 @@
         <v>41</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>102</v>
       </c>
       <c r="E16" s="34"/>
       <c r="F16" s="8" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="G16" s="9"/>
     </row>
@@ -5065,14 +5060,14 @@
         <v>42</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="D17" s="12" t="s">
         <v>103</v>
       </c>
       <c r="E17" s="23"/>
       <c r="F17" s="2" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="G17" s="9"/>
     </row>
@@ -5084,14 +5079,14 @@
         <v>43</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="D18" s="8" t="s">
         <v>104</v>
       </c>
       <c r="E18" s="34"/>
       <c r="F18" s="8" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="G18" s="9"/>
     </row>
@@ -5103,14 +5098,14 @@
         <v>44</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>105</v>
       </c>
       <c r="E19" s="23"/>
       <c r="F19" s="2" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="G19" s="9"/>
     </row>
@@ -5122,14 +5117,14 @@
         <v>45</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>106</v>
       </c>
       <c r="E20" s="34"/>
       <c r="F20" s="8" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="G20" s="9"/>
     </row>
@@ -5141,14 +5136,14 @@
         <v>46</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="D21" s="12" t="s">
         <v>107</v>
       </c>
       <c r="E21" s="35"/>
       <c r="F21" s="43" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -5159,14 +5154,14 @@
         <v>47</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="E22" s="34"/>
       <c r="F22" s="8" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="G22" s="9"/>
     </row>
@@ -5178,16 +5173,16 @@
         <v>48</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="D23" s="12" t="s">
         <v>108</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="G23" s="9"/>
     </row>
@@ -5199,14 +5194,14 @@
         <v>49</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="D24" s="24" t="s">
         <v>109</v>
       </c>
       <c r="E24" s="34"/>
       <c r="F24" s="8" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="G24" s="9"/>
     </row>
@@ -5218,14 +5213,14 @@
         <v>128</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="D25" s="12" t="s">
         <v>110</v>
       </c>
       <c r="E25" s="12"/>
       <c r="F25" s="2" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="G25" s="9"/>
     </row>
@@ -5285,7 +5280,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -5293,22 +5288,24 @@
     <col min="3" max="3" width="35" customWidth="1"/>
     <col min="4" max="4" width="26.109375" customWidth="1"/>
     <col min="5" max="7" width="26.109375" style="47" customWidth="1"/>
-    <col min="8" max="8" width="39" customWidth="1"/>
+    <col min="8" max="8" width="21" style="48" customWidth="1"/>
+    <col min="9" max="9" width="39" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="48" t="s">
+    <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="51" t="s">
         <v>112</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-    </row>
-    <row r="2" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+    </row>
+    <row r="2" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
         <v>72</v>
       </c>
@@ -5319,36 +5316,39 @@
         <v>2</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>400</v>
-      </c>
-      <c r="F2" s="10" t="s">
+        <v>395</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="20" t="s">
+        <v>391</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>393</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>410</v>
+      </c>
+      <c r="D3" s="20" t="s">
         <v>399</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="20" t="s">
-        <v>396</v>
-      </c>
-      <c r="B3" s="20" t="s">
-        <v>398</v>
-      </c>
-      <c r="C3" s="20" t="s">
-        <v>415</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>404</v>
-      </c>
       <c r="E3" s="20" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="F3" s="20" t="s">
         <v>14</v>
@@ -5357,46 +5357,48 @@
         <v>95</v>
       </c>
       <c r="H3" s="20"/>
-    </row>
-    <row r="4" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="52" t="s">
-        <v>396</v>
-      </c>
-      <c r="B4" s="52" t="s">
-        <v>403</v>
-      </c>
-      <c r="C4" s="52" t="s">
-        <v>416</v>
-      </c>
-      <c r="D4" s="52" t="s">
-        <v>404</v>
-      </c>
-      <c r="E4" s="52" t="s">
-        <v>402</v>
-      </c>
-      <c r="F4" s="52" t="s">
+      <c r="I3" s="20"/>
+    </row>
+    <row r="4" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="50" t="s">
+        <v>391</v>
+      </c>
+      <c r="B4" s="50" t="s">
+        <v>398</v>
+      </c>
+      <c r="C4" s="50" t="s">
+        <v>411</v>
+      </c>
+      <c r="D4" s="50" t="s">
+        <v>399</v>
+      </c>
+      <c r="E4" s="50" t="s">
+        <v>397</v>
+      </c>
+      <c r="F4" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="G4" s="52" t="s">
+      <c r="G4" s="50" t="s">
         <v>95</v>
       </c>
-      <c r="H4" s="52"/>
-    </row>
-    <row r="5" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H4" s="50"/>
+      <c r="I4" s="50"/>
+    </row>
+    <row r="5" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="20" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="B5" s="20" t="s">
+        <v>407</v>
+      </c>
+      <c r="C5" s="20" t="s">
         <v>412</v>
-      </c>
-      <c r="C5" s="20" t="s">
-        <v>417</v>
       </c>
       <c r="D5" s="20" t="s">
         <v>135</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="F5" s="20" t="s">
         <v>14</v>
@@ -5405,94 +5407,98 @@
         <v>108</v>
       </c>
       <c r="H5" s="20"/>
-    </row>
-    <row r="6" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="52" t="s">
-        <v>396</v>
-      </c>
-      <c r="B6" s="52" t="s">
-        <v>411</v>
-      </c>
-      <c r="C6" s="52" t="s">
-        <v>418</v>
-      </c>
-      <c r="D6" s="52" t="s">
+      <c r="I5" s="20"/>
+    </row>
+    <row r="6" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="50" t="s">
+        <v>391</v>
+      </c>
+      <c r="B6" s="50" t="s">
+        <v>406</v>
+      </c>
+      <c r="C6" s="50" t="s">
+        <v>413</v>
+      </c>
+      <c r="D6" s="50" t="s">
         <v>135</v>
       </c>
-      <c r="E6" s="52" t="s">
-        <v>413</v>
-      </c>
-      <c r="F6" s="52" t="s">
+      <c r="E6" s="50" t="s">
+        <v>408</v>
+      </c>
+      <c r="F6" s="50" t="s">
         <v>65</v>
       </c>
-      <c r="G6" s="52" t="s">
+      <c r="G6" s="50" t="s">
         <v>108</v>
       </c>
-      <c r="H6" s="52"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H6" s="50"/>
+      <c r="I6" s="50"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="20" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="F7" s="20" t="s">
         <v>65</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="H7" s="20"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="52" t="s">
-        <v>396</v>
-      </c>
-      <c r="B8" s="52" t="s">
-        <v>407</v>
-      </c>
-      <c r="C8" s="52" t="s">
-        <v>420</v>
-      </c>
-      <c r="D8" s="52" t="s">
+      <c r="I7" s="20"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="50" t="s">
+        <v>391</v>
+      </c>
+      <c r="B8" s="50" t="s">
+        <v>402</v>
+      </c>
+      <c r="C8" s="50" t="s">
+        <v>415</v>
+      </c>
+      <c r="D8" s="50" t="s">
+        <v>400</v>
+      </c>
+      <c r="E8" s="50" t="s">
+        <v>397</v>
+      </c>
+      <c r="F8" s="50" t="s">
+        <v>66</v>
+      </c>
+      <c r="G8" s="50" t="s">
+        <v>261</v>
+      </c>
+      <c r="H8" s="50"/>
+      <c r="I8" s="50"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="20" t="s">
+        <v>391</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>403</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="D9" s="20" t="s">
         <v>405</v>
       </c>
-      <c r="E8" s="52" t="s">
-        <v>402</v>
-      </c>
-      <c r="F8" s="52" t="s">
-        <v>66</v>
-      </c>
-      <c r="G8" s="52" t="s">
-        <v>265</v>
-      </c>
-      <c r="H8" s="52"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="20" t="s">
-        <v>396</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>408</v>
-      </c>
-      <c r="C9" s="20" t="s">
-        <v>421</v>
-      </c>
-      <c r="D9" s="20" t="s">
-        <v>410</v>
-      </c>
       <c r="E9" s="20" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="F9" s="20" t="s">
         <v>65</v>
@@ -5501,96 +5507,101 @@
         <v>109</v>
       </c>
       <c r="H9" s="20"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="52" t="s">
-        <v>396</v>
-      </c>
-      <c r="B10" s="52" t="s">
-        <v>409</v>
-      </c>
-      <c r="C10" s="52" t="s">
-        <v>422</v>
-      </c>
-      <c r="D10" s="52" t="s">
-        <v>410</v>
-      </c>
-      <c r="E10" s="52" t="s">
-        <v>397</v>
-      </c>
-      <c r="F10" s="52" t="s">
+      <c r="I9" s="20"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="50" t="s">
+        <v>391</v>
+      </c>
+      <c r="B10" s="50" t="s">
+        <v>404</v>
+      </c>
+      <c r="C10" s="50" t="s">
+        <v>417</v>
+      </c>
+      <c r="D10" s="50" t="s">
+        <v>405</v>
+      </c>
+      <c r="E10" s="50" t="s">
+        <v>392</v>
+      </c>
+      <c r="F10" s="50" t="s">
         <v>70</v>
       </c>
-      <c r="G10" s="52" t="s">
+      <c r="G10" s="50" t="s">
         <v>109</v>
       </c>
-      <c r="H10" s="52"/>
-    </row>
-    <row r="11" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="H10" s="50"/>
+      <c r="I10" s="50"/>
+    </row>
+    <row r="11" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A11" s="20" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="G11" s="33" t="s">
         <v>105</v>
       </c>
-      <c r="H11" s="20"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="52" t="s">
+      <c r="H11" s="33"/>
+      <c r="I11" s="20"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="50" t="s">
         <v>50</v>
       </c>
-      <c r="B12" s="52" t="s">
-        <v>330</v>
-      </c>
-      <c r="C12" s="52" t="s">
-        <v>328</v>
-      </c>
-      <c r="D12" s="52" t="s">
+      <c r="B12" s="50" t="s">
+        <v>326</v>
+      </c>
+      <c r="C12" s="50" t="s">
+        <v>324</v>
+      </c>
+      <c r="D12" s="50"/>
+      <c r="E12" s="50"/>
+      <c r="F12" s="50"/>
+      <c r="G12" s="50"/>
+      <c r="H12" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="E12" s="52"/>
-      <c r="F12" s="52"/>
-      <c r="G12" s="52"/>
-      <c r="H12" s="52" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="I12" s="50" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="20" t="s">
         <v>50</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>329</v>
-      </c>
-      <c r="D13" s="20" t="s">
-        <v>65</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="D13" s="20"/>
       <c r="E13" s="20"/>
       <c r="F13" s="20"/>
       <c r="G13" s="20"/>
-      <c r="H13" s="20" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H13" s="33" t="s">
+        <v>65</v>
+      </c>
+      <c r="I13" s="33" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="21"/>
       <c r="B14" s="21"/>
       <c r="C14" s="21"/>
@@ -5598,55 +5609,56 @@
       <c r="E14" s="21"/>
       <c r="F14" s="21"/>
       <c r="G14" s="21"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H14" s="21"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E15"/>
       <c r="F15"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="38"/>
       <c r="E16"/>
       <c r="F16"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="51"/>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="49"/>
       <c r="E17"/>
       <c r="F17"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="51"/>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="49"/>
       <c r="E18"/>
       <c r="F18"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="51"/>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="49"/>
       <c r="C19" s="47"/>
       <c r="E19"/>
       <c r="F19"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C20" s="47"/>
       <c r="E20"/>
       <c r="F20"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C21" s="47"/>
       <c r="E21"/>
       <c r="F21"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C22" s="47"/>
       <c r="D22" s="47"/>
       <c r="E22"/>
       <c r="F22"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C23" s="47"/>
       <c r="D23" s="47"/>
       <c r="E23"/>
       <c r="F23"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="29"/>
       <c r="B27" s="29"/>
       <c r="C27" s="29"/>
@@ -5654,34 +5666,39 @@
       <c r="E27" s="29"/>
       <c r="F27" s="29"/>
       <c r="G27" s="29"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H27" s="29"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="D28" s="40"/>
       <c r="E28" s="40"/>
       <c r="F28" s="40"/>
       <c r="G28" s="40"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H28" s="40"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="D31" s="40"/>
       <c r="E31" s="40"/>
       <c r="F31" s="40"/>
       <c r="G31" s="40"/>
-    </row>
-    <row r="33" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="H31" s="40"/>
+    </row>
+    <row r="33" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D33" s="40"/>
       <c r="E33" s="40"/>
       <c r="F33" s="40"/>
       <c r="G33" s="40"/>
-    </row>
-    <row r="34" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="H33" s="40"/>
+    </row>
+    <row r="34" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D34" s="40"/>
       <c r="E34" s="40"/>
       <c r="F34" s="40"/>
       <c r="G34" s="40"/>
+      <c r="H34" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5699,12 +5716,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="51" t="s">
         <v>114</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
     </row>
     <row r="2" spans="1:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
@@ -5717,7 +5734,7 @@
         <v>2</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -5728,7 +5745,7 @@
         <v>115</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>14</v>
@@ -5742,7 +5759,7 @@
         <v>116</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="D4" s="19" t="s">
         <v>14</v>
@@ -5756,7 +5773,7 @@
         <v>117</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D5" s="12" t="s">
         <v>14</v>
@@ -5767,10 +5784,10 @@
         <v>52</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>100</v>
@@ -5781,10 +5798,10 @@
         <v>52</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D7" s="12" t="s">
         <v>110</v>
@@ -5795,10 +5812,10 @@
         <v>52</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D8" s="19" t="s">
         <v>97</v>
@@ -5809,13 +5826,13 @@
         <v>52</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">

--- a/data/Capus_LHommeBicycle_1893/Capus_LHommeBicycle_1893.xlsx
+++ b/data/Capus_LHommeBicycle_1893/Capus_LHommeBicycle_1893.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mathilde\Desktop\Doctorat - 2025-2028\Pipeline\SFonto\data\Capus_LHommeBicycle_1893\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61CC6BE3-FFAB-440E-89FE-E2BCA8D18353}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDE25BBE-F34B-4549-84E0-235367802289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Work" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="419">
   <si>
     <t>Classe</t>
   </si>
@@ -576,9 +576,6 @@
   </si>
   <si>
     <t>Common means of transportation</t>
-  </si>
-  <si>
-    <t>:Born_on_natural_bicycle</t>
   </si>
   <si>
     <t>Bicycle</t>
@@ -994,33 +991,6 @@
     <t>d-uses</t>
   </si>
   <si>
-    <t>GP0 has feature G17 Feature</t>
-  </si>
-  <si>
-    <t>P2 has feature E55 Type</t>
-  </si>
-  <si>
-    <t>:psychological_feature</t>
-  </si>
-  <si>
-    <t>:biographical_feature</t>
-  </si>
-  <si>
-    <t>:physical_feature</t>
-  </si>
-  <si>
-    <t>:Native_of_Provence</t>
-  </si>
-  <si>
-    <t>:Fame</t>
-  </si>
-  <si>
-    <t>:Physical_ability</t>
-  </si>
-  <si>
-    <t>:Beauty</t>
-  </si>
-  <si>
     <t>Melancholy</t>
   </si>
   <si>
@@ -1330,6 +1300,12 @@
   </si>
   <si>
     <t>temporal location / duration</t>
+  </si>
+  <si>
+    <t>property</t>
+  </si>
+  <si>
+    <t>value</t>
   </si>
 </sst>
 </file>
@@ -1415,7 +1391,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1470,12 +1446,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1639,11 +1609,14 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1652,9 +1625,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2021,13 +1991,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="52" t="s">
         <v>113</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
@@ -2051,7 +2021,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="C3" s="33" t="s">
         <v>165</v>
@@ -2068,10 +2038,10 @@
       <c r="B4" s="3"/>
       <c r="C4" s="13"/>
       <c r="D4" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="E4" s="13" t="s">
         <v>239</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -2112,10 +2082,10 @@
       <c r="B8" s="3"/>
       <c r="C8" s="13"/>
       <c r="D8" s="3" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="41" customFormat="1" x14ac:dyDescent="0.3">
@@ -2123,7 +2093,7 @@
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>164</v>
@@ -2134,7 +2104,7 @@
       <c r="B10" s="3"/>
       <c r="C10" s="13"/>
       <c r="D10" s="3" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>136</v>
@@ -2145,10 +2115,10 @@
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="21" customFormat="1" x14ac:dyDescent="0.3">
@@ -2156,7 +2126,7 @@
       <c r="B12" s="3"/>
       <c r="C12" s="13"/>
       <c r="D12" s="13" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E12" s="13" t="s">
         <v>79</v>
@@ -2167,7 +2137,7 @@
       <c r="B13" s="33"/>
       <c r="C13" s="33"/>
       <c r="D13" s="33" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E13" s="33" t="s">
         <v>78</v>
@@ -2178,7 +2148,7 @@
       <c r="B14" s="3"/>
       <c r="C14" s="13"/>
       <c r="D14" s="13" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E14" s="13" t="s">
         <v>54</v>
@@ -2189,7 +2159,7 @@
       <c r="B15" s="33"/>
       <c r="C15" s="33"/>
       <c r="D15" s="20" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E15" s="20" t="s">
         <v>56</v>
@@ -2200,7 +2170,7 @@
         <v>9</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>61</v>
@@ -2209,7 +2179,7 @@
         <v>10</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -2275,13 +2245,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="52" t="s">
         <v>118</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -2294,10 +2264,10 @@
         <v>119</v>
       </c>
       <c r="D2" s="10" t="s">
+        <v>309</v>
+      </c>
+      <c r="E2" s="10" t="s">
         <v>310</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2311,10 +2281,10 @@
         <v>55</v>
       </c>
       <c r="D3" s="22" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E3" s="22" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2322,10 +2292,10 @@
       <c r="B4" s="20"/>
       <c r="C4" s="20"/>
       <c r="D4" s="20" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2333,10 +2303,10 @@
       <c r="B5" s="22"/>
       <c r="C5" s="22"/>
       <c r="D5" s="22" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E5" s="22" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2344,10 +2314,10 @@
       <c r="B6" s="20"/>
       <c r="C6" s="20"/>
       <c r="D6" s="20" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2355,10 +2325,10 @@
       <c r="B7" s="22"/>
       <c r="C7" s="22"/>
       <c r="D7" s="22" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2366,10 +2336,10 @@
       <c r="B8" s="20"/>
       <c r="C8" s="20"/>
       <c r="D8" s="20" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2377,10 +2347,10 @@
       <c r="B9" s="22"/>
       <c r="C9" s="22"/>
       <c r="D9" s="22" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E9" s="22" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2388,10 +2358,10 @@
       <c r="B10" s="20"/>
       <c r="C10" s="20"/>
       <c r="D10" s="20" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2399,10 +2369,10 @@
       <c r="B11" s="22"/>
       <c r="C11" s="22"/>
       <c r="D11" s="22" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2410,10 +2380,10 @@
       <c r="B12" s="20"/>
       <c r="C12" s="20"/>
       <c r="D12" s="20" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="13" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2421,10 +2391,10 @@
       <c r="B13" s="22"/>
       <c r="C13" s="22"/>
       <c r="D13" s="22" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="14" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2432,10 +2402,10 @@
       <c r="B14" s="20"/>
       <c r="C14" s="20"/>
       <c r="D14" s="20" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="15" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2443,10 +2413,10 @@
       <c r="B15" s="22"/>
       <c r="C15" s="22"/>
       <c r="D15" s="22" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="16" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2454,10 +2424,10 @@
       <c r="B16" s="20"/>
       <c r="C16" s="20"/>
       <c r="D16" s="20" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="17" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2465,10 +2435,10 @@
       <c r="B17" s="22"/>
       <c r="C17" s="22"/>
       <c r="D17" s="22" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E17" s="22" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="18" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2476,10 +2446,10 @@
       <c r="B18" s="20"/>
       <c r="C18" s="20"/>
       <c r="D18" s="20" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="19" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2487,10 +2457,10 @@
       <c r="B19" s="22"/>
       <c r="C19" s="22"/>
       <c r="D19" s="22" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E19" s="22" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="20" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2498,10 +2468,10 @@
       <c r="B20" s="20"/>
       <c r="C20" s="20"/>
       <c r="D20" s="20" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="21" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2509,10 +2479,10 @@
       <c r="B21" s="22"/>
       <c r="C21" s="22"/>
       <c r="D21" s="22" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E21" s="22" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="22" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2520,10 +2490,10 @@
       <c r="B22" s="20"/>
       <c r="C22" s="20"/>
       <c r="D22" s="20" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="23" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2531,10 +2501,10 @@
       <c r="B23" s="22"/>
       <c r="C23" s="22"/>
       <c r="D23" s="22" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E23" s="22" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="24" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2542,10 +2512,10 @@
       <c r="B24" s="20"/>
       <c r="C24" s="20"/>
       <c r="D24" s="20" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E24" s="20" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="25" spans="1:5" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2553,10 +2523,10 @@
       <c r="B25" s="22"/>
       <c r="C25" s="22"/>
       <c r="D25" s="22" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E25" s="22" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2570,10 +2540,10 @@
         <v>57</v>
       </c>
       <c r="D26" s="20" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E26" s="20" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
@@ -2581,10 +2551,10 @@
       <c r="B27" s="22"/>
       <c r="C27" s="22"/>
       <c r="D27" s="22" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E27" s="22" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
@@ -2592,10 +2562,10 @@
       <c r="B28" s="20"/>
       <c r="C28" s="20"/>
       <c r="D28" s="20" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E28" s="20" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
@@ -2603,10 +2573,10 @@
       <c r="B29" s="22"/>
       <c r="C29" s="22"/>
       <c r="D29" s="22" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E29" s="22" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
@@ -2614,10 +2584,10 @@
       <c r="B30" s="20"/>
       <c r="C30" s="20"/>
       <c r="D30" s="20" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E30" s="20" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
@@ -2625,10 +2595,10 @@
       <c r="B31" s="22"/>
       <c r="C31" s="22"/>
       <c r="D31" s="22" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E31" s="22" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
@@ -2636,10 +2606,10 @@
       <c r="B32" s="20"/>
       <c r="C32" s="20"/>
       <c r="D32" s="20" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E32" s="20" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
@@ -2647,10 +2617,10 @@
       <c r="B33" s="22"/>
       <c r="C33" s="22"/>
       <c r="D33" s="22" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E33" s="22" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
@@ -2658,10 +2628,10 @@
       <c r="B34" s="20"/>
       <c r="C34" s="20"/>
       <c r="D34" s="20" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E34" s="20" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
@@ -2669,10 +2639,10 @@
       <c r="B35" s="22"/>
       <c r="C35" s="22"/>
       <c r="D35" s="22" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E35" s="22" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
@@ -2680,10 +2650,10 @@
       <c r="B36" s="20"/>
       <c r="C36" s="20"/>
       <c r="D36" s="20" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E36" s="20" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
@@ -2691,10 +2661,10 @@
       <c r="B37" s="22"/>
       <c r="C37" s="22"/>
       <c r="D37" s="22" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E37" s="22" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
@@ -2702,10 +2672,10 @@
       <c r="B38" s="20"/>
       <c r="C38" s="20"/>
       <c r="D38" s="20" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E38" s="20" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
@@ -2713,10 +2683,10 @@
       <c r="B39" s="22"/>
       <c r="C39" s="22"/>
       <c r="D39" s="22" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E39" s="22" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
@@ -2724,10 +2694,10 @@
       <c r="B40" s="20"/>
       <c r="C40" s="20"/>
       <c r="D40" s="20" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E40" s="20" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
@@ -2735,10 +2705,10 @@
       <c r="B41" s="22"/>
       <c r="C41" s="22"/>
       <c r="D41" s="22" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E41" s="22" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
@@ -2746,10 +2716,10 @@
       <c r="B42" s="20"/>
       <c r="C42" s="20"/>
       <c r="D42" s="20" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E42" s="20" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
@@ -2757,10 +2727,10 @@
       <c r="B43" s="22"/>
       <c r="C43" s="22"/>
       <c r="D43" s="22" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E43" s="22" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
@@ -2768,10 +2738,10 @@
       <c r="B44" s="20"/>
       <c r="C44" s="20"/>
       <c r="D44" s="20" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E44" s="20" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
@@ -2779,10 +2749,10 @@
       <c r="B45" s="22"/>
       <c r="C45" s="22"/>
       <c r="D45" s="22" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E45" s="22" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
@@ -2790,10 +2760,10 @@
       <c r="B46" s="20"/>
       <c r="C46" s="20"/>
       <c r="D46" s="20" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E46" s="20" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
@@ -2801,10 +2771,10 @@
       <c r="B47" s="22"/>
       <c r="C47" s="22"/>
       <c r="D47" s="22" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E47" s="22" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
@@ -2812,10 +2782,10 @@
       <c r="B48" s="20"/>
       <c r="C48" s="20"/>
       <c r="D48" s="20" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E48" s="20" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -2829,16 +2799,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:O25"/>
+  <dimension ref="A1:O26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="2" max="2" width="30.44140625" customWidth="1"/>
     <col min="3" max="3" width="25.21875" customWidth="1"/>
     <col min="4" max="4" width="27.109375" style="9" customWidth="1"/>
     <col min="5" max="5" width="27.109375" style="16" customWidth="1"/>
     <col min="6" max="6" width="29.77734375" customWidth="1"/>
-    <col min="7" max="7" width="28" customWidth="1"/>
+    <col min="7" max="7" width="29.77734375" style="50" customWidth="1"/>
     <col min="8" max="8" width="21" style="16" customWidth="1"/>
     <col min="9" max="11" width="21" style="44" customWidth="1"/>
     <col min="12" max="12" width="18.77734375" customWidth="1"/>
@@ -2847,20 +2817,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="52" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
     </row>
     <row r="2" spans="1:15" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
@@ -2876,28 +2846,28 @@
         <v>161</v>
       </c>
       <c r="E2" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="I2" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="F2" s="10" t="s">
-        <v>315</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>316</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>255</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>243</v>
-      </c>
       <c r="J2" s="1" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="M2" s="44"/>
       <c r="N2" s="44"/>
@@ -2914,19 +2884,19 @@
         <v>15</v>
       </c>
       <c r="D3" s="33" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="E3" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="F3" s="20" t="s">
-        <v>320</v>
-      </c>
-      <c r="G3" s="20" t="s">
-        <v>318</v>
+      <c r="F3" s="33" t="s">
+        <v>377</v>
+      </c>
+      <c r="G3" s="33" t="s">
+        <v>20</v>
       </c>
       <c r="H3" s="20" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>30</v>
@@ -2935,175 +2905,197 @@
       <c r="K3" s="20"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A4" s="17" t="s">
+    <row r="4" spans="1:15" s="39" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
       <c r="F4" s="17" t="s">
-        <v>322</v>
+        <v>378</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>319</v>
-      </c>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-    </row>
-    <row r="5" spans="1:15" s="21" customFormat="1" x14ac:dyDescent="0.3">
+        <v>343</v>
+      </c>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="20" t="s">
         <v>13</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="20"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20" t="s">
-        <v>321</v>
-      </c>
-      <c r="G5" s="20" t="s">
-        <v>318</v>
-      </c>
-      <c r="H5" s="20"/>
+        <v>64</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="D5" s="33" t="s">
+        <v>352</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="F5" s="33" t="s">
+        <v>378</v>
+      </c>
+      <c r="G5" s="33" t="s">
+        <v>343</v>
+      </c>
+      <c r="H5" s="20" t="s">
+        <v>256</v>
+      </c>
       <c r="I5" s="20"/>
       <c r="J5" s="20"/>
       <c r="K5" s="20"/>
       <c r="L5" s="20"/>
     </row>
-    <row r="6" spans="1:15" s="39" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A6" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
+      <c r="B6" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>78</v>
+      </c>
       <c r="F6" s="17" t="s">
-        <v>353</v>
+        <v>378</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>318</v>
-      </c>
-      <c r="H6" s="17"/>
+        <v>344</v>
+      </c>
+      <c r="H6" s="17" t="s">
+        <v>257</v>
+      </c>
       <c r="I6" s="17"/>
       <c r="J6" s="17"/>
       <c r="K6" s="17"/>
       <c r="L6" s="17"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="20" t="s">
         <v>13</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>166</v>
-      </c>
-      <c r="D7" s="33" t="s">
-        <v>362</v>
+        <v>168</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>352</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>78</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>353</v>
-      </c>
-      <c r="G7" s="33" t="s">
-        <v>318</v>
-      </c>
-      <c r="H7" s="20" t="s">
-        <v>257</v>
-      </c>
+        <v>378</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>343</v>
+      </c>
+      <c r="H7" s="20"/>
       <c r="I7" s="20"/>
       <c r="J7" s="20"/>
       <c r="K7" s="20"/>
       <c r="L7" s="20"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
         <v>13</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>167</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>362</v>
+        <v>169</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>352</v>
       </c>
       <c r="E8" s="17" t="s">
         <v>78</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>323</v>
+        <v>378</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>319</v>
-      </c>
-      <c r="H8" s="17" t="s">
-        <v>258</v>
-      </c>
-      <c r="I8" s="17"/>
+        <v>343</v>
+      </c>
+      <c r="H8" s="17"/>
+      <c r="I8" s="17" t="s">
+        <v>146</v>
+      </c>
       <c r="J8" s="17"/>
       <c r="K8" s="17"/>
       <c r="L8" s="17"/>
     </row>
     <row r="9" spans="1:15" s="21" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="33" t="s">
+      <c r="A9" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="33" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
+      <c r="B9" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>352</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>78</v>
+      </c>
       <c r="F9" s="20" t="s">
-        <v>354</v>
-      </c>
-      <c r="G9" s="33" t="s">
-        <v>318</v>
+        <v>378</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>343</v>
       </c>
       <c r="H9" s="20"/>
-      <c r="I9" s="20"/>
+      <c r="I9" s="20" t="s">
+        <v>145</v>
+      </c>
       <c r="J9" s="20"/>
       <c r="K9" s="20"/>
       <c r="L9" s="20"/>
     </row>
-    <row r="10" spans="1:15" s="21" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="E10" s="17" t="s">
         <v>78</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>353</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>318</v>
+        <v>378</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>343</v>
       </c>
       <c r="H10" s="17"/>
       <c r="I10" s="17"/>
@@ -3113,315 +3105,199 @@
     </row>
     <row r="11" spans="1:15" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="20" t="s">
-        <v>13</v>
+        <v>354</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>69</v>
+        <v>355</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>169</v>
-      </c>
-      <c r="D11" s="20" t="s">
-        <v>362</v>
-      </c>
-      <c r="E11" s="20" t="s">
-        <v>78</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
       <c r="F11" s="20"/>
-      <c r="G11" s="33"/>
+      <c r="G11" s="20"/>
       <c r="H11" s="20"/>
-      <c r="I11" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="J11" s="20"/>
-      <c r="K11" s="20"/>
-      <c r="L11" s="20"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K11" s="20" t="s">
+        <v>367</v>
+      </c>
+      <c r="L11" s="20" t="s">
+        <v>373</v>
+      </c>
     </row>
     <row r="12" spans="1:15" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
-        <v>13</v>
+        <v>354</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="C12" s="17"/>
+        <v>357</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>362</v>
+      </c>
       <c r="D12" s="17"/>
       <c r="E12" s="17"/>
-      <c r="F12" s="17" t="s">
-        <v>353</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>318</v>
-      </c>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
       <c r="H12" s="17"/>
       <c r="I12" s="17"/>
-      <c r="J12" s="17"/>
-      <c r="K12" s="17"/>
-      <c r="L12" s="17"/>
+      <c r="J12" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="K12" s="17" t="s">
+        <v>368</v>
+      </c>
+      <c r="L12" s="17" t="s">
+        <v>374</v>
+      </c>
     </row>
     <row r="13" spans="1:15" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="20" t="s">
-        <v>13</v>
+        <v>354</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>67</v>
+        <v>358</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="D13" s="20" t="s">
-        <v>362</v>
-      </c>
-      <c r="E13" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="F13" s="20" t="s">
-        <v>353</v>
-      </c>
-      <c r="G13" s="33" t="s">
-        <v>318</v>
-      </c>
+        <v>363</v>
+      </c>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
       <c r="H13" s="20"/>
-      <c r="I13" s="20" t="s">
-        <v>145</v>
-      </c>
-      <c r="J13" s="20"/>
-      <c r="K13" s="20"/>
-      <c r="L13" s="20"/>
-    </row>
-    <row r="14" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I13" s="20"/>
+      <c r="J13" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K13" s="20" t="s">
+        <v>369</v>
+      </c>
+      <c r="L13" s="20" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="17" t="s">
-        <v>16</v>
+        <v>354</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>70</v>
+        <v>359</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>362</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="F14" s="17" t="s">
-        <v>178</v>
-      </c>
-      <c r="G14" s="17" t="s">
-        <v>319</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
       <c r="H14" s="17"/>
       <c r="I14" s="17"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="17"/>
-      <c r="L14" s="17"/>
-    </row>
-    <row r="15" spans="1:15" s="21" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J14" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="K14" s="17" t="s">
+        <v>370</v>
+      </c>
+      <c r="L14" s="17" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="20" t="s">
-        <v>16</v>
+        <v>354</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="C15" s="20"/>
+        <v>360</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>365</v>
+      </c>
       <c r="D15" s="20"/>
       <c r="E15" s="20"/>
-      <c r="F15" s="20" t="s">
-        <v>353</v>
-      </c>
-      <c r="G15" s="33" t="s">
-        <v>318</v>
-      </c>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
       <c r="H15" s="20"/>
       <c r="I15" s="20"/>
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="J15" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="K15" s="20" t="s">
+        <v>371</v>
+      </c>
+      <c r="L15" s="20" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" s="21" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A16" s="17" t="s">
+        <v>354</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>361</v>
+      </c>
+      <c r="C16" s="17" t="s">
         <v>364</v>
-      </c>
-      <c r="B16" s="17" t="s">
-        <v>365</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>366</v>
       </c>
       <c r="D16" s="17"/>
       <c r="E16" s="17"/>
       <c r="F16" s="17"/>
-      <c r="G16" s="17" t="s">
-        <v>317</v>
-      </c>
+      <c r="G16" s="17"/>
       <c r="H16" s="17"/>
       <c r="I16" s="17"/>
       <c r="J16" s="17" t="s">
-        <v>14</v>
+        <v>69</v>
       </c>
       <c r="K16" s="17" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="L16" s="17" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" s="21" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="20" t="s">
-        <v>364</v>
-      </c>
-      <c r="B17" s="20" t="s">
-        <v>367</v>
-      </c>
-      <c r="C17" s="20" t="s">
-        <v>372</v>
-      </c>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="20" t="s">
-        <v>317</v>
-      </c>
-      <c r="H17" s="20"/>
-      <c r="I17" s="20"/>
-      <c r="J17" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="K17" s="20" t="s">
-        <v>378</v>
-      </c>
-      <c r="L17" s="20" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="17" t="s">
-        <v>364</v>
-      </c>
-      <c r="B18" s="17" t="s">
-        <v>368</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>373</v>
-      </c>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="H18" s="17"/>
-      <c r="I18" s="17"/>
-      <c r="J18" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="K18" s="17" t="s">
-        <v>379</v>
-      </c>
-      <c r="L18" s="17" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" s="21" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="20" t="s">
-        <v>364</v>
-      </c>
-      <c r="B19" s="20" t="s">
-        <v>369</v>
-      </c>
-      <c r="C19" s="20" t="s">
-        <v>376</v>
-      </c>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20" t="s">
-        <v>317</v>
-      </c>
-      <c r="H19" s="20"/>
-      <c r="I19" s="20"/>
-      <c r="J19" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="K19" s="20" t="s">
-        <v>380</v>
-      </c>
-      <c r="L19" s="20" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="17" t="s">
-        <v>364</v>
-      </c>
-      <c r="B20" s="17" t="s">
-        <v>370</v>
-      </c>
-      <c r="C20" s="17" t="s">
-        <v>375</v>
-      </c>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17" t="s">
-        <v>317</v>
-      </c>
-      <c r="H20" s="17"/>
-      <c r="I20" s="17"/>
-      <c r="J20" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="K20" s="17" t="s">
-        <v>381</v>
-      </c>
-      <c r="L20" s="17" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" s="21" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A21" s="20" t="s">
-        <v>364</v>
-      </c>
-      <c r="B21" s="20" t="s">
-        <v>371</v>
-      </c>
-      <c r="C21" s="20" t="s">
         <v>374</v>
       </c>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20" t="s">
-        <v>317</v>
-      </c>
-      <c r="H21" s="20"/>
-      <c r="I21" s="20"/>
-      <c r="J21" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="K21" s="20" t="s">
-        <v>382</v>
-      </c>
-      <c r="L21" s="20" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="G22" s="20"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="G23" s="38"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="F24" s="46" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="F25" s="46" t="s">
-        <v>388</v>
-      </c>
+    </row>
+    <row r="19" spans="5:7" x14ac:dyDescent="0.3">
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+    </row>
+    <row r="20" spans="5:7" x14ac:dyDescent="0.3">
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
+    </row>
+    <row r="21" spans="5:7" x14ac:dyDescent="0.3">
+      <c r="E21" s="21"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="21"/>
+    </row>
+    <row r="22" spans="5:7" x14ac:dyDescent="0.3">
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+    </row>
+    <row r="23" spans="5:7" x14ac:dyDescent="0.3">
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="21"/>
+    </row>
+    <row r="24" spans="5:7" x14ac:dyDescent="0.3">
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="21"/>
+    </row>
+    <row r="25" spans="5:7" x14ac:dyDescent="0.3">
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="21"/>
+    </row>
+    <row r="26" spans="5:7" x14ac:dyDescent="0.3">
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3445,14 +3321,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="52" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
@@ -3471,7 +3347,7 @@
         <v>162</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G2" s="21"/>
     </row>
@@ -3483,13 +3359,13 @@
         <v>30</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D3" s="20" t="s">
         <v>73</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="F3" s="20" t="s">
         <v>78</v>
@@ -3501,34 +3377,34 @@
         <v>129</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>181</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>182</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>74</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="F4" s="5"/>
     </row>
     <row r="5" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="20" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D5" s="20" t="s">
         <v>74</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="F5" s="20"/>
     </row>
@@ -3537,7 +3413,7 @@
         <v>17</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>172</v>
@@ -3546,7 +3422,7 @@
         <v>73</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="F6" s="18"/>
     </row>
@@ -3564,7 +3440,7 @@
         <v>75</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="F7" s="12"/>
     </row>
@@ -3582,7 +3458,7 @@
         <v>76</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="F8" s="18"/>
     </row>
@@ -3600,7 +3476,7 @@
         <v>176</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="F9" s="20"/>
     </row>
@@ -3618,7 +3494,7 @@
         <v>73</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="F10" s="18"/>
     </row>
@@ -3645,15 +3521,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="52" t="s">
         <v>150</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
@@ -3675,7 +3551,7 @@
         <v>158</v>
       </c>
       <c r="G2" s="32" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -3686,7 +3562,7 @@
         <v>144</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>149</v>
@@ -3698,7 +3574,7 @@
         <v>23</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -3709,7 +3585,7 @@
         <v>152</v>
       </c>
       <c r="C4" s="30" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D4" s="31" t="s">
         <v>151</v>
@@ -3717,7 +3593,7 @@
       <c r="E4" s="31"/>
       <c r="F4" s="31"/>
       <c r="G4" s="31" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
@@ -3728,7 +3604,7 @@
         <v>154</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>155</v>
@@ -3738,7 +3614,7 @@
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
@@ -3746,37 +3622,37 @@
         <v>153</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C6" s="30" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E6" s="30" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="F6" s="31"/>
       <c r="G6" s="31" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="33" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B7" s="20" t="s">
         <v>68</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D7" s="20"/>
       <c r="E7" s="20"/>
       <c r="F7" s="33"/>
       <c r="G7" s="33" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="H7" s="33"/>
     </row>
@@ -3785,56 +3661,56 @@
         <v>153</v>
       </c>
       <c r="B8" s="30" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C8" s="30" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E8" s="30" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F8" s="30"/>
       <c r="G8" s="31" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="H8" s="33"/>
     </row>
     <row r="9" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="20" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B9" s="20" t="s">
         <v>134</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D9" s="20"/>
       <c r="E9" s="20"/>
       <c r="F9" s="20"/>
       <c r="G9" s="33" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="H9" s="20"/>
     </row>
     <row r="10" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="30" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B10" s="30" t="s">
         <v>142</v>
       </c>
       <c r="C10" s="30" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D10" s="30"/>
       <c r="E10" s="30"/>
       <c r="F10" s="30"/>
       <c r="G10" s="31" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="H10" s="20"/>
     </row>
@@ -3861,14 +3737,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="52" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
       <c r="G1" s="21"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -3888,7 +3764,7 @@
         <v>92</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G2" s="16"/>
     </row>
@@ -3900,7 +3776,7 @@
         <v>78</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>139</v>
@@ -3917,7 +3793,7 @@
         <v>79</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D4" s="19" t="s">
         <v>84</v>
@@ -3934,7 +3810,7 @@
         <v>20</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>21</v>
@@ -3953,7 +3829,7 @@
         <v>80</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>85</v>
@@ -3970,7 +3846,7 @@
         <v>81</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D7" s="12" t="s">
         <v>160</v>
@@ -3987,7 +3863,7 @@
         <v>82</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D8" s="19" t="s">
         <v>160</v>
@@ -4004,7 +3880,7 @@
         <v>99</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D9" s="12" t="s">
         <v>86</v>
@@ -4021,7 +3897,7 @@
         <v>83</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D10" s="19" t="s">
         <v>87</v>
@@ -4076,7 +3952,7 @@
         <v>140</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D13" s="20" t="s">
         <v>21</v>
@@ -4096,7 +3972,7 @@
         <v>141</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>21</v>
@@ -4112,7 +3988,7 @@
         <v>89</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D15" s="20" t="s">
         <v>21</v>
@@ -4128,7 +4004,7 @@
         <v>90</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D16" s="19" t="s">
         <v>21</v>
@@ -4145,7 +4021,7 @@
         <v>91</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D17" s="12" t="s">
         <v>88</v>
@@ -4158,10 +4034,10 @@
         <v>159</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D18" s="19"/>
       <c r="E18" s="19"/>
@@ -4172,10 +4048,10 @@
         <v>159</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
@@ -4208,17 +4084,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="52" t="s">
         <v>94</v>
       </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
     </row>
     <row r="2" spans="1:9" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
@@ -4231,22 +4107,22 @@
         <v>2</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>246</v>
-      </c>
       <c r="G2" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -4257,7 +4133,7 @@
         <v>95</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D3" s="12"/>
       <c r="E3" s="2" t="s">
@@ -4269,7 +4145,7 @@
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="12" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -4280,7 +4156,7 @@
         <v>96</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D4" s="22" t="s">
         <v>95</v>
@@ -4289,16 +4165,16 @@
         <v>156</v>
       </c>
       <c r="F4" s="22" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G4" s="22" t="s">
         <v>80</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="I4" s="22" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -4309,7 +4185,7 @@
         <v>97</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D5" s="20" t="s">
         <v>96</v>
@@ -4318,14 +4194,14 @@
         <v>14</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G5" s="12" t="s">
         <v>80</v>
       </c>
       <c r="H5" s="12"/>
       <c r="I5" s="12" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -4336,7 +4212,7 @@
         <v>98</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D6" s="22" t="s">
         <v>97</v>
@@ -4350,7 +4226,7 @@
       </c>
       <c r="H6" s="22"/>
       <c r="I6" s="22" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -4358,10 +4234,10 @@
         <v>120</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D7" s="20" t="s">
         <v>98</v>
@@ -4372,10 +4248,10 @@
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -4386,23 +4262,23 @@
         <v>100</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>14</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G8" s="22" t="s">
         <v>83</v>
       </c>
       <c r="H8" s="22"/>
       <c r="I8" s="22" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -4413,7 +4289,7 @@
         <v>101</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D9" s="33" t="s">
         <v>100</v>
@@ -4427,7 +4303,7 @@
       </c>
       <c r="H9" s="12"/>
       <c r="I9" s="12" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -4435,10 +4311,10 @@
         <v>120</v>
       </c>
       <c r="B10" s="22" t="s">
+        <v>218</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>219</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>220</v>
       </c>
       <c r="D10" s="22" t="s">
         <v>101</v>
@@ -4454,7 +4330,7 @@
       </c>
       <c r="H10" s="22"/>
       <c r="I10" s="22" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -4465,10 +4341,10 @@
         <v>102</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E11" s="12" t="s">
         <v>124</v>
@@ -4481,7 +4357,7 @@
       </c>
       <c r="H11" s="12"/>
       <c r="I11" s="12" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -4492,7 +4368,7 @@
         <v>103</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D12" s="22" t="s">
         <v>102</v>
@@ -4506,7 +4382,7 @@
       </c>
       <c r="H12" s="22"/>
       <c r="I12" s="22" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -4517,7 +4393,7 @@
         <v>104</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D13" s="20" t="s">
         <v>103</v>
@@ -4531,7 +4407,7 @@
       </c>
       <c r="H13" s="12"/>
       <c r="I13" s="12" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -4542,7 +4418,7 @@
         <v>105</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D14" s="22" t="s">
         <v>104</v>
@@ -4554,7 +4430,7 @@
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
       <c r="I14" s="22" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="9" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
@@ -4565,7 +4441,7 @@
         <v>132</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D15" s="20" t="s">
         <v>105</v>
@@ -4577,7 +4453,7 @@
       <c r="G15" s="12"/>
       <c r="H15" s="12"/>
       <c r="I15" s="12" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -4588,7 +4464,7 @@
         <v>106</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D16" s="22" t="s">
         <v>132</v>
@@ -4600,7 +4476,7 @@
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
       <c r="I16" s="22" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -4611,7 +4487,7 @@
         <v>107</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D17" s="20" t="s">
         <v>106</v>
@@ -4625,7 +4501,7 @@
       <c r="G17" s="12"/>
       <c r="H17" s="12"/>
       <c r="I17" s="12" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="18" spans="1:9" s="9" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
@@ -4633,10 +4509,10 @@
         <v>120</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D18" s="22" t="s">
         <v>107</v>
@@ -4648,7 +4524,7 @@
       <c r="G18" s="7"/>
       <c r="H18" s="7"/>
       <c r="I18" s="22" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -4659,10 +4535,10 @@
         <v>108</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>126</v>
@@ -4671,7 +4547,7 @@
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="12" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -4682,7 +4558,7 @@
         <v>109</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D20" s="22" t="s">
         <v>108</v>
@@ -4694,7 +4570,7 @@
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
       <c r="I20" s="22" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -4705,19 +4581,19 @@
         <v>110</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D21" s="20" t="s">
         <v>109</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="12" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
@@ -4747,14 +4623,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="52" t="s">
         <v>111</v>
       </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
@@ -4770,10 +4646,10 @@
         <v>127</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H2" s="9"/>
     </row>
@@ -4785,14 +4661,14 @@
         <v>27</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>95</v>
       </c>
       <c r="E3" s="23"/>
       <c r="F3" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="G3" s="9"/>
       <c r="H3" s="9"/>
@@ -4805,14 +4681,14 @@
         <v>28</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>95</v>
       </c>
       <c r="E4" s="34"/>
       <c r="F4" s="8" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="G4" s="9"/>
       <c r="H4" s="9"/>
@@ -4825,12 +4701,12 @@
         <v>29</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="23"/>
       <c r="F5" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="G5" s="9"/>
       <c r="H5" s="9"/>
@@ -4843,12 +4719,12 @@
         <v>31</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="34"/>
       <c r="F6" s="8" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="G6" s="9"/>
     </row>
@@ -4860,16 +4736,16 @@
         <v>32</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>96</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="G7" s="9"/>
     </row>
@@ -4881,16 +4757,16 @@
         <v>33</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="D8" s="24" t="s">
         <v>97</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="G8" s="9"/>
     </row>
@@ -4902,14 +4778,14 @@
         <v>34</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="D9" s="12" t="s">
         <v>98</v>
       </c>
       <c r="E9" s="23"/>
       <c r="F9" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="G9" s="9"/>
     </row>
@@ -4921,16 +4797,16 @@
         <v>35</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="G10" s="9"/>
     </row>
@@ -4942,16 +4818,16 @@
         <v>36</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="D11" s="12" t="s">
         <v>100</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="G11" s="9"/>
     </row>
@@ -4963,16 +4839,16 @@
         <v>37</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>100</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="G12" s="9"/>
     </row>
@@ -4984,14 +4860,14 @@
         <v>38</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="D13" s="12" t="s">
         <v>101</v>
       </c>
       <c r="E13" s="23"/>
       <c r="F13" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="G13" s="9"/>
     </row>
@@ -5003,14 +4879,14 @@
         <v>39</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E14" s="34"/>
       <c r="F14" s="8" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="G14" s="9"/>
     </row>
@@ -5022,14 +4898,14 @@
         <v>40</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="D15" s="12" t="s">
         <v>102</v>
       </c>
       <c r="E15" s="23"/>
       <c r="F15" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="G15" s="9"/>
     </row>
@@ -5041,14 +4917,14 @@
         <v>41</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>102</v>
       </c>
       <c r="E16" s="34"/>
       <c r="F16" s="8" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="G16" s="9"/>
     </row>
@@ -5060,14 +4936,14 @@
         <v>42</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="D17" s="12" t="s">
         <v>103</v>
       </c>
       <c r="E17" s="23"/>
       <c r="F17" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="G17" s="9"/>
     </row>
@@ -5079,14 +4955,14 @@
         <v>43</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="D18" s="8" t="s">
         <v>104</v>
       </c>
       <c r="E18" s="34"/>
       <c r="F18" s="8" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="G18" s="9"/>
     </row>
@@ -5098,14 +4974,14 @@
         <v>44</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>105</v>
       </c>
       <c r="E19" s="23"/>
       <c r="F19" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="G19" s="9"/>
     </row>
@@ -5117,14 +4993,14 @@
         <v>45</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>106</v>
       </c>
       <c r="E20" s="34"/>
       <c r="F20" s="8" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="G20" s="9"/>
     </row>
@@ -5136,14 +5012,14 @@
         <v>46</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="D21" s="12" t="s">
         <v>107</v>
       </c>
       <c r="E21" s="35"/>
       <c r="F21" s="43" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -5154,14 +5030,14 @@
         <v>47</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E22" s="34"/>
       <c r="F22" s="8" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="G22" s="9"/>
     </row>
@@ -5173,16 +5049,16 @@
         <v>48</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="D23" s="12" t="s">
         <v>108</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="G23" s="9"/>
     </row>
@@ -5194,14 +5070,14 @@
         <v>49</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="D24" s="24" t="s">
         <v>109</v>
       </c>
       <c r="E24" s="34"/>
       <c r="F24" s="8" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="G24" s="9"/>
     </row>
@@ -5213,14 +5089,14 @@
         <v>128</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="D25" s="12" t="s">
         <v>110</v>
       </c>
       <c r="E25" s="12"/>
       <c r="F25" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="G25" s="9"/>
     </row>
@@ -5287,23 +5163,23 @@
     <col min="2" max="2" width="32" customWidth="1"/>
     <col min="3" max="3" width="35" customWidth="1"/>
     <col min="4" max="4" width="26.109375" customWidth="1"/>
-    <col min="5" max="7" width="26.109375" style="47" customWidth="1"/>
-    <col min="8" max="8" width="21" style="48" customWidth="1"/>
+    <col min="5" max="7" width="26.109375" style="46" customWidth="1"/>
+    <col min="8" max="8" width="21" style="47" customWidth="1"/>
     <col min="9" max="9" width="39" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
     </row>
     <row r="2" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
@@ -5316,39 +5192,39 @@
         <v>2</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="F3" s="20" t="s">
         <v>14</v>
@@ -5360,45 +5236,45 @@
       <c r="I3" s="20"/>
     </row>
     <row r="4" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="50" t="s">
-        <v>391</v>
-      </c>
-      <c r="B4" s="50" t="s">
-        <v>398</v>
-      </c>
-      <c r="C4" s="50" t="s">
-        <v>411</v>
-      </c>
-      <c r="D4" s="50" t="s">
-        <v>399</v>
-      </c>
-      <c r="E4" s="50" t="s">
-        <v>397</v>
-      </c>
-      <c r="F4" s="50" t="s">
+      <c r="A4" s="49" t="s">
+        <v>381</v>
+      </c>
+      <c r="B4" s="49" t="s">
+        <v>388</v>
+      </c>
+      <c r="C4" s="49" t="s">
+        <v>401</v>
+      </c>
+      <c r="D4" s="49" t="s">
+        <v>389</v>
+      </c>
+      <c r="E4" s="49" t="s">
+        <v>387</v>
+      </c>
+      <c r="F4" s="49" t="s">
         <v>64</v>
       </c>
-      <c r="G4" s="50" t="s">
+      <c r="G4" s="49" t="s">
         <v>95</v>
       </c>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
+      <c r="H4" s="49"/>
+      <c r="I4" s="49"/>
     </row>
     <row r="5" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="20" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="D5" s="20" t="s">
         <v>135</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="F5" s="20" t="s">
         <v>14</v>
@@ -5410,95 +5286,95 @@
       <c r="I5" s="20"/>
     </row>
     <row r="6" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="50" t="s">
-        <v>391</v>
-      </c>
-      <c r="B6" s="50" t="s">
-        <v>406</v>
-      </c>
-      <c r="C6" s="50" t="s">
-        <v>413</v>
-      </c>
-      <c r="D6" s="50" t="s">
+      <c r="A6" s="49" t="s">
+        <v>381</v>
+      </c>
+      <c r="B6" s="49" t="s">
+        <v>396</v>
+      </c>
+      <c r="C6" s="49" t="s">
+        <v>403</v>
+      </c>
+      <c r="D6" s="49" t="s">
         <v>135</v>
       </c>
-      <c r="E6" s="50" t="s">
-        <v>408</v>
-      </c>
-      <c r="F6" s="50" t="s">
+      <c r="E6" s="49" t="s">
+        <v>398</v>
+      </c>
+      <c r="F6" s="49" t="s">
         <v>65</v>
       </c>
-      <c r="G6" s="50" t="s">
+      <c r="G6" s="49" t="s">
         <v>108</v>
       </c>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
+      <c r="H6" s="49"/>
+      <c r="I6" s="49"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="20" t="s">
+        <v>381</v>
+      </c>
+      <c r="B7" s="20" t="s">
         <v>391</v>
       </c>
-      <c r="B7" s="20" t="s">
-        <v>401</v>
-      </c>
       <c r="C7" s="20" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="F7" s="20" t="s">
         <v>65</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H7" s="20"/>
       <c r="I7" s="20"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="50" t="s">
-        <v>391</v>
-      </c>
-      <c r="B8" s="50" t="s">
-        <v>402</v>
-      </c>
-      <c r="C8" s="50" t="s">
-        <v>415</v>
-      </c>
-      <c r="D8" s="50" t="s">
-        <v>400</v>
-      </c>
-      <c r="E8" s="50" t="s">
-        <v>397</v>
-      </c>
-      <c r="F8" s="50" t="s">
+      <c r="A8" s="49" t="s">
+        <v>381</v>
+      </c>
+      <c r="B8" s="49" t="s">
+        <v>392</v>
+      </c>
+      <c r="C8" s="49" t="s">
+        <v>405</v>
+      </c>
+      <c r="D8" s="49" t="s">
+        <v>390</v>
+      </c>
+      <c r="E8" s="49" t="s">
+        <v>387</v>
+      </c>
+      <c r="F8" s="49" t="s">
         <v>66</v>
       </c>
-      <c r="G8" s="50" t="s">
-        <v>261</v>
-      </c>
-      <c r="H8" s="50"/>
-      <c r="I8" s="50"/>
+      <c r="G8" s="49" t="s">
+        <v>260</v>
+      </c>
+      <c r="H8" s="49"/>
+      <c r="I8" s="49"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="20" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="F9" s="20" t="s">
         <v>65</v>
@@ -5510,48 +5386,48 @@
       <c r="I9" s="20"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="50" t="s">
-        <v>391</v>
-      </c>
-      <c r="B10" s="50" t="s">
-        <v>404</v>
-      </c>
-      <c r="C10" s="50" t="s">
-        <v>417</v>
-      </c>
-      <c r="D10" s="50" t="s">
-        <v>405</v>
-      </c>
-      <c r="E10" s="50" t="s">
-        <v>392</v>
-      </c>
-      <c r="F10" s="50" t="s">
+      <c r="A10" s="49" t="s">
+        <v>381</v>
+      </c>
+      <c r="B10" s="49" t="s">
+        <v>394</v>
+      </c>
+      <c r="C10" s="49" t="s">
+        <v>407</v>
+      </c>
+      <c r="D10" s="49" t="s">
+        <v>395</v>
+      </c>
+      <c r="E10" s="49" t="s">
+        <v>382</v>
+      </c>
+      <c r="F10" s="49" t="s">
         <v>70</v>
       </c>
-      <c r="G10" s="50" t="s">
+      <c r="G10" s="49" t="s">
         <v>109</v>
       </c>
-      <c r="H10" s="50"/>
-      <c r="I10" s="50"/>
+      <c r="H10" s="49"/>
+      <c r="I10" s="49"/>
     </row>
     <row r="11" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A11" s="20" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G11" s="33" t="s">
         <v>105</v>
@@ -5560,24 +5436,24 @@
       <c r="I11" s="20"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="50" t="s">
+      <c r="A12" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="B12" s="50" t="s">
-        <v>326</v>
-      </c>
-      <c r="C12" s="50" t="s">
-        <v>324</v>
-      </c>
-      <c r="D12" s="50"/>
-      <c r="E12" s="50"/>
-      <c r="F12" s="50"/>
-      <c r="G12" s="50"/>
-      <c r="H12" s="54" t="s">
+      <c r="B12" s="49" t="s">
+        <v>316</v>
+      </c>
+      <c r="C12" s="49" t="s">
+        <v>314</v>
+      </c>
+      <c r="D12" s="49"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="49"/>
+      <c r="G12" s="49"/>
+      <c r="H12" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="I12" s="50" t="s">
-        <v>329</v>
+      <c r="I12" s="49" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
@@ -5585,10 +5461,10 @@
         <v>50</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="D13" s="20"/>
       <c r="E13" s="20"/>
@@ -5598,7 +5474,7 @@
         <v>65</v>
       </c>
       <c r="I13" s="33" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
@@ -5621,40 +5497,40 @@
       <c r="F16"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="49"/>
+      <c r="A17" s="48"/>
       <c r="E17"/>
       <c r="F17"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="49"/>
+      <c r="A18" s="48"/>
       <c r="E18"/>
       <c r="F18"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="49"/>
-      <c r="C19" s="47"/>
+      <c r="A19" s="48"/>
+      <c r="C19" s="46"/>
       <c r="E19"/>
       <c r="F19"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C20" s="47"/>
+      <c r="C20" s="46"/>
       <c r="E20"/>
       <c r="F20"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C21" s="47"/>
+      <c r="C21" s="46"/>
       <c r="E21"/>
       <c r="F21"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C22" s="47"/>
-      <c r="D22" s="47"/>
+      <c r="C22" s="46"/>
+      <c r="D22" s="46"/>
       <c r="E22"/>
       <c r="F22"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C23" s="47"/>
-      <c r="D23" s="47"/>
+      <c r="C23" s="46"/>
+      <c r="D23" s="46"/>
       <c r="E23"/>
       <c r="F23"/>
     </row>
@@ -5716,12 +5592,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="52" t="s">
         <v>114</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
     </row>
     <row r="2" spans="1:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
@@ -5745,7 +5621,7 @@
         <v>115</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>14</v>
@@ -5759,7 +5635,7 @@
         <v>116</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D4" s="19" t="s">
         <v>14</v>
@@ -5773,7 +5649,7 @@
         <v>117</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D5" s="12" t="s">
         <v>14</v>
@@ -5784,10 +5660,10 @@
         <v>52</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>100</v>
@@ -5798,10 +5674,10 @@
         <v>52</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D7" s="12" t="s">
         <v>110</v>
@@ -5812,10 +5688,10 @@
         <v>52</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D8" s="19" t="s">
         <v>97</v>
@@ -5826,13 +5702,13 @@
         <v>52</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">

--- a/data/Capus_LHommeBicycle_1893/Capus_LHommeBicycle_1893.xlsx
+++ b/data/Capus_LHommeBicycle_1893/Capus_LHommeBicycle_1893.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mathilde\Desktop\Doctorat - 2025-2028\Pipeline\SFonto\data\Capus_LHommeBicycle_1893\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDE25BBE-F34B-4549-84E0-235367802289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18995BC7-85F8-4A42-9B0E-EE23C5B7525E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Work" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="424">
   <si>
     <t>Classe</t>
   </si>
@@ -1190,10 +1190,6 @@
     <t>HP9i is personality of</t>
   </si>
   <si>
-    <t>:Event_doctor_consultation,
-:Event_surgeon_consultation</t>
-  </si>
-  <si>
     <t>H7_Relationship_Assignment</t>
   </si>
   <si>
@@ -1306,6 +1302,24 @@
   </si>
   <si>
     <t>value</t>
+  </si>
+  <si>
+    <t>:Sequence_Fabula</t>
+  </si>
+  <si>
+    <t>:Sequence_Syuzhet</t>
+  </si>
+  <si>
+    <t>:Sequence_Medicine_fails_to_diagnose_a_disease</t>
+  </si>
+  <si>
+    <t>:Sequence_Bicycle_hybridization</t>
+  </si>
+  <si>
+    <t>:Sequence_Hybrid_race_birth</t>
+  </si>
+  <si>
+    <t>:Sequence_Mastering_bicycle</t>
   </si>
 </sst>
 </file>
@@ -1456,7 +1470,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1494,11 +1508,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1625,6 +1650,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2234,7 +2262,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -2274,8 +2302,8 @@
       <c r="A3" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="B3" s="22" t="s">
-        <v>54</v>
+      <c r="B3" s="7" t="s">
+        <v>418</v>
       </c>
       <c r="C3" s="22" t="s">
         <v>55</v>
@@ -2533,8 +2561,8 @@
       <c r="A26" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="B26" s="20" t="s">
-        <v>56</v>
+      <c r="B26" s="33" t="s">
+        <v>419</v>
       </c>
       <c r="C26" s="20" t="s">
         <v>57</v>
@@ -2786,6 +2814,110 @@
       </c>
       <c r="E48" s="20" t="s">
         <v>308</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A49" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="C49" s="22"/>
+      <c r="D49" s="22" t="s">
+        <v>263</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" s="20"/>
+      <c r="B50" s="20"/>
+      <c r="C50" s="20"/>
+      <c r="D50" s="20" t="s">
+        <v>264</v>
+      </c>
+      <c r="E50" s="33" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" s="22"/>
+      <c r="B51" s="22"/>
+      <c r="C51" s="22"/>
+      <c r="D51" s="22" t="s">
+        <v>265</v>
+      </c>
+      <c r="E51" s="55" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="B52" s="33" t="s">
+        <v>421</v>
+      </c>
+      <c r="C52" s="20"/>
+      <c r="D52" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="E52" s="20" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" s="22"/>
+      <c r="B53" s="22"/>
+      <c r="C53" s="22"/>
+      <c r="D53" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="B54" s="33" t="s">
+        <v>422</v>
+      </c>
+      <c r="C54" s="20"/>
+      <c r="D54" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="E54" s="20" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55" s="22"/>
+      <c r="B55" s="22"/>
+      <c r="C55" s="22"/>
+      <c r="D55" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" s="33" t="s">
+        <v>53</v>
+      </c>
+      <c r="B56" s="33" t="s">
+        <v>423</v>
+      </c>
+      <c r="C56" s="20"/>
+      <c r="D56" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="E56" s="20" t="s">
+        <v>291</v>
       </c>
     </row>
   </sheetData>
@@ -2849,10 +2981,10 @@
         <v>241</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>417</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>418</v>
       </c>
       <c r="H2" s="10" t="s">
         <v>254</v>
@@ -4034,7 +4166,7 @@
         <v>159</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C18" s="19" t="s">
         <v>209</v>
@@ -4048,7 +4180,7 @@
         <v>159</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>210</v>
@@ -4119,7 +4251,7 @@
         <v>243</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I2" s="10" t="s">
         <v>261</v>
@@ -4171,7 +4303,7 @@
         <v>80</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="I4" s="22" t="s">
         <v>262</v>
@@ -4248,7 +4380,7 @@
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="I7" s="12" t="s">
         <v>262</v>
@@ -5192,19 +5324,19 @@
         <v>2</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="I2" s="10" t="s">
         <v>318</v>
@@ -5212,19 +5344,19 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
+        <v>380</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>382</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>399</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>388</v>
+      </c>
+      <c r="E3" s="20" t="s">
         <v>381</v>
-      </c>
-      <c r="B3" s="20" t="s">
-        <v>383</v>
-      </c>
-      <c r="C3" s="20" t="s">
-        <v>400</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>389</v>
-      </c>
-      <c r="E3" s="20" t="s">
-        <v>382</v>
       </c>
       <c r="F3" s="20" t="s">
         <v>14</v>
@@ -5237,19 +5369,19 @@
     </row>
     <row r="4" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B4" s="49" t="s">
+        <v>387</v>
+      </c>
+      <c r="C4" s="49" t="s">
+        <v>400</v>
+      </c>
+      <c r="D4" s="49" t="s">
         <v>388</v>
       </c>
-      <c r="C4" s="49" t="s">
-        <v>401</v>
-      </c>
-      <c r="D4" s="49" t="s">
-        <v>389</v>
-      </c>
       <c r="E4" s="49" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="F4" s="49" t="s">
         <v>64</v>
@@ -5262,19 +5394,19 @@
     </row>
     <row r="5" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="20" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D5" s="20" t="s">
         <v>135</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="F5" s="20" t="s">
         <v>14</v>
@@ -5287,19 +5419,19 @@
     </row>
     <row r="6" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="49" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B6" s="49" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C6" s="49" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D6" s="49" t="s">
         <v>135</v>
       </c>
       <c r="E6" s="49" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="F6" s="49" t="s">
         <v>65</v>
@@ -5312,19 +5444,19 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="20" t="s">
+        <v>380</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>390</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>403</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>389</v>
+      </c>
+      <c r="E7" s="20" t="s">
         <v>381</v>
-      </c>
-      <c r="B7" s="20" t="s">
-        <v>391</v>
-      </c>
-      <c r="C7" s="20" t="s">
-        <v>404</v>
-      </c>
-      <c r="D7" s="20" t="s">
-        <v>390</v>
-      </c>
-      <c r="E7" s="20" t="s">
-        <v>382</v>
       </c>
       <c r="F7" s="20" t="s">
         <v>65</v>
@@ -5337,19 +5469,19 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="49" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B8" s="49" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C8" s="49" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D8" s="49" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E8" s="49" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="F8" s="49" t="s">
         <v>66</v>
@@ -5362,19 +5494,19 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="20" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="F9" s="20" t="s">
         <v>65</v>
@@ -5387,19 +5519,19 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="49" t="s">
+        <v>380</v>
+      </c>
+      <c r="B10" s="49" t="s">
+        <v>393</v>
+      </c>
+      <c r="C10" s="49" t="s">
+        <v>406</v>
+      </c>
+      <c r="D10" s="49" t="s">
+        <v>394</v>
+      </c>
+      <c r="E10" s="49" t="s">
         <v>381</v>
-      </c>
-      <c r="B10" s="49" t="s">
-        <v>394</v>
-      </c>
-      <c r="C10" s="49" t="s">
-        <v>407</v>
-      </c>
-      <c r="D10" s="49" t="s">
-        <v>395</v>
-      </c>
-      <c r="E10" s="49" t="s">
-        <v>382</v>
       </c>
       <c r="F10" s="49" t="s">
         <v>70</v>
@@ -5412,19 +5544,19 @@
     </row>
     <row r="11" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A11" s="20" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B11" s="20" t="s">
+        <v>407</v>
+      </c>
+      <c r="C11" s="20" t="s">
         <v>408</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="D11" s="20" t="s">
         <v>409</v>
       </c>
-      <c r="D11" s="20" t="s">
+      <c r="E11" s="20" t="s">
         <v>410</v>
-      </c>
-      <c r="E11" s="20" t="s">
-        <v>411</v>
       </c>
       <c r="F11" s="20" t="s">
         <v>194</v>
@@ -5474,7 +5606,7 @@
         <v>65</v>
       </c>
       <c r="I13" s="33" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
@@ -5655,7 +5787,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
         <v>52</v>
       </c>
@@ -5665,8 +5797,8 @@
       <c r="C6" s="19" t="s">
         <v>234</v>
       </c>
-      <c r="D6" s="19" t="s">
-        <v>100</v>
+      <c r="D6" s="6" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -5679,8 +5811,8 @@
       <c r="C7" s="12" t="s">
         <v>235</v>
       </c>
-      <c r="D7" s="12" t="s">
-        <v>110</v>
+      <c r="D7" s="2" t="s">
+        <v>422</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
@@ -5693,8 +5825,8 @@
       <c r="C8" s="19" t="s">
         <v>236</v>
       </c>
-      <c r="D8" s="19" t="s">
-        <v>97</v>
+      <c r="D8" s="6" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
@@ -5707,8 +5839,8 @@
       <c r="C9" s="12" t="s">
         <v>237</v>
       </c>
-      <c r="D9" s="12" t="s">
-        <v>380</v>
+      <c r="D9" s="2" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
